--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Patient</t>
+    <t>This StructureDefinition contains the maps for VistA PATIENT (file 2) to FHIR Patient</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3980" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,7 +333,7 @@
 Outpat.Workload.PatientReligionCode</t>
   </si>
   <si>
-    <t>1598: terminologyMaps using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (#2-.08)</t>
+    <t>1598: transform using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (#2-.08)</t>
   </si>
   <si>
     <t>Patient.extension.id</t>
@@ -358,19 +358,6 @@
     <t>Patient.extension.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
@@ -415,6 +402,12 @@
   </si>
   <si>
     <t>valueCode</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFgenderIdentity</t>
   </si>
   <si>
     <t>Patient.Patient.Gender
@@ -497,11 +490,18 @@
     <t>Patient.modifierExtension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -553,6 +553,12 @@
     <t>Patient.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t>Patient.identifier.use</t>
   </si>
   <si>
@@ -566,9 +572,6 @@
   </si>
   <si>
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>Identifies the purpose for this identifier, if known .</t>
@@ -1113,9 +1116,6 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
-  </si>
-  <si>
     <t>.patient.administrativeGenderCode</t>
   </si>
   <si>
@@ -1593,10 +1593,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://va.gov/fhir/ValueSet/VFMaritalStatus</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -3585,14 +3582,14 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>38</v>
@@ -3607,14 +3604,12 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>38</v>
@@ -3654,7 +3649,7 @@
         <v>94</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>38</v>
@@ -3663,7 +3658,7 @@
         <v>95</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -3678,7 +3673,7 @@
         <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>38</v>
@@ -3701,10 +3696,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3730,13 +3725,13 @@
         <v>60</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3786,7 +3781,7 @@
         <v>38</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>46</v>
@@ -3824,10 +3819,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3853,10 +3848,10 @@
         <v>66</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3895,17 +3890,17 @@
         <v>38</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3943,13 +3938,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>38</v>
@@ -3974,10 +3969,10 @@
         <v>66</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -4004,13 +3999,11 @@
         <v>38</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>38</v>
@@ -4028,7 +4021,7 @@
         <v>38</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
@@ -4058,21 +4051,21 @@
         <v>38</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>38</v>
@@ -4094,13 +4087,13 @@
         <v>38</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4160,7 +4153,7 @@
         <v>37</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>97</v>
@@ -4189,13 +4182,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>38</v>
@@ -4217,13 +4210,13 @@
         <v>38</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4283,7 +4276,7 @@
         <v>37</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>97</v>
@@ -4312,13 +4305,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>38</v>
@@ -4340,16 +4333,16 @@
         <v>38</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4408,13 +4401,13 @@
         <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>38</v>
@@ -4437,13 +4430,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>38</v>
@@ -4465,7 +4458,7 @@
         <v>38</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>92</v>
@@ -4531,7 +4524,7 @@
         <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>97</v>
@@ -4560,14 +4553,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4589,13 +4582,13 @@
         <v>91</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>151</v>
@@ -4936,7 +4929,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4958,13 +4951,13 @@
         <v>91</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -5005,7 +4998,7 @@
         <v>94</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>38</v>
@@ -5014,7 +5007,7 @@
         <v>95</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -5052,10 +5045,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5081,16 +5074,16 @@
         <v>66</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>38</v>
@@ -5115,13 +5108,13 @@
         <v>38</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>38</v>
@@ -5139,7 +5132,7 @@
         <v>38</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -5154,7 +5147,7 @@
         <v>58</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>38</v>
@@ -5177,10 +5170,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5203,19 +5196,19 @@
         <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>38</v>
@@ -5240,13 +5233,13 @@
         <v>38</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>38</v>
@@ -5264,7 +5257,7 @@
         <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -5279,7 +5272,7 @@
         <v>58</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>38</v>
@@ -5288,7 +5281,7 @@
         <v>38</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>38</v>
@@ -5302,10 +5295,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5331,16 +5324,16 @@
         <v>60</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>38</v>
@@ -5353,7 +5346,7 @@
         <v>38</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>38</v>
@@ -5389,7 +5382,7 @@
         <v>38</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -5404,7 +5397,7 @@
         <v>58</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>38</v>
@@ -5413,7 +5406,7 @@
         <v>38</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>38</v>
@@ -5427,10 +5420,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5456,13 +5449,13 @@
         <v>101</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5476,7 +5469,7 @@
         <v>38</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>38</v>
@@ -5512,7 +5505,7 @@
         <v>38</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -5527,7 +5520,7 @@
         <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>38</v>
@@ -5536,7 +5529,7 @@
         <v>38</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>38</v>
@@ -5550,10 +5543,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5576,13 +5569,13 @@
         <v>47</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5633,7 +5626,7 @@
         <v>38</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -5648,7 +5641,7 @@
         <v>58</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>38</v>
@@ -5657,7 +5650,7 @@
         <v>38</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>38</v>
@@ -5671,10 +5664,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5697,16 +5690,16 @@
         <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5756,7 +5749,7 @@
         <v>38</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -5771,7 +5764,7 @@
         <v>58</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>38</v>
@@ -5780,7 +5773,7 @@
         <v>38</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>38</v>
@@ -5794,10 +5787,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5820,70 +5813,70 @@
         <v>47</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="R28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="R28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -5898,13 +5891,13 @@
         <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>38</v>
@@ -5921,10 +5914,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5947,19 +5940,19 @@
         <v>47</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>38</v>
@@ -6008,7 +6001,7 @@
         <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -6023,16 +6016,16 @@
         <v>58</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>38</v>
@@ -6046,10 +6039,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6167,14 +6160,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6196,13 +6189,13 @@
         <v>91</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6243,7 +6236,7 @@
         <v>94</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>38</v>
@@ -6252,7 +6245,7 @@
         <v>95</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -6290,10 +6283,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6319,16 +6312,16 @@
         <v>66</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>38</v>
@@ -6353,13 +6346,13 @@
         <v>38</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>38</v>
@@ -6377,7 +6370,7 @@
         <v>38</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -6392,7 +6385,7 @@
         <v>58</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>38</v>
@@ -6401,7 +6394,7 @@
         <v>38</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>38</v>
@@ -6415,10 +6408,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6444,16 +6437,16 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>38</v>
@@ -6502,7 +6495,7 @@
         <v>38</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -6517,7 +6510,7 @@
         <v>58</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>38</v>
@@ -6526,28 +6519,28 @@
         <v>38</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6569,13 +6562,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6625,7 +6618,7 @@
         <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -6634,13 +6627,13 @@
         <v>46</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>38</v>
@@ -6649,7 +6642,7 @@
         <v>38</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>38</v>
@@ -6663,14 +6656,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6692,13 +6685,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6748,7 +6741,7 @@
         <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -6757,13 +6750,13 @@
         <v>37</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>38</v>
@@ -6772,7 +6765,7 @@
         <v>38</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>38</v>
@@ -6786,10 +6779,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6815,10 +6808,10 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6869,7 +6862,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6884,7 +6877,7 @@
         <v>58</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>38</v>
@@ -6893,7 +6886,7 @@
         <v>38</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>38</v>
@@ -6907,10 +6900,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6936,10 +6929,10 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6990,7 +6983,7 @@
         <v>38</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -7005,7 +6998,7 @@
         <v>58</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>38</v>
@@ -7014,7 +7007,7 @@
         <v>38</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>38</v>
@@ -7028,10 +7021,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7054,17 +7047,17 @@
         <v>47</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>38</v>
@@ -7113,7 +7106,7 @@
         <v>38</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -7128,7 +7121,7 @@
         <v>58</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>38</v>
@@ -7137,7 +7130,7 @@
         <v>38</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>38</v>
@@ -7151,10 +7144,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7177,19 +7170,19 @@
         <v>47</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>38</v>
@@ -7238,7 +7231,7 @@
         <v>38</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -7253,16 +7246,16 @@
         <v>58</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>38</v>
@@ -7276,10 +7269,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7397,14 +7390,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7426,13 +7419,13 @@
         <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7473,7 +7466,7 @@
         <v>94</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>38</v>
@@ -7482,7 +7475,7 @@
         <v>95</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -7520,10 +7513,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7549,10 +7542,10 @@
         <v>66</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7579,13 +7572,13 @@
         <v>38</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>38</v>
@@ -7603,7 +7596,7 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -7612,13 +7605,13 @@
         <v>46</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>38</v>
@@ -7627,7 +7620,7 @@
         <v>38</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>38</v>
@@ -7641,10 +7634,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7670,16 +7663,16 @@
         <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>38</v>
@@ -7728,7 +7721,7 @@
         <v>38</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -7743,7 +7736,7 @@
         <v>58</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>38</v>
@@ -7752,7 +7745,7 @@
         <v>38</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>38</v>
@@ -7761,15 +7754,15 @@
         <v>38</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7795,16 +7788,16 @@
         <v>66</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>38</v>
@@ -7829,11 +7822,11 @@
         <v>38</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>38</v>
@@ -7851,7 +7844,7 @@
         <v>38</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -7866,7 +7859,7 @@
         <v>58</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>38</v>
@@ -7875,7 +7868,7 @@
         <v>38</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>38</v>
@@ -7889,10 +7882,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7915,16 +7908,16 @@
         <v>47</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7974,7 +7967,7 @@
         <v>38</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -8012,10 +8005,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8038,13 +8031,13 @@
         <v>47</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8095,7 +8088,7 @@
         <v>38</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -8110,7 +8103,7 @@
         <v>58</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>38</v>
@@ -8133,10 +8126,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8162,16 +8155,16 @@
         <v>66</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>38</v>
@@ -8196,11 +8189,11 @@
         <v>38</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>347</v>
+        <v>123</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>38</v>
@@ -8218,7 +8211,7 @@
         <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -8233,7 +8226,7 @@
         <v>58</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>348</v>
@@ -8456,7 +8449,7 @@
         <v>38</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8884,7 +8877,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8906,13 +8899,13 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8953,7 +8946,7 @@
         <v>94</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>38</v>
@@ -8962,7 +8955,7 @@
         <v>95</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -9063,7 +9056,7 @@
         <v>38</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y54" t="s" s="2">
         <v>394</v>
@@ -9102,7 +9095,7 @@
         <v>58</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>38</v>
@@ -9186,7 +9179,7 @@
         <v>38</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y55" t="s" s="2">
         <v>403</v>
@@ -9225,7 +9218,7 @@
         <v>58</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>38</v>
@@ -9286,7 +9279,7 @@
         <v>410</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>38</v>
@@ -9350,7 +9343,7 @@
         <v>58</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>38</v>
@@ -9797,7 +9790,7 @@
         <v>38</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>446</v>
@@ -10129,7 +10122,7 @@
         <v>47</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>472</v>
@@ -10203,7 +10196,7 @@
         <v>58</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>38</v>
@@ -10354,7 +10347,7 @@
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10376,13 +10369,13 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10423,7 +10416,7 @@
         <v>94</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>38</v>
@@ -10432,7 +10425,7 @@
         <v>95</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -10744,7 +10737,7 @@
         <v>38</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>499</v>
@@ -10779,13 +10772,11 @@
         <v>38</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y68" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>38</v>
@@ -10818,33 +10809,33 @@
         <v>58</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10867,19 +10858,19 @@
         <v>38</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>38</v>
@@ -10928,7 +10919,7 @@
         <v>38</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -10943,7 +10934,7 @@
         <v>58</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>105</v>
@@ -10952,7 +10943,7 @@
         <v>38</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>38</v>
@@ -10966,10 +10957,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10992,19 +10983,19 @@
         <v>38</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>38</v>
@@ -11053,7 +11044,7 @@
         <v>38</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -11068,7 +11059,7 @@
         <v>58</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>105</v>
@@ -11077,7 +11068,7 @@
         <v>38</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>38</v>
@@ -11091,10 +11082,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11117,19 +11108,19 @@
         <v>38</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>38</v>
@@ -11178,7 +11169,7 @@
         <v>38</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -11190,10 +11181,10 @@
         <v>38</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AK71" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>105</v>
@@ -11216,10 +11207,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11337,14 +11328,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11366,13 +11357,13 @@
         <v>91</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11422,7 +11413,7 @@
         <v>38</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -11460,14 +11451,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11489,13 +11480,13 @@
         <v>91</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="N74" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>151</v>
@@ -11547,7 +11538,7 @@
         <v>38</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -11585,10 +11576,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11611,17 +11602,17 @@
         <v>38</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>38</v>
@@ -11646,14 +11637,14 @@
         <v>38</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>545</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>38</v>
       </c>
@@ -11670,7 +11661,7 @@
         <v>38</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11685,7 +11676,7 @@
         <v>58</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>105</v>
@@ -11694,7 +11685,7 @@
         <v>38</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>38</v>
@@ -11708,10 +11699,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11734,17 +11725,17 @@
         <v>38</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>38</v>
@@ -11793,7 +11784,7 @@
         <v>38</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -11808,7 +11799,7 @@
         <v>58</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>105</v>
@@ -11817,7 +11808,7 @@
         <v>38</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>38</v>
@@ -11831,10 +11822,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11857,19 +11848,19 @@
         <v>38</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>38</v>
@@ -11918,7 +11909,7 @@
         <v>38</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -11933,7 +11924,7 @@
         <v>58</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>105</v>
@@ -11942,7 +11933,7 @@
         <v>38</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>38</v>
@@ -11956,10 +11947,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11985,14 +11976,14 @@
         <v>378</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>38</v>
@@ -12041,7 +12032,7 @@
         <v>38</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -12065,7 +12056,7 @@
         <v>38</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>38</v>
@@ -12079,10 +12070,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12108,14 +12099,14 @@
         <v>66</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>38</v>
@@ -12140,14 +12131,14 @@
         <v>38</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="Z79" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="AA79" t="s" s="2">
         <v>38</v>
       </c>
@@ -12164,7 +12155,7 @@
         <v>38</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -12179,7 +12170,7 @@
         <v>58</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>105</v>
@@ -12188,7 +12179,7 @@
         <v>38</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>38</v>
@@ -12202,10 +12193,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12228,17 +12219,17 @@
         <v>38</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>38</v>
@@ -12287,7 +12278,7 @@
         <v>38</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -12296,13 +12287,13 @@
         <v>46</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>105</v>
@@ -12311,7 +12302,7 @@
         <v>38</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>38</v>
@@ -12325,10 +12316,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12351,13 +12342,13 @@
         <v>38</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12408,7 +12399,7 @@
         <v>38</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -12423,7 +12414,7 @@
         <v>58</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>105</v>
@@ -12446,10 +12437,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12472,19 +12463,19 @@
         <v>38</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>38</v>
@@ -12533,7 +12524,7 @@
         <v>38</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -12548,10 +12539,10 @@
         <v>58</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>38</v>
@@ -12571,10 +12562,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12692,14 +12683,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12721,13 +12712,13 @@
         <v>91</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12777,7 +12768,7 @@
         <v>38</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
@@ -12815,14 +12806,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12844,13 +12835,13 @@
         <v>91</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>151</v>
@@ -12902,7 +12893,7 @@
         <v>38</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
@@ -12940,10 +12931,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12966,19 +12957,19 @@
         <v>38</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>38</v>
@@ -13003,11 +12994,11 @@
         <v>38</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>38</v>
@@ -13025,7 +13016,7 @@
         <v>38</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>46</v>
@@ -13040,33 +13031,33 @@
         <v>58</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>599</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13089,19 +13080,19 @@
         <v>38</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>38</v>
@@ -13150,7 +13141,7 @@
         <v>38</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
@@ -13165,16 +13156,16 @@
         <v>58</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>38</v>
@@ -13188,14 +13179,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13214,16 +13205,16 @@
         <v>38</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13273,7 +13264,7 @@
         <v>38</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
@@ -13288,7 +13279,7 @@
         <v>58</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>105</v>
@@ -13297,7 +13288,7 @@
         <v>38</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>38</v>
@@ -13311,10 +13302,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13337,19 +13328,19 @@
         <v>47</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>38</v>
@@ -13398,7 +13389,7 @@
         <v>38</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -13413,10 +13404,10 @@
         <v>58</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>38</v>
@@ -13436,10 +13427,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13557,14 +13548,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13586,13 +13577,13 @@
         <v>91</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13633,7 +13624,7 @@
         <v>94</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>38</v>
@@ -13642,7 +13633,7 @@
         <v>95</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
@@ -13680,10 +13671,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13709,13 +13700,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13765,7 +13756,7 @@
         <v>38</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -13774,7 +13765,7 @@
         <v>46</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>58</v>
@@ -13803,10 +13794,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13832,13 +13823,13 @@
         <v>60</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13864,31 +13855,31 @@
         <v>38</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -13926,10 +13917,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13955,13 +13946,13 @@
         <v>154</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14011,7 +14002,7 @@
         <v>38</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -14026,7 +14017,7 @@
         <v>58</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>38</v>
@@ -14049,10 +14040,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14078,13 +14069,13 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14134,7 +14125,7 @@
         <v>38</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
@@ -14167,15 +14158,15 @@
         <v>38</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14198,19 +14189,19 @@
         <v>47</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>38</v>
@@ -14259,7 +14250,7 @@
         <v>38</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>36</v>
@@ -14274,7 +14265,7 @@
         <v>58</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>105</v>
@@ -14297,10 +14288,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14418,14 +14409,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14447,13 +14438,13 @@
         <v>91</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14503,7 +14494,7 @@
         <v>38</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -14541,14 +14532,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14570,13 +14561,13 @@
         <v>91</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>151</v>
@@ -14628,7 +14619,7 @@
         <v>38</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -14666,10 +14657,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14692,16 +14683,16 @@
         <v>47</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14751,7 +14742,7 @@
         <v>38</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>46</v>
@@ -14775,7 +14766,7 @@
         <v>38</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>38</v>
@@ -14789,10 +14780,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14818,10 +14809,10 @@
         <v>66</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14848,14 +14839,14 @@
         <v>38</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>667</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>38</v>
       </c>
@@ -14872,7 +14863,7 @@
         <v>38</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>46</v>
@@ -14887,7 +14878,7 @@
         <v>58</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>105</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5445" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5445" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -246,10 +246,10 @@
     <t>Mapping: LOINC code for the element</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t xml:space="preserve">SubjectOfCare Client Resident
@@ -799,13 +799,13 @@
     <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity</t>
   </si>
   <si>
+    <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (#2-.02)</t>
+  </si>
+  <si>
     <t>Patient.Patient.Gender
 SPatient.SPatient.Gender</t>
   </si>
   <si>
-    <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (#2-.02)</t>
-  </si>
-  <si>
     <t>Patient.extension:genderIdentity</t>
   </si>
   <si>
@@ -858,6 +858,9 @@
   </si>
   <si>
     <t>PID-3</t>
+  </si>
+  <si>
+    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
   </si>
   <si>
     <t>Patient.Patient.PatientICN
@@ -866,9 +869,6 @@
 SPatient.SPatientGISAddress.PatientICN</t>
   </si>
   <si>
-    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
-  </si>
-  <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
@@ -1153,15 +1153,15 @@
     <t>implied by XPN.11</t>
   </si>
   <si>
+    <t>273: source value from PATIENT - NAME (#2-.01)</t>
+  </si>
+  <si>
     <t>SPatient.SPatient.PatientFirstName
 SPatient.SPatient.PatientLastName
 SPatient.SPatient.PatientName
 SPatient.SPatientAlias.PatientName</t>
   </si>
   <si>
-    <t>273: source value from PATIENT - NAME (#2-.01)</t>
-  </si>
-  <si>
     <t>Patient.name.family</t>
   </si>
   <si>
@@ -1438,13 +1438,13 @@
     <t>PID-8</t>
   </si>
   <si>
+    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
+  </si>
+  <si>
     <t>Patient.Patient.SelfIdentifiedGender
 SPatient.SPatient.SelfIdentifiedGender</t>
   </si>
   <si>
-    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
-  </si>
-  <si>
     <t>Patient.birthDate</t>
   </si>
   <si>
@@ -1476,13 +1476,13 @@
     <t>21112-8</t>
   </si>
   <si>
+    <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
+  </si>
+  <si>
     <t>SPatient.PlaceOfBirth.BirthDateTime
 SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
-    <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
-  </si>
-  <si>
     <t>Patient.deceased[x]</t>
   </si>
   <si>
@@ -1522,13 +1522,13 @@
 </t>
   </si>
   <si>
+    <t>285: source value from PATIENT - DATE OF DEATH (#2-.351) case not null</t>
+  </si>
+  <si>
     <t>Patient.Patient.DeathDateTime
 SPatient.SPatient.DeathDateTime</t>
   </si>
   <si>
-    <t>285: source value from PATIENT - DATE OF DEATH (#2-.351) case not null</t>
-  </si>
-  <si>
     <t>Patient.address</t>
   </si>
   <si>
@@ -1662,10 +1662,10 @@
     <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
   </si>
   <si>
+    <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (#2-.113)</t>
+  </si>
+  <si>
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
-  </si>
-  <si>
-    <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (#2-.113)</t>
   </si>
   <si>
     <t>Patient.address.city</t>
@@ -1693,10 +1693,10 @@
     <t>XAD.3</t>
   </si>
   <si>
+    <t>289: source value from PATIENT - CITY (#2-.114)</t>
+  </si>
+  <si>
     <t>SPatient.SPatientGISAddress.City</t>
-  </si>
-  <si>
-    <t>289: source value from PATIENT - CITY (#2-.114)</t>
   </si>
   <si>
     <t>Patient.address.district</t>
@@ -1755,10 +1755,10 @@
     <t>XAD.4</t>
   </si>
   <si>
+    <t>290: source value from PATIENT - STATE (#2-.115)</t>
+  </si>
+  <si>
     <t>SPatient.SPatientGISAddress.StateIEN</t>
-  </si>
-  <si>
-    <t>290: source value from PATIENT - STATE (#2-.115)</t>
   </si>
   <si>
     <t>Patient.address.postalCode</t>
@@ -1786,10 +1786,10 @@
     <t>XAD.5</t>
   </si>
   <si>
+    <t>291: source value from PATIENT - ZIP+4 (#2-.1112)</t>
+  </si>
+  <si>
     <t>SPatient.SPatientGISAddress.Zip4</t>
-  </si>
-  <si>
-    <t>291: source value from PATIENT - ZIP+4 (#2-.1112)</t>
   </si>
   <si>
     <t>Patient.address.country</t>
@@ -1925,11 +1925,11 @@
     <t>PID-16</t>
   </si>
   <si>
+    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
+  </si>
+  <si>
     <t>Outpat.Visit.PatientMaritalStatus
 Outpat.Workload.PatientMaritalStatus</t>
-  </si>
-  <si>
-    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -2366,6 +2366,10 @@
   </si>
   <si>
     <t>Reference.display</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-20:296: fixed value "Veterans Health Administration" {null}</t>
   </si>
   <si>
     <t>296: fixed value = Veterans Health Administration</t>
@@ -2791,8 +2795,8 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.13671875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="117.13671875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6096,10 +6100,10 @@
         <v>81</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -8536,10 +8540,10 @@
         <v>81</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -12718,10 +12722,10 @@
         <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -15055,10 +15059,10 @@
         <v>81</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -15545,10 +15549,10 @@
         <v>81</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>595</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -15670,10 +15674,10 @@
         <v>81</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>81</v>
+        <v>604</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -18013,10 +18017,10 @@
         <v>81</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>705</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -19104,7 +19108,7 @@
         <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>101</v>
+        <v>754</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>132</v>
@@ -19122,18 +19126,18 @@
         <v>81</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>81</v>
+        <v>755</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>754</v>
+        <v>81</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19159,16 +19163,16 @@
         <v>632</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -19217,7 +19221,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -19232,7 +19236,7 @@
         <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>153</v>
@@ -19255,10 +19259,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19376,10 +19380,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19499,10 +19503,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19624,10 +19628,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19650,16 +19654,16 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19709,7 +19713,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>89</v>
@@ -19733,7 +19737,7 @@
         <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19747,10 +19751,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19776,10 +19780,10 @@
         <v>109</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19809,10 +19813,10 @@
         <v>182</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>81</v>
@@ -19830,7 +19834,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -19845,7 +19849,7 @@
         <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>153</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2369,7 +2369,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-20:296: fixed value "Veterans Health Administration" {null}</t>
+inv-26:296: fixed value = Veterans Health Administration {null}</t>
   </si>
   <si>
     <t>296: fixed value = Veterans Health Administration</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -910,6 +910,120 @@
     <t>PID-3</t>
   </si>
   <si>
+    <t>Patient.identifier.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Patient.identifier.type</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique within the system.</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
     <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
   </si>
   <si>
@@ -917,120 +1031,6 @@
 Patient.PatientICN.PatientICN
 SPatient.SPatient.PatientICN
 SPatient.SPatientGISAddress.PatientICN</t>
-  </si>
-  <si>
-    <t>Patient.identifier.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Patient.identifier.type</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique within the system.</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>Patient.identifier.period</t>
@@ -10514,18 +10514,18 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10643,10 +10643,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10766,10 +10766,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10795,16 +10795,16 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10832,28 +10832,28 @@
         <v>182</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10868,7 +10868,7 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10891,10 +10891,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10920,16 +10920,16 @@
         <v>266</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10954,31 +10954,31 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10993,7 +10993,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -11002,7 +11002,7 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -11016,10 +11016,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11045,16 +11045,16 @@
         <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -11067,7 +11067,7 @@
         <v>81</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>81</v>
@@ -11103,7 +11103,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11118,7 +11118,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
@@ -11127,7 +11127,7 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -11141,10 +11141,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11170,13 +11170,13 @@
         <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11190,7 +11190,7 @@
         <v>81</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>81</v>
@@ -11226,7 +11226,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11241,25 +11241,25 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -15509,7 +15509,7 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y103" t="s" s="2">
         <v>564</v>
@@ -17106,7 +17106,7 @@
         <v>81</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y116" t="s" s="2">
         <v>564</v>
@@ -19195,7 +19195,7 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y133" t="s" s="2">
         <v>564</v>
@@ -20550,7 +20550,7 @@
         <v>81</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y144" t="s" s="2">
         <v>696</v>
@@ -21907,7 +21907,7 @@
         <v>81</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
@@ -22768,7 +22768,7 @@
         <v>81</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y162" t="s" s="2">
         <v>786</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$196</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6647" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7659" uniqueCount="850">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2042,6 +2042,90 @@
   </si>
   <si>
     <t>Patient.address:temp.period</t>
+  </si>
+  <si>
+    <t>Patient.address:physical</t>
+  </si>
+  <si>
+    <t>physical</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.id</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.extension</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.use</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.type</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.text</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.line</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.city</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.district</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.state</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.postalCode</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.country</t>
+  </si>
+  <si>
+    <t>Patient.address:physical.period</t>
+  </si>
+  <si>
+    <t>Patient.address:postal</t>
+  </si>
+  <si>
+    <t>postal</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.id</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.extension</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.use</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.type</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.text</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.line</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.city</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.district</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.state</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.postalCode</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.country</t>
+  </si>
+  <si>
+    <t>Patient.address:postal.period</t>
   </si>
   <si>
     <t>Patient.maritalStatus</t>
@@ -2895,7 +2979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ170"/>
+  <dimension ref="A1:AQ196"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.8515625" customWidth="true" bestFit="true"/>
@@ -19627,9 +19711,11 @@
         <v>651</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
       </c>
@@ -19641,26 +19727,28 @@
         <v>89</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>266</v>
+        <v>499</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>652</v>
+        <v>500</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O137" t="s" s="2">
-        <v>654</v>
+        <v>503</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -19685,11 +19773,13 @@
         <v>81</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>655</v>
+        <v>81</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>81</v>
@@ -19707,13 +19797,13 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>651</v>
+        <v>498</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>81</v>
@@ -19722,33 +19812,33 @@
         <v>101</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>656</v>
+        <v>505</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>657</v>
+        <v>506</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>658</v>
+        <v>507</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>659</v>
+        <v>81</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>660</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>661</v>
+        <v>508</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19771,20 +19861,16 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>662</v>
+        <v>149</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>663</v>
+        <v>150</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
       </c>
@@ -19832,7 +19918,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>661</v>
+        <v>152</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19844,19 +19930,19 @@
         <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>667</v>
+        <v>153</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>668</v>
+        <v>81</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>81</v>
@@ -19870,14 +19956,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>669</v>
+        <v>509</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19896,20 +19982,18 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>670</v>
+        <v>134</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>671</v>
+        <v>157</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>672</v>
+        <v>158</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>81</v>
       </c>
@@ -19945,19 +20029,19 @@
         <v>81</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>669</v>
+        <v>161</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19969,19 +20053,19 @@
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>675</v>
+        <v>153</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>676</v>
+        <v>81</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>81</v>
@@ -19995,10 +20079,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>677</v>
+        <v>655</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>677</v>
+        <v>510</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20009,31 +20093,31 @@
         <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>678</v>
+        <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>679</v>
+        <v>511</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>680</v>
+        <v>512</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>681</v>
+        <v>513</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>682</v>
+        <v>514</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
@@ -20046,7 +20130,7 @@
         <v>81</v>
       </c>
       <c r="T140" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="U140" t="s" s="2">
         <v>81</v>
@@ -20058,13 +20142,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>81</v>
+        <v>516</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -20082,31 +20166,31 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>677</v>
+        <v>518</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>683</v>
+        <v>101</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>684</v>
+        <v>368</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -20120,10 +20204,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>685</v>
+        <v>656</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>685</v>
+        <v>520</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20143,18 +20227,20 @@
         <v>81</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>150</v>
+        <v>521</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -20167,7 +20253,7 @@
         <v>81</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>81</v>
+        <v>524</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>81</v>
@@ -20179,13 +20265,13 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -20203,7 +20289,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>152</v>
+        <v>527</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -20215,10 +20301,10 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>153</v>
+        <v>368</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>81</v>
@@ -20227,7 +20313,7 @@
         <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>81</v>
+        <v>528</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -20241,21 +20327,21 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>686</v>
+        <v>529</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>81</v>
@@ -20264,21 +20350,23 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>157</v>
+        <v>530</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>158</v>
+        <v>531</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -20290,7 +20378,7 @@
         <v>81</v>
       </c>
       <c r="T142" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="U142" t="s" s="2">
         <v>81</v>
@@ -20326,22 +20414,22 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>161</v>
+        <v>534</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>153</v>
+        <v>376</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>81</v>
@@ -20350,7 +20438,7 @@
         <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>81</v>
+        <v>535</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>81</v>
@@ -20364,14 +20452,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>687</v>
+        <v>658</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>687</v>
+        <v>536</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>688</v>
+        <v>81</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -20381,29 +20469,25 @@
         <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J143" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>689</v>
+        <v>537</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>81</v>
       </c>
@@ -20415,7 +20499,7 @@
         <v>81</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>81</v>
@@ -20451,7 +20535,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>691</v>
+        <v>540</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -20463,10 +20547,10 @@
         <v>81</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>132</v>
+        <v>541</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>81</v>
@@ -20475,7 +20559,7 @@
         <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>81</v>
@@ -20489,44 +20573,42 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>692</v>
+        <v>659</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>692</v>
+        <v>543</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>693</v>
+        <v>545</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>694</v>
+        <v>546</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" t="s" s="2">
-        <v>695</v>
-      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>81</v>
       </c>
@@ -20538,7 +20620,7 @@
         <v>81</v>
       </c>
       <c r="T144" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="U144" t="s" s="2">
         <v>81</v>
@@ -20550,13 +20632,13 @@
         <v>81</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>696</v>
+        <v>81</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>697</v>
+        <v>81</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>81</v>
@@ -20574,13 +20656,13 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>692</v>
+        <v>548</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>81</v>
@@ -20589,16 +20671,16 @@
         <v>101</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>698</v>
+        <v>549</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>699</v>
+        <v>550</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -20612,14 +20694,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>700</v>
+        <v>551</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -20635,21 +20717,21 @@
         <v>81</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>701</v>
+        <v>553</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" t="s" s="2">
-        <v>703</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>81</v>
       </c>
@@ -20661,7 +20743,7 @@
         <v>81</v>
       </c>
       <c r="T145" t="s" s="2">
-        <v>81</v>
+        <v>556</v>
       </c>
       <c r="U145" t="s" s="2">
         <v>81</v>
@@ -20697,7 +20779,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>700</v>
+        <v>557</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20712,16 +20794,16 @@
         <v>101</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>355</v>
+        <v>558</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>704</v>
+        <v>559</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>81</v>
@@ -20735,46 +20817,42 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>705</v>
+        <v>661</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>705</v>
+        <v>560</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>706</v>
+        <v>562</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>81</v>
       </c>
@@ -20798,13 +20876,13 @@
         <v>81</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>81</v>
+        <v>565</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>81</v>
@@ -20822,13 +20900,13 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>705</v>
+        <v>566</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>81</v>
@@ -20837,16 +20915,16 @@
         <v>101</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>422</v>
+        <v>567</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>709</v>
+        <v>568</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>81</v>
@@ -20860,14 +20938,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>710</v>
+        <v>662</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>710</v>
+        <v>569</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20877,27 +20955,25 @@
         <v>89</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>499</v>
+        <v>149</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>711</v>
+        <v>571</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>712</v>
+        <v>572</v>
       </c>
       <c r="N147" s="2"/>
-      <c r="O147" t="s" s="2">
-        <v>713</v>
-      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>81</v>
       </c>
@@ -20909,7 +20985,7 @@
         <v>81</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>81</v>
@@ -20945,7 +21021,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>710</v>
+        <v>574</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20960,16 +21036,16 @@
         <v>101</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>714</v>
+        <v>576</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -20983,10 +21059,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>715</v>
+        <v>663</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>715</v>
+        <v>577</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21006,21 +21082,21 @@
         <v>81</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>464</v>
+        <v>578</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>81</v>
       </c>
@@ -21044,13 +21120,13 @@
         <v>81</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>718</v>
+        <v>81</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>719</v>
+        <v>81</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
@@ -21068,7 +21144,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>715</v>
+        <v>581</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -21083,16 +21159,16 @@
         <v>101</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>244</v>
+        <v>582</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>720</v>
+        <v>583</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -21106,10 +21182,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>721</v>
+        <v>664</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>721</v>
+        <v>584</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21123,26 +21199,26 @@
         <v>89</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>722</v>
+        <v>585</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>723</v>
+        <v>586</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>724</v>
+        <v>587</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
@@ -21155,7 +21231,7 @@
         <v>81</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>81</v>
@@ -21191,7 +21267,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>721</v>
+        <v>589</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -21200,22 +21276,22 @@
         <v>89</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>725</v>
+        <v>81</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>726</v>
+        <v>414</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>727</v>
+        <v>590</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>81</v>
@@ -21229,12 +21305,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>728</v>
+        <v>665</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C150" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="D150" t="s" s="2">
         <v>81</v>
       </c>
@@ -21246,25 +21324,29 @@
         <v>89</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>729</v>
+        <v>500</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
       </c>
@@ -21312,13 +21394,13 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>728</v>
+        <v>498</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>81</v>
@@ -21327,16 +21409,16 @@
         <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>731</v>
+        <v>505</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>153</v>
+        <v>506</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -21350,10 +21432,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>732</v>
+        <v>667</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>732</v>
+        <v>508</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21364,7 +21446,7 @@
         <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>81</v>
@@ -21376,20 +21458,16 @@
         <v>81</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>678</v>
+        <v>149</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>733</v>
+        <v>150</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>736</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>81</v>
       </c>
@@ -21437,25 +21515,25 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>732</v>
+        <v>152</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>737</v>
+        <v>153</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>738</v>
+        <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>81</v>
@@ -21475,21 +21553,21 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>739</v>
+        <v>668</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>739</v>
+        <v>509</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>81</v>
@@ -21501,15 +21579,17 @@
         <v>81</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -21546,31 +21626,31 @@
         <v>81</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>153</v>
@@ -21596,44 +21676,46 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>740</v>
+        <v>669</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>740</v>
+        <v>510</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>157</v>
+        <v>511</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>158</v>
+        <v>512</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O153" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -21645,7 +21727,7 @@
         <v>81</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>81</v>
@@ -21657,13 +21739,13 @@
         <v>81</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>81</v>
+        <v>516</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>81</v>
@@ -21681,22 +21763,22 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>153</v>
+        <v>368</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>81</v>
@@ -21705,7 +21787,7 @@
         <v>81</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>81</v>
@@ -21719,46 +21801,44 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>741</v>
+        <v>670</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>741</v>
+        <v>520</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>688</v>
+        <v>81</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>689</v>
+        <v>521</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>690</v>
+        <v>522</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -21770,7 +21850,7 @@
         <v>81</v>
       </c>
       <c r="T154" t="s" s="2">
-        <v>81</v>
+        <v>524</v>
       </c>
       <c r="U154" t="s" s="2">
         <v>81</v>
@@ -21782,13 +21862,13 @@
         <v>81</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>81</v>
@@ -21806,22 +21886,22 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>691</v>
+        <v>527</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>132</v>
+        <v>368</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>81</v>
@@ -21830,7 +21910,7 @@
         <v>81</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>81</v>
+        <v>528</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21844,10 +21924,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>742</v>
+        <v>671</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>742</v>
+        <v>529</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21855,34 +21935,34 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J155" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I155" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K155" t="s" s="2">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>743</v>
+        <v>530</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>744</v>
+        <v>531</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>745</v>
+        <v>532</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>746</v>
+        <v>374</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21895,7 +21975,7 @@
         <v>81</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>81</v>
@@ -21907,11 +21987,13 @@
         <v>81</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y155" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z155" t="s" s="2">
-        <v>747</v>
+        <v>81</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>81</v>
@@ -21929,10 +22011,10 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>742</v>
+        <v>534</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>89</v>
@@ -21944,22 +22026,22 @@
         <v>101</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>748</v>
+        <v>376</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>749</v>
+        <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>750</v>
+        <v>535</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>751</v>
+        <v>81</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>81</v>
@@ -21967,10 +22049,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>752</v>
+        <v>672</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>752</v>
+        <v>536</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21981,32 +22063,28 @@
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>341</v>
+        <v>149</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>753</v>
+        <v>537</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>756</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>81</v>
       </c>
@@ -22018,7 +22096,7 @@
         <v>81</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>81</v>
@@ -22054,13 +22132,13 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>752</v>
+        <v>540</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>81</v>
@@ -22069,16 +22147,16 @@
         <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>757</v>
+        <v>541</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>758</v>
+        <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>759</v>
+        <v>542</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>81</v>
@@ -22092,43 +22170,41 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>760</v>
+        <v>673</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>760</v>
+        <v>543</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>761</v>
+        <v>544</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>762</v>
+        <v>149</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>763</v>
+        <v>545</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>765</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -22141,7 +22217,7 @@
         <v>81</v>
       </c>
       <c r="T157" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="U157" t="s" s="2">
         <v>81</v>
@@ -22177,13 +22253,13 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>760</v>
+        <v>548</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>81</v>
@@ -22192,16 +22268,16 @@
         <v>101</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>766</v>
+        <v>549</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>767</v>
+        <v>550</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>81</v>
@@ -22215,14 +22291,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>768</v>
+        <v>674</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>768</v>
+        <v>551</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -22241,20 +22317,18 @@
         <v>90</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>333</v>
+        <v>149</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>769</v>
+        <v>553</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>770</v>
+        <v>554</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>772</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>81</v>
       </c>
@@ -22266,7 +22340,7 @@
         <v>81</v>
       </c>
       <c r="T158" t="s" s="2">
-        <v>81</v>
+        <v>556</v>
       </c>
       <c r="U158" t="s" s="2">
         <v>81</v>
@@ -22302,7 +22376,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>768</v>
+        <v>557</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -22317,16 +22391,16 @@
         <v>101</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>726</v>
+        <v>558</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>773</v>
+        <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>81</v>
@@ -22340,14 +22414,14 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>774</v>
+        <v>675</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>774</v>
+        <v>560</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22357,22 +22431,22 @@
         <v>89</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
         <v>149</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>150</v>
+        <v>562</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>151</v>
+        <v>563</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -22399,13 +22473,13 @@
         <v>81</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>81</v>
+        <v>565</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>81</v>
@@ -22423,7 +22497,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>152</v>
+        <v>566</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -22435,10 +22509,10 @@
         <v>81</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>153</v>
+        <v>567</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>81</v>
@@ -22447,7 +22521,7 @@
         <v>81</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>81</v>
@@ -22461,43 +22535,41 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>775</v>
+        <v>676</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>775</v>
+        <v>569</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>156</v>
+        <v>570</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>157</v>
+        <v>571</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>81</v>
@@ -22510,7 +22582,7 @@
         <v>81</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>81</v>
@@ -22534,34 +22606,34 @@
         <v>81</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC160" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="AD160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>161</v>
+        <v>574</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>153</v>
+        <v>575</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>81</v>
@@ -22570,7 +22642,7 @@
         <v>81</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>81</v>
+        <v>576</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>81</v>
@@ -22584,10 +22656,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>776</v>
+        <v>677</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>776</v>
+        <v>577</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22613,13 +22685,13 @@
         <v>149</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>777</v>
+        <v>578</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>778</v>
+        <v>579</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>779</v>
+        <v>580</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -22669,7 +22741,7 @@
         <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>780</v>
+        <v>581</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22678,13 +22750,13 @@
         <v>89</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>781</v>
+        <v>81</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>132</v>
+        <v>582</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>81</v>
@@ -22693,7 +22765,7 @@
         <v>81</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>81</v>
@@ -22707,10 +22779,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>782</v>
+        <v>678</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>782</v>
+        <v>584</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22724,7 +22796,7 @@
         <v>89</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>81</v>
@@ -22733,18 +22805,18 @@
         <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>103</v>
+        <v>326</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>783</v>
+        <v>585</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O162" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
       </c>
@@ -22756,7 +22828,7 @@
         <v>81</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>81</v>
@@ -22768,13 +22840,13 @@
         <v>81</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>786</v>
+        <v>81</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>787</v>
+        <v>81</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>81</v>
@@ -22792,7 +22864,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>788</v>
+        <v>589</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22807,7 +22879,7 @@
         <v>101</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>132</v>
+        <v>414</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>81</v>
@@ -22816,7 +22888,7 @@
         <v>81</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>81</v>
+        <v>590</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>81</v>
@@ -22830,10 +22902,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>789</v>
+        <v>679</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>789</v>
+        <v>679</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22853,21 +22925,21 @@
         <v>81</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>790</v>
+        <v>680</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N163" s="2"/>
+      <c r="O163" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
       </c>
@@ -22891,13 +22963,11 @@
         <v>81</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>81</v>
+        <v>683</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -22915,7 +22985,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>793</v>
+        <v>679</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22930,33 +23000,33 @@
         <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>794</v>
+        <v>684</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>81</v>
+        <v>685</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>81</v>
+        <v>686</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>81</v>
+        <v>687</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>81</v>
+        <v>688</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>795</v>
+        <v>689</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>795</v>
+        <v>689</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22976,21 +23046,23 @@
         <v>81</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>149</v>
+        <v>690</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>796</v>
+        <v>691</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>797</v>
+        <v>692</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
       </c>
@@ -23038,7 +23110,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>799</v>
+        <v>689</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -23050,25 +23122,25 @@
         <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>800</v>
+        <v>101</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>132</v>
+        <v>695</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>81</v>
+        <v>696</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>801</v>
+        <v>81</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>81</v>
@@ -23076,10 +23148,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>802</v>
+        <v>697</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>802</v>
+        <v>697</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23096,25 +23168,25 @@
         <v>81</v>
       </c>
       <c r="I165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>803</v>
+        <v>699</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>804</v>
+        <v>700</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>805</v>
+        <v>701</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>806</v>
+        <v>702</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -23163,7 +23235,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>802</v>
+        <v>697</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -23178,7 +23250,7 @@
         <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>807</v>
+        <v>703</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>153</v>
@@ -23187,7 +23259,7 @@
         <v>81</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>81</v>
+        <v>704</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -23201,10 +23273,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>808</v>
+        <v>705</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>808</v>
+        <v>705</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23215,7 +23287,7 @@
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>81</v>
@@ -23227,16 +23299,20 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>149</v>
+        <v>706</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>150</v>
+        <v>707</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>710</v>
+      </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
       </c>
@@ -23284,25 +23360,25 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>152</v>
+        <v>705</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>81</v>
+        <v>711</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AL166" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>81</v>
@@ -23322,21 +23398,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>809</v>
+        <v>713</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>809</v>
+        <v>713</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>81</v>
@@ -23348,17 +23424,15 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>81</v>
@@ -23407,19 +23481,19 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>153</v>
@@ -23445,14 +23519,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>810</v>
+        <v>714</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>810</v>
+        <v>714</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>688</v>
+        <v>156</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -23465,26 +23539,24 @@
         <v>81</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>689</v>
+        <v>157</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>690</v>
+        <v>158</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O168" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>81</v>
       </c>
@@ -23532,7 +23604,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>691</v>
+        <v>161</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -23547,7 +23619,7 @@
         <v>140</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>81</v>
@@ -23570,44 +23642,46 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>811</v>
+        <v>715</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>811</v>
+        <v>715</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>81</v>
+        <v>716</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J169" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>812</v>
+        <v>134</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>813</v>
+        <v>717</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>814</v>
+        <v>718</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="O169" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
       </c>
@@ -23655,31 +23729,31 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>811</v>
+        <v>719</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>281</v>
+        <v>132</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>816</v>
+        <v>81</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -23693,10 +23767,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23704,10 +23778,10 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>81</v>
@@ -23716,19 +23790,21 @@
         <v>81</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>818</v>
+        <v>721</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>819</v>
+        <v>722</v>
       </c>
       <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
+      <c r="O170" t="s" s="2">
+        <v>723</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -23752,13 +23828,13 @@
         <v>81</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>182</v>
+        <v>301</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>819</v>
+        <v>724</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>820</v>
+        <v>725</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -23776,13 +23852,13 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>817</v>
+        <v>720</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>81</v>
@@ -23791,7 +23867,7 @@
         <v>101</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>821</v>
+        <v>726</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>153</v>
@@ -23800,7 +23876,7 @@
         <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>81</v>
+        <v>727</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>81</v>
@@ -23809,11 +23885,3213 @@
         <v>81</v>
       </c>
       <c r="AQ170" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N171" s="2"/>
+      <c r="O171" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ171" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ172" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="N173" s="2"/>
+      <c r="O173" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ173" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N174" s="2"/>
+      <c r="O174" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ174" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="175" hidden="true">
+      <c r="A175" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="P175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ175" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="176" hidden="true">
+      <c r="A176" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ176" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="177" hidden="true">
+      <c r="A177" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="P177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AL177" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ177" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
+      <c r="P178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ178" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="179" hidden="true">
+      <c r="A179" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O179" s="2"/>
+      <c r="P179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q179" s="2"/>
+      <c r="R179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ179" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="180" hidden="true">
+      <c r="A180" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q180" s="2"/>
+      <c r="R180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP180" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ180" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="181" hidden="true">
+      <c r="A181" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="P181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q181" s="2"/>
+      <c r="R181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y181" s="2"/>
+      <c r="Z181" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AL181" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AM181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN181" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AO181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP181" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AQ181" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="182" hidden="true">
+      <c r="A182" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C182" s="2"/>
+      <c r="D182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G182" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="P182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q182" s="2"/>
+      <c r="R182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="AL182" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AM182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN182" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AO182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP182" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ182" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="183" hidden="true">
+      <c r="A183" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="O183" s="2"/>
+      <c r="P183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q183" s="2"/>
+      <c r="R183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK183" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AL183" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN183" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AO183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ183" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="184" hidden="true">
+      <c r="A184" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="P184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q184" s="2"/>
+      <c r="R184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK184" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AL184" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP184" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ184" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="185" hidden="true">
+      <c r="A185" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G185" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N185" s="2"/>
+      <c r="O185" s="2"/>
+      <c r="P185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q185" s="2"/>
+      <c r="R185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK185" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP185" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ185" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="186" hidden="true">
+      <c r="A186" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O186" s="2"/>
+      <c r="P186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK186" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ186" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="O187" s="2"/>
+      <c r="P187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ187" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="188" hidden="true">
+      <c r="A188" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L188" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="O188" s="2"/>
+      <c r="P188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q188" s="2"/>
+      <c r="R188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK188" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ188" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="189" hidden="true">
+      <c r="A189" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="O189" s="2"/>
+      <c r="P189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK189" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AL189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ189" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="190" hidden="true">
+      <c r="A190" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="O190" s="2"/>
+      <c r="P190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="AK190" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP190" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AQ190" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="191" hidden="true">
+      <c r="A191" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="P191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK191" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="AL191" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ191" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="192" hidden="true">
+      <c r="A192" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N192" s="2"/>
+      <c r="O192" s="2"/>
+      <c r="P192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK192" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP192" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ192" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="193" hidden="true">
+      <c r="A193" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O193" s="2"/>
+      <c r="P193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK193" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP193" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ193" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ194" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="195" hidden="true">
+      <c r="A195" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="O195" s="2"/>
+      <c r="P195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q195" s="2"/>
+      <c r="R195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK195" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL195" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN195" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="AO195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ195" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="196" hidden="true">
+      <c r="A196" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="C196" s="2"/>
+      <c r="D196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E196" s="2"/>
+      <c r="F196" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G196" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J196" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K196" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L196" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="M196" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
+      <c r="P196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q196" s="2"/>
+      <c r="R196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X196" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y196" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="Z196" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="AA196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF196" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AG196" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH196" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ196" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK196" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="AL196" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP196" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ196" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ170">
+  <autoFilter ref="A1:AQ196">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -23823,7 +27101,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI169">
+  <conditionalFormatting sqref="A2:AI195">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA PATIENT (file 2) to FHIR Patient</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (#2) to us-core-patient</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$157</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7855" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6296" uniqueCount="809">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2008,132 +2008,6 @@
     <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (#2-.1218)</t>
   </si>
   <si>
-    <t>Patient.address:temp</t>
-  </si>
-  <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.id</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.extension</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.use</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.type</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.text</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.line</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.city</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.district</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.state</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.postalCode</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.country</t>
-  </si>
-  <si>
-    <t>Patient.address:temp.period</t>
-  </si>
-  <si>
-    <t>Patient.address:physical</t>
-  </si>
-  <si>
-    <t>physical</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.id</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.extension</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.use</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.type</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.text</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.line</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.city</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.district</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.state</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.postalCode</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.country</t>
-  </si>
-  <si>
-    <t>Patient.address:physical.period</t>
-  </si>
-  <si>
-    <t>Patient.address:postal</t>
-  </si>
-  <si>
-    <t>postal</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.id</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.extension</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.use</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.type</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.text</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.line</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.city</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.district</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.state</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.postalCode</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.country</t>
-  </si>
-  <si>
-    <t>Patient.address:postal.period</t>
-  </si>
-  <si>
     <t>Patient.maritalStatus</t>
   </si>
   <si>
@@ -2599,10 +2473,6 @@
   </si>
   <si>
     <t>Reference.display</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-27:296: fixed value = Veterans Health Administration {null}</t>
   </si>
   <si>
     <t>296: fixed value = Veterans Health Administration</t>
@@ -2985,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR196"/>
+  <dimension ref="A1:AR157"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.8515625" customWidth="true" bestFit="true"/>
@@ -6054,14 +5924,14 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -6076,14 +5946,12 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -6147,7 +6015,7 @@
         <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
@@ -6316,7 +6184,7 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -8554,14 +8422,14 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -8576,14 +8444,12 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -8647,7 +8513,7 @@
         <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -8816,7 +8682,7 @@
         <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -9692,7 +9558,7 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -10440,7 +10306,7 @@
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -12462,7 +12328,7 @@
         <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -14604,7 +14470,7 @@
         <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>91</v>
@@ -17748,7 +17614,7 @@
         <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
@@ -18250,7 +18116,7 @@
         <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>82</v>
@@ -18376,7 +18242,7 @@
         <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>82</v>
@@ -18490,11 +18356,9 @@
         <v>639</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>640</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>82</v>
       </c>
@@ -18512,22 +18376,20 @@
         <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>501</v>
+        <v>267</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>502</v>
+        <v>640</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>505</v>
+        <v>642</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -18552,13 +18414,11 @@
         <v>82</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>82</v>
@@ -18576,13 +18436,13 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>500</v>
+        <v>639</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
@@ -18591,25 +18451,25 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>507</v>
+        <v>644</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>508</v>
+        <v>645</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>509</v>
+        <v>646</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>82</v>
@@ -18617,10 +18477,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>510</v>
+        <v>649</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18643,16 +18503,20 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>151</v>
+        <v>651</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>652</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -18700,7 +18564,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>153</v>
+        <v>649</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -18712,19 +18576,19 @@
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL125" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -18741,14 +18605,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>511</v>
+        <v>657</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -18767,18 +18631,20 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>135</v>
+        <v>658</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>158</v>
+        <v>659</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>159</v>
+        <v>660</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -18814,19 +18680,19 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>162</v>
+        <v>657</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18838,19 +18704,19 @@
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL126" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>82</v>
+        <v>664</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -18867,10 +18733,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>512</v>
+        <v>665</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18881,31 +18747,31 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>110</v>
+        <v>666</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>513</v>
+        <v>667</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>514</v>
+        <v>668</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>515</v>
+        <v>669</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>516</v>
+        <v>670</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -18918,7 +18784,7 @@
         <v>82</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>82</v>
@@ -18930,13 +18796,13 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -18954,31 +18820,31 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>520</v>
+        <v>665</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>671</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>370</v>
+        <v>672</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -18995,10 +18861,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>522</v>
+        <v>673</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19018,20 +18884,18 @@
         <v>82</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>523</v>
+        <v>151</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -19044,7 +18908,7 @@
         <v>82</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>82</v>
@@ -19056,13 +18920,13 @@
         <v>82</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -19080,7 +18944,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>529</v>
+        <v>153</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19092,10 +18956,10 @@
         <v>82</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>370</v>
+        <v>154</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -19104,7 +18968,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19121,21 +18985,21 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>531</v>
+        <v>674</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>82</v>
@@ -19144,23 +19008,21 @@
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>532</v>
+        <v>158</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>533</v>
+        <v>159</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -19172,7 +19034,7 @@
         <v>82</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>82</v>
@@ -19208,22 +19070,22 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>536</v>
+        <v>162</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>378</v>
+        <v>154</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -19232,7 +19094,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -19249,14 +19111,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>538</v>
+        <v>675</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19266,25 +19128,29 @@
         <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I130" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>539</v>
+        <v>677</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -19296,7 +19162,7 @@
         <v>82</v>
       </c>
       <c r="T130" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="U130" t="s" s="2">
         <v>82</v>
@@ -19332,7 +19198,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>542</v>
+        <v>679</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19344,10 +19210,10 @@
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>543</v>
+        <v>133</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>82</v>
@@ -19356,7 +19222,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19373,42 +19239,44 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>647</v>
+        <v>680</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>545</v>
+        <v>680</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>547</v>
+        <v>681</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>548</v>
+        <v>682</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -19420,7 +19288,7 @@
         <v>82</v>
       </c>
       <c r="T131" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="U131" t="s" s="2">
         <v>82</v>
@@ -19432,13 +19300,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>82</v>
+        <v>684</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>82</v>
+        <v>685</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -19456,13 +19324,13 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>550</v>
+        <v>680</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
@@ -19471,16 +19339,16 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>551</v>
+        <v>686</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>552</v>
+        <v>687</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -19497,14 +19365,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>553</v>
+        <v>688</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -19520,21 +19388,21 @@
         <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>150</v>
+        <v>352</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>555</v>
+        <v>689</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -19546,7 +19414,7 @@
         <v>82</v>
       </c>
       <c r="T132" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="U132" t="s" s="2">
         <v>82</v>
@@ -19582,7 +19450,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>559</v>
+        <v>688</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19597,16 +19465,16 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>560</v>
+        <v>357</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>561</v>
+        <v>692</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -19623,42 +19491,46 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>562</v>
+        <v>693</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>150</v>
+        <v>419</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>564</v>
+        <v>694</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -19682,13 +19554,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -19706,13 +19578,13 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>568</v>
+        <v>693</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
@@ -19721,16 +19593,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>569</v>
+        <v>424</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>570</v>
+        <v>697</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -19747,14 +19619,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>650</v>
+        <v>698</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>571</v>
+        <v>698</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -19764,25 +19636,27 @@
         <v>90</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>150</v>
+        <v>501</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>573</v>
+        <v>699</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>574</v>
+        <v>700</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
+      <c r="O134" t="s" s="2">
+        <v>701</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -19794,7 +19668,7 @@
         <v>82</v>
       </c>
       <c r="T134" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="U134" t="s" s="2">
         <v>82</v>
@@ -19830,7 +19704,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>576</v>
+        <v>698</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19845,16 +19719,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>577</v>
+        <v>507</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>578</v>
+        <v>702</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -19871,10 +19745,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>651</v>
+        <v>703</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>579</v>
+        <v>703</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19894,21 +19768,21 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>580</v>
+        <v>466</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>704</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -19932,13 +19806,13 @@
         <v>82</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>82</v>
+        <v>706</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>82</v>
+        <v>707</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>82</v>
@@ -19956,7 +19830,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>583</v>
+        <v>703</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19971,16 +19845,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>584</v>
+        <v>245</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>585</v>
+        <v>708</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -19997,10 +19871,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>652</v>
+        <v>709</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>586</v>
+        <v>709</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20014,26 +19888,26 @@
         <v>90</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>587</v>
+        <v>710</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>588</v>
+        <v>711</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>589</v>
+        <v>712</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -20046,7 +19920,7 @@
         <v>82</v>
       </c>
       <c r="T136" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="U136" t="s" s="2">
         <v>82</v>
@@ -20082,7 +19956,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>591</v>
+        <v>709</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20091,22 +19965,22 @@
         <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>82</v>
+        <v>713</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>416</v>
+        <v>714</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>592</v>
+        <v>715</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20123,14 +19997,12 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>654</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>82</v>
       </c>
@@ -20142,29 +20014,25 @@
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>501</v>
+        <v>328</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>502</v>
+        <v>717</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -20212,13 +20080,13 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>500</v>
+        <v>716</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>82</v>
@@ -20227,16 +20095,16 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>507</v>
+        <v>719</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>508</v>
+        <v>154</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -20253,10 +20121,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>655</v>
+        <v>720</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20267,7 +20135,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
@@ -20279,16 +20147,20 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>150</v>
+        <v>666</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>151</v>
+        <v>721</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>724</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -20336,25 +20208,25 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>153</v>
+        <v>720</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>154</v>
+        <v>725</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>82</v>
+        <v>726</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
@@ -20377,21 +20249,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>656</v>
+        <v>727</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>511</v>
+        <v>727</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
@@ -20403,17 +20275,15 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20450,31 +20320,31 @@
         <v>82</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>154</v>
@@ -20503,46 +20373,44 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>657</v>
+        <v>728</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>512</v>
+        <v>728</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>513</v>
+        <v>158</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>514</v>
+        <v>159</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>82</v>
       </c>
@@ -20554,7 +20422,7 @@
         <v>82</v>
       </c>
       <c r="T140" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="U140" t="s" s="2">
         <v>82</v>
@@ -20566,13 +20434,13 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -20590,22 +20458,22 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>520</v>
+        <v>162</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>370</v>
+        <v>154</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -20614,7 +20482,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -20631,44 +20499,46 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>658</v>
+        <v>729</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>522</v>
+        <v>729</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J141" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>523</v>
+        <v>677</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>524</v>
+        <v>678</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -20680,7 +20550,7 @@
         <v>82</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>82</v>
@@ -20692,13 +20562,13 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -20716,22 +20586,22 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>529</v>
+        <v>679</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>370</v>
+        <v>133</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -20740,7 +20610,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -20757,10 +20627,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>659</v>
+        <v>730</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>531</v>
+        <v>730</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20768,34 +20638,34 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>532</v>
+        <v>731</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>533</v>
+        <v>732</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>534</v>
+        <v>733</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>376</v>
+        <v>734</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -20808,7 +20678,7 @@
         <v>82</v>
       </c>
       <c r="T142" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="U142" t="s" s="2">
         <v>82</v>
@@ -20820,13 +20690,11 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>82</v>
+        <v>735</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -20844,10 +20712,10 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>536</v>
+        <v>730</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>90</v>
@@ -20859,22 +20727,22 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>378</v>
+        <v>736</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>82</v>
+        <v>737</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>537</v>
+        <v>738</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>82</v>
+        <v>739</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>82</v>
@@ -20885,10 +20753,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>538</v>
+        <v>740</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20899,28 +20767,32 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>539</v>
+        <v>741</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>744</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -20932,7 +20804,7 @@
         <v>82</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>82</v>
@@ -20968,13 +20840,13 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>542</v>
+        <v>740</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>82</v>
@@ -20983,16 +20855,16 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>543</v>
+        <v>745</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>82</v>
+        <v>746</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>544</v>
+        <v>747</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -21009,41 +20881,43 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>661</v>
+        <v>748</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>545</v>
+        <v>748</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>546</v>
+        <v>749</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>547</v>
+        <v>751</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>752</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>753</v>
+      </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -21056,7 +20930,7 @@
         <v>82</v>
       </c>
       <c r="T144" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="U144" t="s" s="2">
         <v>82</v>
@@ -21092,13 +20966,13 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>550</v>
+        <v>748</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>82</v>
@@ -21107,16 +20981,16 @@
         <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>551</v>
+        <v>754</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>552</v>
+        <v>755</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -21133,14 +21007,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>662</v>
+        <v>756</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>553</v>
+        <v>756</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -21159,18 +21033,20 @@
         <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>150</v>
+        <v>335</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>555</v>
+        <v>757</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>556</v>
+        <v>758</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>759</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>760</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
       </c>
@@ -21182,7 +21058,7 @@
         <v>82</v>
       </c>
       <c r="T145" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="U145" t="s" s="2">
         <v>82</v>
@@ -21218,7 +21094,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>559</v>
+        <v>756</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -21233,16 +21109,16 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>560</v>
+        <v>714</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>82</v>
+        <v>761</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -21259,14 +21135,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>663</v>
+        <v>762</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>562</v>
+        <v>762</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -21276,22 +21152,22 @@
         <v>90</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>564</v>
+        <v>151</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>565</v>
+        <v>152</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -21318,13 +21194,13 @@
         <v>82</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -21342,7 +21218,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>568</v>
+        <v>153</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21354,10 +21230,10 @@
         <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>569</v>
+        <v>154</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -21366,7 +21242,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -21383,41 +21259,43 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>664</v>
+        <v>763</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>571</v>
+        <v>763</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>572</v>
+        <v>157</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>573</v>
+        <v>158</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N147" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -21430,7 +21308,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21454,34 +21332,34 @@
         <v>82</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>576</v>
+        <v>162</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>577</v>
+        <v>154</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -21490,7 +21368,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -21507,10 +21385,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>665</v>
+        <v>764</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>579</v>
+        <v>764</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21536,13 +21414,13 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>580</v>
+        <v>765</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>581</v>
+        <v>766</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>582</v>
+        <v>767</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -21592,7 +21470,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>583</v>
+        <v>768</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21601,13 +21479,13 @@
         <v>90</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>82</v>
+        <v>769</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>584</v>
+        <v>133</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>82</v>
@@ -21616,7 +21494,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -21633,10 +21511,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>666</v>
+        <v>770</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>586</v>
+        <v>770</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21650,7 +21528,7 @@
         <v>90</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>82</v>
@@ -21659,18 +21537,18 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>587</v>
+        <v>771</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>772</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
       </c>
@@ -21682,7 +21560,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -21694,13 +21572,13 @@
         <v>82</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>82</v>
+        <v>774</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>82</v>
+        <v>775</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -21718,7 +21596,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>591</v>
+        <v>776</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21733,7 +21611,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>416</v>
+        <v>133</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>82</v>
@@ -21742,7 +21620,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -21759,14 +21637,12 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>667</v>
+        <v>777</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>82</v>
       </c>
@@ -21778,7 +21654,7 @@
         <v>90</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>82</v>
@@ -21787,20 +21663,18 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>501</v>
+        <v>278</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>502</v>
+        <v>778</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>503</v>
+        <v>779</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>82</v>
       </c>
@@ -21848,13 +21722,13 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>500</v>
+        <v>781</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>82</v>
@@ -21863,16 +21737,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>507</v>
+        <v>782</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -21889,10 +21763,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>783</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>510</v>
+        <v>783</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21906,24 +21780,26 @@
         <v>90</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>151</v>
+        <v>784</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>785</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>786</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -21972,7 +21848,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>153</v>
+        <v>787</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21984,10 +21860,10 @@
         <v>82</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>82</v>
@@ -22002,7 +21878,7 @@
         <v>82</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>82</v>
+        <v>788</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>82</v>
@@ -22013,14 +21889,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>670</v>
+        <v>789</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>511</v>
+        <v>789</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22033,24 +21909,26 @@
         <v>82</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>135</v>
+        <v>666</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>158</v>
+        <v>790</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>159</v>
+        <v>791</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O152" s="2"/>
+        <v>792</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>793</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
       </c>
@@ -22086,19 +21964,19 @@
         <v>82</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>162</v>
+        <v>789</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22110,13 +21988,13 @@
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
@@ -22139,10 +22017,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>671</v>
+        <v>795</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>512</v>
+        <v>795</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22159,26 +22037,22 @@
         <v>82</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>513</v>
+        <v>151</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -22190,7 +22064,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22202,13 +22076,13 @@
         <v>82</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -22226,7 +22100,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>520</v>
+        <v>153</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22238,10 +22112,10 @@
         <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>370</v>
+        <v>154</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>82</v>
@@ -22250,7 +22124,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22267,21 +22141,21 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>672</v>
+        <v>796</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>522</v>
+        <v>796</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>82</v>
@@ -22290,19 +22164,19 @@
         <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>523</v>
+        <v>158</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>524</v>
+        <v>159</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>525</v>
+        <v>160</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22316,7 +22190,7 @@
         <v>82</v>
       </c>
       <c r="T154" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="U154" t="s" s="2">
         <v>82</v>
@@ -22328,13 +22202,13 @@
         <v>82</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -22352,22 +22226,22 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>529</v>
+        <v>162</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>370</v>
+        <v>154</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>82</v>
@@ -22376,7 +22250,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22393,45 +22267,45 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>673</v>
+        <v>797</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>531</v>
+        <v>797</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J155" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>532</v>
+        <v>677</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>533</v>
+        <v>678</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>534</v>
+        <v>160</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22444,7 +22318,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22480,22 +22354,22 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>536</v>
+        <v>679</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>378</v>
+        <v>133</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>82</v>
@@ -22504,7 +22378,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22521,10 +22395,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>674</v>
+        <v>798</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>538</v>
+        <v>798</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22532,13 +22406,13 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>82</v>
@@ -22547,15 +22421,17 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>150</v>
+        <v>799</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>539</v>
+        <v>800</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>802</v>
+      </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22568,7 +22444,7 @@
         <v>82</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>82</v>
@@ -22604,13 +22480,13 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>542</v>
+        <v>798</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>82</v>
@@ -22619,16 +22495,16 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>543</v>
+        <v>282</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>544</v>
+        <v>803</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -22645,24 +22521,24 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>675</v>
+        <v>804</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>545</v>
+        <v>804</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>82</v>
@@ -22671,13 +22547,13 @@
         <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>547</v>
+        <v>805</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>548</v>
+        <v>806</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -22692,7 +22568,7 @@
         <v>82</v>
       </c>
       <c r="T157" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="U157" t="s" s="2">
         <v>82</v>
@@ -22704,13 +22580,13 @@
         <v>82</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>82</v>
+        <v>806</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>82</v>
+        <v>807</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>82</v>
@@ -22728,10 +22604,10 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>550</v>
+        <v>804</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>90</v>
@@ -22743,16 +22619,16 @@
         <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>551</v>
+        <v>808</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -22764,4929 +22640,11 @@
         <v>82</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O158" s="2"/>
-      <c r="P158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR158" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
-      <c r="P159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR159" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
-      <c r="P160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR160" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O161" s="2"/>
-      <c r="P161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR161" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR162" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="163" hidden="true">
-      <c r="A163" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G163" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K163" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L163" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="P163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q163" s="2"/>
-      <c r="R163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X163" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y163" s="2"/>
-      <c r="Z163" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AG163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK163" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP163" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AQ163" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AR163" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="164" hidden="true">
-      <c r="A164" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C164" s="2"/>
-      <c r="D164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E164" s="2"/>
-      <c r="F164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G164" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K164" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="L164" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q164" s="2"/>
-      <c r="R164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ164" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK164" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR164" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="165" hidden="true">
-      <c r="A165" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C165" s="2"/>
-      <c r="D165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E165" s="2"/>
-      <c r="F165" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K165" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="P165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q165" s="2"/>
-      <c r="R165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AG165" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK165" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="AL165" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR165" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="166" hidden="true">
-      <c r="A166" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C166" s="2"/>
-      <c r="D166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E166" s="2"/>
-      <c r="F166" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K166" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="P166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q166" s="2"/>
-      <c r="R166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="AK166" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR166" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="167" hidden="true">
-      <c r="A167" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C167" s="2"/>
-      <c r="D167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E167" s="2"/>
-      <c r="F167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G167" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K167" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" s="2"/>
-      <c r="P167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q167" s="2"/>
-      <c r="R167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK167" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR167" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="168" hidden="true">
-      <c r="A168" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K168" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O168" s="2"/>
-      <c r="P168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q168" s="2"/>
-      <c r="R168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR168" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="169" hidden="true">
-      <c r="A169" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C169" s="2"/>
-      <c r="D169" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="E169" s="2"/>
-      <c r="F169" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K169" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="P169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q169" s="2"/>
-      <c r="R169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR169" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="170" hidden="true">
-      <c r="A170" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E170" s="2"/>
-      <c r="F170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N170" s="2"/>
-      <c r="O170" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="P170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q170" s="2"/>
-      <c r="R170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK170" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR170" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="171" hidden="true">
-      <c r="A171" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E171" s="2"/>
-      <c r="F171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G171" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K171" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N171" s="2"/>
-      <c r="O171" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q171" s="2"/>
-      <c r="R171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK171" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AL171" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR171" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="172" hidden="true">
-      <c r="A172" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="C172" s="2"/>
-      <c r="D172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E172" s="2"/>
-      <c r="F172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K172" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q172" s="2"/>
-      <c r="R172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ172" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK172" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR172" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="173" hidden="true">
-      <c r="A173" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C173" s="2"/>
-      <c r="D173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E173" s="2"/>
-      <c r="F173" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G173" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K173" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="L173" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="P173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q173" s="2"/>
-      <c r="R173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AG173" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK173" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR173" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="174" hidden="true">
-      <c r="A174" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C174" s="2"/>
-      <c r="D174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E174" s="2"/>
-      <c r="F174" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G174" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K174" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L174" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="P174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q174" s="2"/>
-      <c r="R174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X174" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="Z174" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AA174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF174" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH174" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ174" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK174" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AL174" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR174" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="175" hidden="true">
-      <c r="A175" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="N175" s="2"/>
-      <c r="O175" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="P175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK175" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="AL175" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR175" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="176" hidden="true">
-      <c r="A176" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
-      <c r="P176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK176" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="AL176" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR176" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="177" hidden="true">
-      <c r="A177" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="P177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK177" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="AL177" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR177" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="178" hidden="true">
-      <c r="A178" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
-      <c r="P178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK178" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR178" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O179" s="2"/>
-      <c r="P179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR179" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="180" hidden="true">
-      <c r="A180" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="P180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK180" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR180" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="181" hidden="true">
-      <c r="A181" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="P181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y181" s="2"/>
-      <c r="Z181" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK181" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="AL181" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="AO181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP181" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="AQ181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR181" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="182" hidden="true">
-      <c r="A182" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="P182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AM182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AO182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ182" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR182" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="183" hidden="true">
-      <c r="A183" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="O183" s="2"/>
-      <c r="P183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK183" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="AO183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR183" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="P184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK184" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="AL184" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ184" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR184" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N185" s="2"/>
-      <c r="O185" s="2"/>
-      <c r="P185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK185" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR185" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O186" s="2"/>
-      <c r="P186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR186" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="O187" s="2"/>
-      <c r="P187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR187" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="O188" s="2"/>
-      <c r="P188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR188" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR189" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP190" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AQ190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR190" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR191" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
-      <c r="P192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR192" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O193" s="2"/>
-      <c r="P193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR193" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="194" hidden="true">
-      <c r="A194" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR194" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR195" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="196" hidden="true">
-      <c r="A196" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N196" s="2"/>
-      <c r="O196" s="2"/>
-      <c r="P196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR196" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR196">
+  <autoFilter ref="A1:AR157">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27696,7 +22654,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI195">
+  <conditionalFormatting sqref="A2:AI156">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="866">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2638,6 +2638,9 @@
   </si>
   <si>
     <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Veterans Health Administration</t>
   </si>
   <si>
     <t>Reference.display</t>
@@ -23741,7 +23744,7 @@
         <v>82</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>82</v>
+        <v>843</v>
       </c>
       <c r="T165" t="s" s="2">
         <v>82</v>
@@ -23780,7 +23783,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -23810,7 +23813,7 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>82</v>
@@ -23821,10 +23824,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23850,16 +23853,16 @@
         <v>722</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -23908,7 +23911,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23923,7 +23926,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>154</v>
@@ -23949,10 +23952,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24073,10 +24076,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24199,10 +24202,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24327,10 +24330,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24353,16 +24356,16 @@
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24412,7 +24415,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>90</v>
@@ -24436,7 +24439,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -24453,10 +24456,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24482,10 +24485,10 @@
         <v>110</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24515,10 +24518,10 @@
         <v>181</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -24536,7 +24539,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>90</v>
@@ -24551,7 +24554,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -977,8 +977,7 @@
     <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (#2-.02)</t>
   </si>
   <si>
-    <t>Patient.Patient.Gender
-SPatient.SPatient.Gender</t>
+    <t>Patient.Patient.Gender,SPatient.SPatient.Gender</t>
   </si>
   <si>
     <t>Patient.extension:genderIdentity</t>
@@ -1035,10 +1034,7 @@
     <t>1598: terminologyMaps using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (#2-.08)</t>
   </si>
   <si>
-    <t>Outpat.Visit.PatientReligion
-Outpat.Visit.PatientReligionCode
-Outpat.Workload.PatientReligion
-Outpat.Workload.PatientReligionCode</t>
+    <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1202,10 +1198,7 @@
     <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
   </si>
   <si>
-    <t>Patient.Patient.PatientICN
-Patient.PatientICN.PatientICN
-SPatient.SPatient.PatientICN
-SPatient.SPatientGISAddress.PatientICN</t>
+    <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.mechanism</t>
@@ -1376,10 +1369,7 @@
     <t>273: source value from PATIENT - NAME (#2-.01)</t>
   </si>
   <si>
-    <t>SPatient.SPatient.PatientFirstName
-SPatient.SPatient.PatientLastName
-SPatient.SPatient.PatientName
-SPatient.SPatientAlias.PatientName</t>
+    <t>SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
   </si>
   <si>
     <t>Patient.name.family</t>
@@ -1661,8 +1651,7 @@
     <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
   </si>
   <si>
-    <t>Patient.Patient.SelfIdentifiedGender
-SPatient.SPatient.SelfIdentifiedGender</t>
+    <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
   </si>
   <si>
     <t>Patient.birthDate</t>
@@ -1699,8 +1688,7 @@
     <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
   </si>
   <si>
-    <t>SPatient.PlaceOfBirth.BirthDateTime
-SPatient.SPatient.BirthDateTime</t>
+    <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
     <t>Patient.deceased[x]</t>
@@ -1745,8 +1733,7 @@
     <t>285: source value from PATIENT - DATE OF DEATH (#2-.351) case not null</t>
   </si>
   <si>
-    <t>Patient.Patient.DeathDateTime
-SPatient.SPatient.DeathDateTime</t>
+    <t>Patient.Patient.DeathDateTime,SPatient.SPatient.DeathDateTime</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2203,8 +2190,7 @@
     <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
   </si>
   <si>
-    <t>Outpat.Visit.PatientMaritalStatus
-Outpat.Workload.PatientMaritalStatus</t>
+    <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -3070,7 +3056,7 @@
     <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="117.13671875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="128.15234375" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,15 +253,6 @@
   </si>
   <si>
     <t>Mapping: LOINC code for the element</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t xml:space="preserve">SubjectOfCare Client Resident
@@ -682,13 +682,13 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (#2-2)</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (#2-2)</t>
   </si>
   <si>
     <t>Patient.extension:race.extension:ombCategory.value[x].display</t>
@@ -1189,19 +1189,19 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
+  </si>
+  <si>
+    <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.mechanism</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
-  </si>
-  <si>
-    <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.mechanism</t>
   </si>
   <si>
     <t>Patient.identifier.period</t>
@@ -1360,16 +1360,16 @@
     <t>HumanName.text</t>
   </si>
   <si>
+    <t>273: source value from PATIENT - NAME (#2-.01)</t>
+  </si>
+  <si>
+    <t>SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
+  </si>
+  <si>
     <t>./formatted</t>
   </si>
   <si>
     <t>implied by XPN.11</t>
-  </si>
-  <si>
-    <t>273: source value from PATIENT - NAME (#2-.01)</t>
-  </si>
-  <si>
-    <t>SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
   </si>
   <si>
     <t>Patient.name.family</t>
@@ -1563,13 +1563,13 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
+    <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (#2-.134)</t>
+  </si>
+  <si>
     <t>./url</t>
   </si>
   <si>
     <t>XTN.1 (or XTN.12)</t>
-  </si>
-  <si>
-    <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (#2-.134)</t>
   </si>
   <si>
     <t>Patient.telecom.use</t>
@@ -1642,16 +1642,16 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
+    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
+  </si>
+  <si>
+    <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
+  </si>
+  <si>
     <t>.patient.administrativeGenderCode</t>
   </si>
   <si>
     <t>PID-8</t>
-  </si>
-  <si>
-    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
-  </si>
-  <si>
-    <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
   </si>
   <si>
     <t>Patient.birthDate</t>
@@ -1673,6 +1673,12 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
+    <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
+  </si>
+  <si>
+    <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
+  </si>
+  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
   </si>
   <si>
@@ -1683,12 +1689,6 @@
   </si>
   <si>
     <t>21112-8</t>
-  </si>
-  <si>
-    <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
-  </si>
-  <si>
-    <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
     <t>Patient.deceased[x]</t>
@@ -2124,15 +2124,15 @@
 </t>
   </si>
   <si>
+    <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (#2-.1217)</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (#2-.1217)</t>
-  </si>
-  <si>
     <t>Patient.address:home.period.end</t>
   </si>
   <si>
@@ -2154,15 +2154,15 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (#2-.1218)</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
   </si>
   <si>
-    <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (#2-.1218)</t>
-  </si>
-  <si>
     <t>Patient.maritalStatus</t>
   </si>
   <si>
@@ -2178,6 +2178,12 @@
     <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus</t>
   </si>
   <si>
+    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
+  </si>
+  <si>
+    <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus</t>
+  </si>
+  <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
   </si>
   <si>
@@ -2185,12 +2191,6 @@
   </si>
   <si>
     <t>PID-16</t>
-  </si>
-  <si>
-    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
-  </si>
-  <si>
-    <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -2464,6 +2464,9 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/simple-language</t>
   </si>
   <si>
+    <t>295: source value from PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (#2-7 &gt; 2.07-.02)</t>
+  </si>
+  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
   </si>
   <si>
@@ -2471,9 +2474,6 @@
   </si>
   <si>
     <t>PID-15, LAN-2</t>
-  </si>
-  <si>
-    <t>295: source value from PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (#2-7 &gt; 2.07-.02)</t>
   </si>
   <si>
     <t>Patient.communication.preferred</t>
@@ -3050,14 +3050,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="156.828125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.8125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="117.13671875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="128.15234375" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="117.13671875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="128.15234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="40.8125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="107.3984375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="40.0703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3296,19 +3296,19 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -3924,16 +3924,16 @@
         <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -4050,16 +4050,16 @@
         <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -4422,16 +4422,16 @@
         <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>82</v>
@@ -4548,16 +4548,16 @@
         <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -4798,16 +4798,16 @@
         <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -5048,16 +5048,16 @@
         <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -5172,16 +5172,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -5296,16 +5296,16 @@
         <v>82</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -5422,16 +5422,16 @@
         <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -5550,25 +5550,25 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
@@ -5676,25 +5676,25 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>82</v>
@@ -5815,10 +5815,10 @@
         <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>82</v>
@@ -5926,25 +5926,25 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>82</v>
@@ -6054,25 +6054,25 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>82</v>
@@ -6304,16 +6304,16 @@
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -6430,16 +6430,16 @@
         <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -6556,16 +6556,16 @@
         <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -6678,16 +6678,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6928,16 +6928,16 @@
         <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -7054,16 +7054,16 @@
         <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -7180,16 +7180,16 @@
         <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -7304,16 +7304,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -7430,16 +7430,16 @@
         <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -7554,16 +7554,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -7804,16 +7804,16 @@
         <v>82</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7930,16 +7930,16 @@
         <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -8180,16 +8180,16 @@
         <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -8430,16 +8430,16 @@
         <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -8552,16 +8552,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -8676,16 +8676,16 @@
         <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -8802,16 +8802,16 @@
         <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8930,25 +8930,25 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>82</v>
@@ -9056,25 +9056,25 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>82</v>
@@ -9180,7 +9180,7 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
@@ -9195,10 +9195,10 @@
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>82</v>
@@ -9306,25 +9306,25 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>82</v>
@@ -9434,25 +9434,25 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>82</v>
@@ -9684,16 +9684,16 @@
         <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -9810,16 +9810,16 @@
         <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9936,16 +9936,16 @@
         <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -10058,16 +10058,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -10308,16 +10308,16 @@
         <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -10434,16 +10434,16 @@
         <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -10560,16 +10560,16 @@
         <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -10684,16 +10684,16 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -10810,16 +10810,16 @@
         <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -10934,16 +10934,16 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -11062,16 +11062,16 @@
         <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -11186,16 +11186,16 @@
         <v>82</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -11436,16 +11436,16 @@
         <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -11558,25 +11558,25 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>82</v>
@@ -11934,16 +11934,16 @@
         <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -12184,16 +12184,16 @@
         <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -12306,25 +12306,25 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AL74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>82</v>
@@ -12434,16 +12434,16 @@
         <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -12560,25 +12560,25 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>82</v>
@@ -12684,16 +12684,16 @@
         <v>82</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -12810,16 +12810,16 @@
         <v>141</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -12938,25 +12938,25 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>82</v>
@@ -13066,25 +13066,25 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>82</v>
@@ -13194,25 +13194,25 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>82</v>
@@ -13323,25 +13323,25 @@
         <v>379</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -13444,25 +13444,25 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>82</v>
@@ -13570,25 +13570,25 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>82</v>
@@ -13700,22 +13700,22 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AP85" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>82</v>
@@ -13828,25 +13828,25 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AP86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>82</v>
@@ -13952,16 +13952,16 @@
         <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -14078,16 +14078,16 @@
         <v>141</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -14206,25 +14206,25 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>82</v>
@@ -14337,19 +14337,19 @@
         <v>434</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>437</v>
@@ -14460,25 +14460,25 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>82</v>
@@ -14586,25 +14586,25 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>82</v>
@@ -14710,25 +14710,25 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -14834,25 +14834,25 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -14960,25 +14960,25 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -15088,25 +15088,25 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>82</v>
@@ -15212,16 +15212,16 @@
         <v>82</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -15338,16 +15338,16 @@
         <v>141</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -15462,25 +15462,25 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN99" t="s" s="2">
+      <c r="AO99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
         <v>82</v>
@@ -15605,10 +15605,10 @@
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15716,25 +15716,25 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -15842,7 +15842,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -15860,7 +15860,7 @@
         <v>82</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>82</v>
@@ -15966,25 +15966,25 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16092,22 +16092,22 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL104" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="AO104" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>529</v>
@@ -16235,13 +16235,13 @@
         <v>539</v>
       </c>
       <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AQ105" t="s" s="2">
+      <c r="AR105" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AR105" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -16346,25 +16346,25 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AP106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16476,25 +16476,25 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16602,25 +16602,25 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>82</v>
@@ -16726,16 +16726,16 @@
         <v>82</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -16852,16 +16852,16 @@
         <v>141</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -16980,25 +16980,25 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17106,25 +17106,25 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ112" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17234,7 +17234,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
@@ -17243,16 +17243,16 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ113" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>82</v>
@@ -17358,25 +17358,25 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ114" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>82</v>
@@ -17482,25 +17482,25 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
+      <c r="AO115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17608,25 +17608,25 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="AL116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN116" t="s" s="2">
+      <c r="AO116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ116" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>82</v>
@@ -17732,25 +17732,25 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AL117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN117" t="s" s="2">
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>82</v>
@@ -17856,25 +17856,25 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN118" t="s" s="2">
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -17982,25 +17982,25 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN119" t="s" s="2">
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ119" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18108,25 +18108,25 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ120" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ120" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18238,25 +18238,25 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL121" t="s" s="2">
+      <c r="AO121" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
+      <c r="AP121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>82</v>
@@ -18362,16 +18362,16 @@
         <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -18488,16 +18488,16 @@
         <v>141</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -18616,25 +18616,25 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ124" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>82</v>
@@ -18742,25 +18742,25 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN125" t="s" s="2">
+      <c r="AO125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>82</v>
@@ -18870,7 +18870,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -18879,16 +18879,16 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -18994,25 +18994,25 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AL127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN127" t="s" s="2">
+      <c r="AO127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AQ127" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19118,25 +19118,25 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AL128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN128" t="s" s="2">
+      <c r="AO128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AQ128" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19244,25 +19244,25 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="AL129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN129" t="s" s="2">
+      <c r="AO129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ129" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>82</v>
@@ -19368,25 +19368,25 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AL130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN130" t="s" s="2">
+      <c r="AO130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AQ130" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>82</v>
@@ -19492,25 +19492,25 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AL131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN131" t="s" s="2">
+      <c r="AO131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ131" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AQ131" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19618,25 +19618,25 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN132" t="s" s="2">
+      <c r="AO132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ132" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AQ132" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>82</v>
@@ -19744,25 +19744,25 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN133" t="s" s="2">
+      <c r="AO133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP133" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ133" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ133" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>82</v>
@@ -19868,16 +19868,16 @@
         <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN134" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -19994,16 +19994,16 @@
         <v>141</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN135" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -20135,10 +20135,10 @@
         <v>82</v>
       </c>
       <c r="AP136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="AQ136" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20263,10 +20263,10 @@
         <v>82</v>
       </c>
       <c r="AP137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AQ137" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>82</v>
@@ -20384,10 +20384,10 @@
         <v>702</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>82</v>
+        <v>703</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>703</v>
+        <v>82</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>704</v>
@@ -20500,25 +20500,25 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN139" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="AL139" t="s" s="2">
+      <c r="AO139" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN139" t="s" s="2">
+      <c r="AP139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ139" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20628,25 +20628,25 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="AL140" t="s" s="2">
+      <c r="AO140" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN140" t="s" s="2">
+      <c r="AP140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ140" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ140" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>82</v>
@@ -20756,19 +20756,19 @@
         <v>727</v>
       </c>
       <c r="AK141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="AL141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>82</v>
@@ -20880,16 +20880,16 @@
         <v>82</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -21006,16 +21006,16 @@
         <v>141</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -21134,16 +21134,16 @@
         <v>141</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -21260,25 +21260,25 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="AL145" t="s" s="2">
+      <c r="AO145" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN145" t="s" s="2">
+      <c r="AP145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ145" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ145" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>82</v>
@@ -21386,25 +21386,25 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AL146" t="s" s="2">
+      <c r="AO146" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN146" t="s" s="2">
+      <c r="AP146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21514,25 +21514,25 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL147" t="s" s="2">
+      <c r="AO147" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN147" t="s" s="2">
+      <c r="AP147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ147" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21640,25 +21640,25 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN148" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL148" t="s" s="2">
+      <c r="AO148" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN148" t="s" s="2">
+      <c r="AP148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ148" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ148" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21766,25 +21766,25 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN149" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL149" t="s" s="2">
+      <c r="AO149" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN149" t="s" s="2">
+      <c r="AP149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ149" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -21892,25 +21892,25 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN150" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AL150" t="s" s="2">
+      <c r="AO150" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN150" t="s" s="2">
+      <c r="AP150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ150" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ150" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22016,19 +22016,19 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN151" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="AL151" t="s" s="2">
+      <c r="AO151" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>82</v>
@@ -22144,19 +22144,19 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN152" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="AL152" t="s" s="2">
+      <c r="AO152" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>82</v>
@@ -22268,16 +22268,16 @@
         <v>82</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22394,16 +22394,16 @@
         <v>141</v>
       </c>
       <c r="AK154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22522,16 +22522,16 @@
         <v>141</v>
       </c>
       <c r="AK155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN155" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22651,22 +22651,22 @@
         <v>792</v>
       </c>
       <c r="AL156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN156" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="AM156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN156" t="s" s="2">
+      <c r="AO156" t="s" s="2">
         <v>794</v>
       </c>
-      <c r="AO156" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ156" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="AQ156" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22776,25 +22776,25 @@
         <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN157" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="AL157" t="s" s="2">
+      <c r="AO157" t="s" s="2">
         <v>802</v>
       </c>
-      <c r="AM157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN157" t="s" s="2">
+      <c r="AP157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ157" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ157" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>82</v>
@@ -22902,25 +22902,25 @@
         <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN158" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AL158" t="s" s="2">
+      <c r="AO158" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN158" t="s" s="2">
+      <c r="AP158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ158" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ158" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>82</v>
@@ -23030,19 +23030,19 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AL159" t="s" s="2">
+      <c r="AO159" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>82</v>
@@ -23154,16 +23154,16 @@
         <v>82</v>
       </c>
       <c r="AK160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN160" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -23280,16 +23280,16 @@
         <v>141</v>
       </c>
       <c r="AK161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN161" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -23406,16 +23406,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN162" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23532,16 +23532,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN163" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23658,16 +23658,16 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN164" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23784,22 +23784,22 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN165" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AL165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>845</v>
+        <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>82</v>
@@ -23912,19 +23912,19 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>851</v>
       </c>
-      <c r="AL166" t="s" s="2">
+      <c r="AO166" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>82</v>
@@ -24036,16 +24036,16 @@
         <v>82</v>
       </c>
       <c r="AK167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24162,16 +24162,16 @@
         <v>141</v>
       </c>
       <c r="AK168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN168" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24290,16 +24290,16 @@
         <v>141</v>
       </c>
       <c r="AK169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN169" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -24416,25 +24416,25 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN170" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL170" t="s" s="2">
+      <c r="AO170" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN170" t="s" s="2">
+      <c r="AP170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ170" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>82</v>
@@ -24540,19 +24540,19 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN171" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="AL171" t="s" s="2">
+      <c r="AO171" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (#2) to us-core-patient</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-patient</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -682,7 +682,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (#2-2)</t>
+    <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (2-2)</t>
   </si>
   <si>
     <t>./code</t>
@@ -874,7 +874,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory</t>
   </si>
   <si>
-    <t>575: terminologyMaps using VF_ethnicityCategory on PATIENT - ETHNICITY INFORMATION (#2-6)</t>
+    <t>575: terminologyMaps using VF_ethnicityCategory on PATIENT - ETHNICITY INFORMATION (2-6)</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:ombCategory.value[x].display</t>
@@ -974,7 +974,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity</t>
   </si>
   <si>
-    <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (#2-.02)</t>
+    <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (2-.02)</t>
   </si>
   <si>
     <t>Patient.Patient.Gender,SPatient.SPatient.Gender</t>
@@ -1031,7 +1031,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFReligion</t>
   </si>
   <si>
-    <t>1598: terminologyMaps using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (#2-.08)</t>
+    <t>1598: terminologyMaps using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (2-.08)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode</t>
@@ -1189,7 +1189,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (#2-991.01)</t>
+    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (2-991.01)</t>
   </si>
   <si>
     <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
@@ -1360,7 +1360,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>273: source value from PATIENT - NAME (#2-.01)</t>
+    <t>273: source value from PATIENT - NAME (2-.01)</t>
   </si>
   <si>
     <t>SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
@@ -1563,7 +1563,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (#2-.134)</t>
+    <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (2-.134)</t>
   </si>
   <si>
     <t>./url</t>
@@ -1642,7 +1642,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (#2-.024)</t>
+    <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (2-.024)</t>
   </si>
   <si>
     <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
@@ -1673,7 +1673,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>284: source value from PATIENT - DATE OF BIRTH (#2-.03)</t>
+    <t>284: source value from PATIENT - DATE OF BIRTH (2-.03)</t>
   </si>
   <si>
     <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
@@ -1730,7 +1730,7 @@
 </t>
   </si>
   <si>
-    <t>285: source value from PATIENT - DATE OF DEATH (#2-.351) case not null</t>
+    <t>285: source value from PATIENT - DATE OF DEATH (2-.351) case not null</t>
   </si>
   <si>
     <t>Patient.Patient.DeathDateTime,SPatient.SPatient.DeathDateTime</t>
@@ -2045,7 +2045,7 @@
     <t>Patient.address:home.line</t>
   </si>
   <si>
-    <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (#2-.113)</t>
+    <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (2-.113)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
@@ -2054,7 +2054,7 @@
     <t>Patient.address:home.city</t>
   </si>
   <si>
-    <t>289: source value from PATIENT - CITY (#2-.114)</t>
+    <t>289: source value from PATIENT - CITY (2-.114)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.City</t>
@@ -2066,7 +2066,7 @@
     <t>Patient.address:home.state</t>
   </si>
   <si>
-    <t>290: source value from PATIENT - STATE (#2-.115)</t>
+    <t>290: source value from PATIENT - STATE (2-.115)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.StateIEN</t>
@@ -2075,7 +2075,7 @@
     <t>Patient.address:home.postalCode</t>
   </si>
   <si>
-    <t>291: source value from PATIENT - ZIP+4 (#2-.1112)</t>
+    <t>291: source value from PATIENT - ZIP+4 (2-.1112)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.Zip4</t>
@@ -2084,7 +2084,7 @@
     <t>Patient.address:home.country</t>
   </si>
   <si>
-    <t>292: source value from PATIENT - COUNTRY (#2-.1173)</t>
+    <t>292: source value from PATIENT - COUNTRY (2-.1173)</t>
   </si>
   <si>
     <t>Patient.address:home.period</t>
@@ -2124,7 +2124,7 @@
 </t>
   </si>
   <si>
-    <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (#2-.1217)</t>
+    <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (2-.1217)</t>
   </si>
   <si>
     <t>./low</t>
@@ -2154,7 +2154,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (#2-.1218)</t>
+    <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (2-.1218)</t>
   </si>
   <si>
     <t>./high</t>
@@ -2178,7 +2178,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus</t>
   </si>
   <si>
-    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (#2-.05)</t>
+    <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (2-.05)</t>
   </si>
   <si>
     <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus</t>
@@ -2464,7 +2464,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/simple-language</t>
   </si>
   <si>
-    <t>295: source value from PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (#2-7 &gt; 2.07-.02)</t>
+    <t>295: source value from PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (2-7 &gt; 2.07-.02)</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -3050,7 +3050,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="117.13671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="128.15234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="867">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -971,10 +971,10 @@
     <t>Patient.extension:birthsex.value[x]</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity</t>
-  </si>
-  <si>
-    <t>554: terminologyMaps using VF_genderIdentity on PATIENT - SEX (2-.02)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFbirthSex</t>
+  </si>
+  <si>
+    <t>554: terminologyMaps using VF_birthSex on PATIENT - SEX (2-.02)</t>
   </si>
   <si>
     <t>Patient.Patient.Gender,SPatient.SPatient.Gender</t>
@@ -1640,6 +1640,9 @@
   </si>
   <si>
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity</t>
   </si>
   <si>
     <t>555: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (2-.024)</t>
@@ -16059,7 +16062,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>308</v>
+        <v>526</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -16092,10 +16095,10 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
@@ -16104,13 +16107,13 @@
         <v>302</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16118,10 +16121,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16144,19 +16147,19 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -16205,7 +16208,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16220,36 +16223,36 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16272,19 +16275,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16321,7 +16324,7 @@
         <v>82</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
@@ -16331,7 +16334,7 @@
         <v>139</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16355,7 +16358,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>154</v>
@@ -16364,7 +16367,7 @@
         <v>82</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16372,13 +16375,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -16400,19 +16403,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16461,7 +16464,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16476,16 +16479,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>154</v>
@@ -16494,7 +16497,7 @@
         <v>82</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16502,10 +16505,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16528,19 +16531,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -16577,7 +16580,7 @@
         <v>82</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
@@ -16587,7 +16590,7 @@
         <v>139</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -16611,16 +16614,16 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>82</v>
@@ -16628,10 +16631,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16752,10 +16755,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16878,10 +16881,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16907,16 +16910,16 @@
         <v>110</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16929,7 +16932,7 @@
         <v>82</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -16944,10 +16947,10 @@
         <v>181</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -16965,7 +16968,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16998,7 +17001,7 @@
         <v>82</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17006,10 +17009,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17035,13 +17038,13 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -17055,7 +17058,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -17070,10 +17073,10 @@
         <v>181</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -17091,7 +17094,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17124,7 +17127,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17132,10 +17135,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17161,13 +17164,13 @@
         <v>150</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>432</v>
@@ -17183,7 +17186,7 @@
         <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>82</v>
@@ -17219,7 +17222,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17252,7 +17255,7 @@
         <v>82</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>82</v>
@@ -17260,10 +17263,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17289,10 +17292,10 @@
         <v>150</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17307,7 +17310,7 @@
         <v>82</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>82</v>
@@ -17343,7 +17346,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17367,7 +17370,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17376,7 +17379,7 @@
         <v>82</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>82</v>
@@ -17384,14 +17387,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17413,10 +17416,10 @@
         <v>150</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17431,7 +17434,7 @@
         <v>82</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>82</v>
@@ -17467,7 +17470,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17491,7 +17494,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -17500,7 +17503,7 @@
         <v>82</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17508,14 +17511,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17537,13 +17540,13 @@
         <v>150</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17557,7 +17560,7 @@
         <v>82</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>82</v>
@@ -17593,7 +17596,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -17617,7 +17620,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -17626,7 +17629,7 @@
         <v>82</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>82</v>
@@ -17634,14 +17637,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -17663,10 +17666,10 @@
         <v>150</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17696,10 +17699,10 @@
         <v>359</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -17717,7 +17720,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -17741,7 +17744,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -17750,7 +17753,7 @@
         <v>82</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>82</v>
@@ -17758,14 +17761,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -17787,10 +17790,10 @@
         <v>150</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17805,7 +17808,7 @@
         <v>82</v>
       </c>
       <c r="T118" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="U118" t="s" s="2">
         <v>82</v>
@@ -17841,7 +17844,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17865,7 +17868,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -17874,7 +17877,7 @@
         <v>82</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -17882,10 +17885,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17911,13 +17914,13 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17967,7 +17970,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17991,7 +17994,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -18000,7 +18003,7 @@
         <v>82</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18008,10 +18011,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18037,14 +18040,14 @@
         <v>385</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18057,7 +18060,7 @@
         <v>82</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>82</v>
@@ -18093,7 +18096,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18126,7 +18129,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18134,13 +18137,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -18162,19 +18165,19 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -18223,7 +18226,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18247,16 +18250,16 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>82</v>
@@ -18264,10 +18267,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18388,10 +18391,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18514,10 +18517,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18543,16 +18546,16 @@
         <v>110</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -18565,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="T124" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="U124" t="s" s="2">
         <v>82</v>
@@ -18580,10 +18583,10 @@
         <v>181</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>82</v>
@@ -18601,7 +18604,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -18634,7 +18637,7 @@
         <v>82</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>82</v>
@@ -18642,10 +18645,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18671,13 +18674,13 @@
         <v>110</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18691,7 +18694,7 @@
         <v>82</v>
       </c>
       <c r="T125" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="U125" t="s" s="2">
         <v>82</v>
@@ -18706,10 +18709,10 @@
         <v>181</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
@@ -18727,7 +18730,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -18760,7 +18763,7 @@
         <v>82</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>82</v>
@@ -18768,10 +18771,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18797,13 +18800,13 @@
         <v>150</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>432</v>
@@ -18819,7 +18822,7 @@
         <v>82</v>
       </c>
       <c r="T126" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="U126" t="s" s="2">
         <v>82</v>
@@ -18855,7 +18858,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18888,7 +18891,7 @@
         <v>82</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -18896,10 +18899,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18925,10 +18928,10 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18943,7 +18946,7 @@
         <v>82</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>82</v>
@@ -18979,7 +18982,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18994,16 +18997,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -19012,7 +19015,7 @@
         <v>82</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19020,14 +19023,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -19049,10 +19052,10 @@
         <v>150</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -19067,7 +19070,7 @@
         <v>82</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>82</v>
@@ -19103,7 +19106,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19118,16 +19121,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19136,7 +19139,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19144,14 +19147,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19173,13 +19176,13 @@
         <v>150</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19193,7 +19196,7 @@
         <v>82</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>82</v>
@@ -19229,7 +19232,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19253,7 +19256,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -19262,7 +19265,7 @@
         <v>82</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>82</v>
@@ -19270,14 +19273,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19299,10 +19302,10 @@
         <v>150</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19332,10 +19335,10 @@
         <v>359</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -19353,7 +19356,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19368,16 +19371,16 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19386,7 +19389,7 @@
         <v>82</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>82</v>
@@ -19394,14 +19397,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -19423,10 +19426,10 @@
         <v>150</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -19441,7 +19444,7 @@
         <v>82</v>
       </c>
       <c r="T131" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="U131" t="s" s="2">
         <v>82</v>
@@ -19477,7 +19480,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19492,16 +19495,16 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -19510,7 +19513,7 @@
         <v>82</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19518,10 +19521,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19547,13 +19550,13 @@
         <v>150</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19603,7 +19606,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19618,7 +19621,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -19627,7 +19630,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -19636,7 +19639,7 @@
         <v>82</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>82</v>
@@ -19644,10 +19647,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19673,14 +19676,14 @@
         <v>385</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -19693,7 +19696,7 @@
         <v>82</v>
       </c>
       <c r="T133" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="U133" t="s" s="2">
         <v>82</v>
@@ -19729,7 +19732,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19762,7 +19765,7 @@
         <v>82</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>82</v>
@@ -19770,10 +19773,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19894,10 +19897,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20020,10 +20023,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20046,16 +20049,16 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -20105,7 +20108,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20114,13 +20117,13 @@
         <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20129,7 +20132,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20138,7 +20141,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20146,10 +20149,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20172,23 +20175,23 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q137" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="R137" t="s" s="2">
         <v>82</v>
@@ -20233,7 +20236,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20242,13 +20245,13 @@
         <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -20257,7 +20260,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -20266,7 +20269,7 @@
         <v>82</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>82</v>
@@ -20274,10 +20277,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20303,14 +20306,14 @@
         <v>324</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -20339,7 +20342,7 @@
       </c>
       <c r="Y138" s="2"/>
       <c r="Z138" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -20357,7 +20360,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20372,25 +20375,25 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>82</v>
@@ -20398,10 +20401,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20424,19 +20427,19 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20485,7 +20488,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20509,7 +20512,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>154</v>
@@ -20518,7 +20521,7 @@
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20526,10 +20529,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20552,19 +20555,19 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20613,7 +20616,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20637,7 +20640,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>154</v>
@@ -20646,7 +20649,7 @@
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>82</v>
@@ -20654,10 +20657,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20680,19 +20683,19 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -20741,7 +20744,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20753,7 +20756,7 @@
         <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>82</v>
@@ -20765,7 +20768,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -20782,10 +20785,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20906,10 +20909,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21032,14 +21035,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -21061,10 +21064,10 @@
         <v>135</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>160</v>
@@ -21119,7 +21122,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -21160,10 +21163,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21189,14 +21192,14 @@
         <v>324</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -21224,10 +21227,10 @@
         <v>359</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -21245,7 +21248,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -21269,7 +21272,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>154</v>
@@ -21278,7 +21281,7 @@
         <v>82</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>82</v>
@@ -21286,10 +21289,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21315,14 +21318,14 @@
         <v>408</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21371,7 +21374,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21404,7 +21407,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21412,10 +21415,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21441,13 +21444,13 @@
         <v>475</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>479</v>
@@ -21499,7 +21502,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21532,7 +21535,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21540,10 +21543,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21566,17 +21569,17 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21625,7 +21628,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21649,7 +21652,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>154</v>
@@ -21658,7 +21661,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21666,10 +21669,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21698,11 +21701,11 @@
         <v>522</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -21730,10 +21733,10 @@
         <v>181</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -21751,7 +21754,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21784,7 +21787,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -21792,10 +21795,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21821,14 +21824,14 @@
         <v>392</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -21877,7 +21880,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21886,7 +21889,7 @@
         <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>102</v>
@@ -21901,7 +21904,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>154</v>
@@ -21910,7 +21913,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -21918,10 +21921,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21947,10 +21950,10 @@
         <v>385</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -22001,7 +22004,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22025,7 +22028,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>154</v>
@@ -22042,10 +22045,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22068,19 +22071,19 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -22129,7 +22132,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22153,10 +22156,10 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>82</v>
@@ -22170,10 +22173,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22294,10 +22297,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22420,14 +22423,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -22449,10 +22452,10 @@
         <v>135</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>160</v>
@@ -22507,7 +22510,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22548,10 +22551,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22577,16 +22580,16 @@
         <v>324</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22615,7 +22618,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -22633,7 +22636,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>90</v>
@@ -22648,7 +22651,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>82</v>
@@ -22657,16 +22660,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22674,10 +22677,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22703,16 +22706,16 @@
         <v>226</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -22761,7 +22764,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -22785,16 +22788,16 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>82</v>
@@ -22802,14 +22805,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -22828,16 +22831,16 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -22887,7 +22890,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -22911,7 +22914,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>154</v>
@@ -22920,7 +22923,7 @@
         <v>82</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>82</v>
@@ -22928,10 +22931,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22957,16 +22960,16 @@
         <v>392</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23015,7 +23018,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23039,10 +23042,10 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>82</v>
@@ -23056,10 +23059,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23180,10 +23183,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23306,10 +23309,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23335,13 +23338,13 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -23391,7 +23394,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23400,7 +23403,7 @@
         <v>90</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>102</v>
@@ -23432,10 +23435,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23461,13 +23464,13 @@
         <v>104</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23496,10 +23499,10 @@
         <v>359</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -23517,7 +23520,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23558,10 +23561,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23587,13 +23590,13 @@
         <v>335</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23643,7 +23646,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23667,7 +23670,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23684,10 +23687,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23713,13 +23716,13 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23730,7 +23733,7 @@
         <v>82</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T165" t="s" s="2">
         <v>82</v>
@@ -23769,7 +23772,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -23784,7 +23787,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>82</v>
@@ -23810,10 +23813,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23836,19 +23839,19 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -23897,7 +23900,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23921,7 +23924,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>154</v>
@@ -23938,10 +23941,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24062,10 +24065,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24188,14 +24191,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24217,10 +24220,10 @@
         <v>135</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>160</v>
@@ -24275,7 +24278,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -24316,10 +24319,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24342,16 +24345,16 @@
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24401,7 +24404,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>90</v>
@@ -24434,7 +24437,7 @@
         <v>82</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>82</v>
@@ -24442,10 +24445,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24471,10 +24474,10 @@
         <v>110</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24504,10 +24507,10 @@
         <v>181</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -24525,7 +24528,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>90</v>
@@ -24549,7 +24552,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="868">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1025,10 +1025,14 @@
 </t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFReligion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>1598: terminologyMaps using VF_Religion on PATIENT - RELIGIOUS PREFERENCE (2-.08)</t>
@@ -11865,7 +11869,7 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>151</v>
@@ -11931,7 +11935,7 @@
         <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>82</v>
@@ -12303,16 +12307,16 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12335,10 +12339,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12364,16 +12368,16 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -12422,7 +12426,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -12463,10 +12467,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12489,17 +12493,17 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -12548,7 +12552,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12572,16 +12576,16 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>82</v>
@@ -12589,10 +12593,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12713,10 +12717,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12839,10 +12843,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12868,16 +12872,16 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12905,10 +12909,10 @@
         <v>181</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12926,7 +12930,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12950,7 +12954,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12967,10 +12971,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12996,16 +13000,16 @@
         <v>324</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13030,13 +13034,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -13054,7 +13058,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -13078,7 +13082,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -13087,7 +13091,7 @@
         <v>82</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>82</v>
@@ -13095,10 +13099,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13124,16 +13128,16 @@
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -13146,7 +13150,7 @@
         <v>82</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>82</v>
@@ -13182,7 +13186,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -13206,7 +13210,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -13215,7 +13219,7 @@
         <v>82</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>82</v>
@@ -13223,10 +13227,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13252,13 +13256,13 @@
         <v>150</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13272,7 +13276,7 @@
         <v>82</v>
       </c>
       <c r="T82" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U82" t="s" s="2">
         <v>82</v>
@@ -13308,7 +13312,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -13323,16 +13327,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -13341,7 +13345,7 @@
         <v>82</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>82</v>
@@ -13349,10 +13353,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13375,13 +13379,13 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13432,7 +13436,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -13456,7 +13460,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -13465,7 +13469,7 @@
         <v>82</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>82</v>
@@ -13473,10 +13477,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13499,16 +13503,16 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13558,7 +13562,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13582,7 +13586,7 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -13591,7 +13595,7 @@
         <v>82</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>82</v>
@@ -13599,10 +13603,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13628,67 +13632,67 @@
         <v>226</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q85" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="R85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q85" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="R85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13712,13 +13716,13 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>82</v>
@@ -13729,10 +13733,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13755,19 +13759,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -13816,7 +13820,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13840,16 +13844,16 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>82</v>
@@ -13857,10 +13861,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13981,10 +13985,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14107,10 +14111,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14136,16 +14140,16 @@
         <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -14173,10 +14177,10 @@
         <v>181</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -14194,7 +14198,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -14218,7 +14222,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -14227,7 +14231,7 @@
         <v>82</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>82</v>
@@ -14235,10 +14239,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14264,16 +14268,16 @@
         <v>150</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -14322,7 +14326,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -14337,16 +14341,16 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -14355,7 +14359,7 @@
         <v>82</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>82</v>
@@ -14363,14 +14367,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -14392,13 +14396,13 @@
         <v>150</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -14448,7 +14452,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -14457,7 +14461,7 @@
         <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>102</v>
@@ -14472,7 +14476,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -14481,7 +14485,7 @@
         <v>82</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>82</v>
@@ -14489,14 +14493,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14518,13 +14522,13 @@
         <v>150</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14574,7 +14578,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14583,7 +14587,7 @@
         <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>102</v>
@@ -14598,7 +14602,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -14607,7 +14611,7 @@
         <v>82</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>82</v>
@@ -14615,10 +14619,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14644,10 +14648,10 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14698,7 +14702,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14722,7 +14726,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -14731,7 +14735,7 @@
         <v>82</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -14739,10 +14743,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14768,10 +14772,10 @@
         <v>150</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14822,7 +14826,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14846,7 +14850,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -14855,7 +14859,7 @@
         <v>82</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -14863,10 +14867,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14889,17 +14893,17 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14948,7 +14952,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14972,7 +14976,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14981,7 +14985,7 @@
         <v>82</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -14989,10 +14993,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15015,19 +15019,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15076,7 +15080,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -15100,16 +15104,16 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>82</v>
@@ -15117,10 +15121,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15241,10 +15245,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15367,10 +15371,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15396,10 +15400,10 @@
         <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -15429,10 +15433,10 @@
         <v>181</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -15450,7 +15454,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -15459,7 +15463,7 @@
         <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>102</v>
@@ -15474,7 +15478,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -15483,7 +15487,7 @@
         <v>82</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AR99" t="s" s="2">
         <v>82</v>
@@ -15491,10 +15495,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15520,16 +15524,16 @@
         <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15578,7 +15582,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15593,7 +15597,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -15602,7 +15606,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -15611,7 +15615,7 @@
         <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15619,10 +15623,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15648,16 +15652,16 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15686,7 +15690,7 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -15704,7 +15708,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15728,7 +15732,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -15737,7 +15741,7 @@
         <v>82</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -15745,10 +15749,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15771,16 +15775,16 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15830,7 +15834,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15871,10 +15875,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15897,13 +15901,13 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15954,7 +15958,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15978,7 +15982,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15995,10 +15999,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16024,16 +16028,16 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -16062,7 +16066,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -16080,7 +16084,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16095,10 +16099,10 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
@@ -16107,13 +16111,13 @@
         <v>302</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16121,10 +16125,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16147,19 +16151,19 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -16208,7 +16212,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16223,36 +16227,36 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16275,19 +16279,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16324,7 +16328,7 @@
         <v>82</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
@@ -16334,7 +16338,7 @@
         <v>139</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16358,7 +16362,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>154</v>
@@ -16367,7 +16371,7 @@
         <v>82</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16375,13 +16379,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -16403,19 +16407,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16464,7 +16468,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16479,16 +16483,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>154</v>
@@ -16497,7 +16501,7 @@
         <v>82</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16505,10 +16509,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16531,19 +16535,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -16580,7 +16584,7 @@
         <v>82</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
@@ -16590,7 +16594,7 @@
         <v>139</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -16614,16 +16618,16 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>82</v>
@@ -16631,10 +16635,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16755,10 +16759,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16881,10 +16885,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16910,16 +16914,16 @@
         <v>110</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16932,7 +16936,7 @@
         <v>82</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -16947,10 +16951,10 @@
         <v>181</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -16968,7 +16972,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16992,7 +16996,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -17001,7 +17005,7 @@
         <v>82</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17009,10 +17013,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17038,13 +17042,13 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -17058,7 +17062,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -17073,10 +17077,10 @@
         <v>181</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -17094,7 +17098,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17118,7 +17122,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -17127,7 +17131,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17135,10 +17139,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17164,16 +17168,16 @@
         <v>150</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -17186,7 +17190,7 @@
         <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>82</v>
@@ -17222,7 +17226,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17246,7 +17250,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -17255,7 +17259,7 @@
         <v>82</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>82</v>
@@ -17263,10 +17267,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17292,10 +17296,10 @@
         <v>150</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17310,7 +17314,7 @@
         <v>82</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>82</v>
@@ -17346,7 +17350,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17370,7 +17374,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17379,7 +17383,7 @@
         <v>82</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>82</v>
@@ -17387,14 +17391,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -17416,10 +17420,10 @@
         <v>150</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17434,7 +17438,7 @@
         <v>82</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>82</v>
@@ -17470,7 +17474,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17494,7 +17498,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -17503,7 +17507,7 @@
         <v>82</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17511,14 +17515,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17540,13 +17544,13 @@
         <v>150</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17560,7 +17564,7 @@
         <v>82</v>
       </c>
       <c r="T116" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="U116" t="s" s="2">
         <v>82</v>
@@ -17596,7 +17600,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -17620,7 +17624,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -17629,7 +17633,7 @@
         <v>82</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>82</v>
@@ -17637,14 +17641,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -17666,10 +17670,10 @@
         <v>150</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17696,13 +17700,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -17720,7 +17724,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -17744,7 +17748,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -17753,7 +17757,7 @@
         <v>82</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>82</v>
@@ -17761,14 +17765,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -17790,10 +17794,10 @@
         <v>150</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17808,7 +17812,7 @@
         <v>82</v>
       </c>
       <c r="T118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="U118" t="s" s="2">
         <v>82</v>
@@ -17844,7 +17848,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17868,7 +17872,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -17877,7 +17881,7 @@
         <v>82</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -17885,10 +17889,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17914,13 +17918,13 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17970,7 +17974,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17994,7 +17998,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -18003,7 +18007,7 @@
         <v>82</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18011,10 +18015,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18037,17 +18041,17 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18060,7 +18064,7 @@
         <v>82</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>82</v>
@@ -18096,7 +18100,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18120,7 +18124,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -18129,7 +18133,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18137,13 +18141,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -18165,19 +18169,19 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -18226,7 +18230,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18250,16 +18254,16 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>82</v>
@@ -18267,10 +18271,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18391,10 +18395,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18517,10 +18521,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18546,16 +18550,16 @@
         <v>110</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -18568,7 +18572,7 @@
         <v>82</v>
       </c>
       <c r="T124" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U124" t="s" s="2">
         <v>82</v>
@@ -18583,10 +18587,10 @@
         <v>181</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>82</v>
@@ -18604,7 +18608,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -18628,7 +18632,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -18637,7 +18641,7 @@
         <v>82</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>82</v>
@@ -18645,10 +18649,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18674,13 +18678,13 @@
         <v>110</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18694,7 +18698,7 @@
         <v>82</v>
       </c>
       <c r="T125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U125" t="s" s="2">
         <v>82</v>
@@ -18709,10 +18713,10 @@
         <v>181</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
@@ -18730,7 +18734,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -18754,7 +18758,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -18763,7 +18767,7 @@
         <v>82</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>82</v>
@@ -18771,10 +18775,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18800,16 +18804,16 @@
         <v>150</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -18822,7 +18826,7 @@
         <v>82</v>
       </c>
       <c r="T126" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="U126" t="s" s="2">
         <v>82</v>
@@ -18858,7 +18862,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18882,7 +18886,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -18891,7 +18895,7 @@
         <v>82</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -18899,10 +18903,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18928,10 +18932,10 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18946,7 +18950,7 @@
         <v>82</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>82</v>
@@ -18982,7 +18986,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18997,16 +19001,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -19015,7 +19019,7 @@
         <v>82</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19023,14 +19027,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -19052,10 +19056,10 @@
         <v>150</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -19070,7 +19074,7 @@
         <v>82</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>82</v>
@@ -19106,7 +19110,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19121,16 +19125,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19139,7 +19143,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19147,14 +19151,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19176,13 +19180,13 @@
         <v>150</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19196,7 +19200,7 @@
         <v>82</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>82</v>
@@ -19232,7 +19236,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19256,7 +19260,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -19265,7 +19269,7 @@
         <v>82</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>82</v>
@@ -19273,14 +19277,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19302,10 +19306,10 @@
         <v>150</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19332,13 +19336,13 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -19356,7 +19360,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19371,16 +19375,16 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19389,7 +19393,7 @@
         <v>82</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>82</v>
@@ -19397,14 +19401,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -19426,10 +19430,10 @@
         <v>150</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -19444,7 +19448,7 @@
         <v>82</v>
       </c>
       <c r="T131" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="U131" t="s" s="2">
         <v>82</v>
@@ -19480,7 +19484,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19495,16 +19499,16 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -19513,7 +19517,7 @@
         <v>82</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19521,10 +19525,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19550,13 +19554,13 @@
         <v>150</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19606,7 +19610,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19621,7 +19625,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -19630,7 +19634,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -19639,7 +19643,7 @@
         <v>82</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>82</v>
@@ -19647,10 +19651,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19673,17 +19677,17 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -19696,7 +19700,7 @@
         <v>82</v>
       </c>
       <c r="T133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U133" t="s" s="2">
         <v>82</v>
@@ -19732,7 +19736,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19756,7 +19760,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -19765,7 +19769,7 @@
         <v>82</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>82</v>
@@ -19773,10 +19777,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19897,10 +19901,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20023,10 +20027,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20049,16 +20053,16 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -20108,7 +20112,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20117,13 +20121,13 @@
         <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20132,7 +20136,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20141,7 +20145,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20149,10 +20153,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20175,23 +20179,23 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q137" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="R137" t="s" s="2">
         <v>82</v>
@@ -20236,7 +20240,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20245,13 +20249,13 @@
         <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -20260,7 +20264,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -20269,7 +20273,7 @@
         <v>82</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>82</v>
@@ -20277,10 +20281,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20306,14 +20310,14 @@
         <v>324</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -20342,7 +20346,7 @@
       </c>
       <c r="Y138" s="2"/>
       <c r="Z138" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -20360,7 +20364,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20375,25 +20379,25 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>82</v>
@@ -20401,10 +20405,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20427,19 +20431,19 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20488,7 +20492,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20512,7 +20516,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>154</v>
@@ -20521,7 +20525,7 @@
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20529,10 +20533,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20555,19 +20559,19 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20616,7 +20620,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20640,7 +20644,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>154</v>
@@ -20649,7 +20653,7 @@
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>82</v>
@@ -20657,10 +20661,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20683,19 +20687,19 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -20744,7 +20748,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20756,7 +20760,7 @@
         <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>82</v>
@@ -20768,7 +20772,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -20785,10 +20789,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20909,10 +20913,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21035,14 +21039,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -21064,16 +21068,16 @@
         <v>135</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -21122,7 +21126,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -21163,10 +21167,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21192,14 +21196,14 @@
         <v>324</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -21224,13 +21228,13 @@
         <v>82</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -21248,7 +21252,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -21272,7 +21276,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>154</v>
@@ -21281,7 +21285,7 @@
         <v>82</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>82</v>
@@ -21289,10 +21293,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21315,17 +21319,17 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21374,7 +21378,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21398,7 +21402,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>154</v>
@@ -21407,7 +21411,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21415,10 +21419,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21441,19 +21445,19 @@
         <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -21502,7 +21506,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21526,7 +21530,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>154</v>
@@ -21535,7 +21539,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21543,10 +21547,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21569,17 +21573,17 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21628,7 +21632,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21652,7 +21656,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>154</v>
@@ -21661,7 +21665,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21669,10 +21673,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21698,14 +21702,14 @@
         <v>110</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -21733,10 +21737,10 @@
         <v>181</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -21754,7 +21758,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21787,7 +21791,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -21795,10 +21799,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21821,17 +21825,17 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -21880,7 +21884,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21889,7 +21893,7 @@
         <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>102</v>
@@ -21904,7 +21908,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>154</v>
@@ -21913,7 +21917,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -21921,10 +21925,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21947,13 +21951,13 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -22004,7 +22008,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22028,7 +22032,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>154</v>
@@ -22045,10 +22049,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22071,19 +22075,19 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -22132,7 +22136,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22156,10 +22160,10 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>82</v>
@@ -22173,10 +22177,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22297,10 +22301,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22423,14 +22427,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -22452,16 +22456,16 @@
         <v>135</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22510,7 +22514,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22551,10 +22555,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22580,16 +22584,16 @@
         <v>324</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22614,11 +22618,11 @@
         <v>82</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -22636,7 +22640,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>90</v>
@@ -22651,7 +22655,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>82</v>
@@ -22660,16 +22664,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22677,10 +22681,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22706,16 +22710,16 @@
         <v>226</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -22764,7 +22768,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -22788,16 +22792,16 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>82</v>
@@ -22805,14 +22809,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -22831,16 +22835,16 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -22890,7 +22894,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -22914,7 +22918,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>154</v>
@@ -22923,7 +22927,7 @@
         <v>82</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>82</v>
@@ -22931,10 +22935,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22957,19 +22961,19 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23018,7 +23022,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23042,10 +23046,10 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AP159" t="s" s="2">
         <v>82</v>
@@ -23059,10 +23063,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23183,10 +23187,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23309,10 +23313,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23338,13 +23342,13 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -23394,7 +23398,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23403,7 +23407,7 @@
         <v>90</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>102</v>
@@ -23435,10 +23439,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23464,13 +23468,13 @@
         <v>104</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23496,13 +23500,13 @@
         <v>82</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -23520,7 +23524,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23561,10 +23565,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23587,16 +23591,16 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23646,7 +23650,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23670,7 +23674,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23687,10 +23691,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23716,13 +23720,13 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23733,7 +23737,7 @@
         <v>82</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="T165" t="s" s="2">
         <v>82</v>
@@ -23772,7 +23776,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -23787,7 +23791,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>82</v>
@@ -23813,10 +23817,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23839,19 +23843,19 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -23900,7 +23904,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23924,7 +23928,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>154</v>
@@ -23941,10 +23945,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24065,10 +24069,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24191,14 +24195,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24220,16 +24224,16 @@
         <v>135</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -24278,7 +24282,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -24319,10 +24323,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24345,16 +24349,16 @@
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24404,7 +24408,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>90</v>
@@ -24428,7 +24432,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>154</v>
@@ -24437,7 +24441,7 @@
         <v>82</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>82</v>
@@ -24445,10 +24449,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24474,10 +24478,10 @@
         <v>110</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24507,10 +24511,10 @@
         <v>181</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -24528,7 +24532,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>90</v>
@@ -24552,7 +24556,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7012" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7012" uniqueCount="878">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2055,25 +2055,28 @@
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
-    <t>Patient.address:home</t>
-  </si>
-  <si>
-    <t>Patient.address:home.id</t>
-  </si>
-  <si>
-    <t>Patient.address:home.extension</t>
-  </si>
-  <si>
-    <t>Patient.address:home.use</t>
-  </si>
-  <si>
-    <t>Patient.address:home.type</t>
-  </si>
-  <si>
-    <t>Patient.address:home.text</t>
-  </si>
-  <si>
-    <t>Patient.address:home.line</t>
+    <t>Patient.address:va-home</t>
+  </si>
+  <si>
+    <t>va-home</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.id</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.extension</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.use</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.type</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.text</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.line</t>
   </si>
   <si>
     <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (2-.113)</t>
@@ -2082,7 +2085,7 @@
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
   </si>
   <si>
-    <t>Patient.address:home.city</t>
+    <t>Patient.address:va-home.city</t>
   </si>
   <si>
     <t>289: source value from PATIENT - CITY (2-.114)</t>
@@ -2091,10 +2094,10 @@
     <t>SPatient.SPatientGISAddress.City</t>
   </si>
   <si>
-    <t>Patient.address:home.district</t>
-  </si>
-  <si>
-    <t>Patient.address:home.state</t>
+    <t>Patient.address:va-home.district</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.state</t>
   </si>
   <si>
     <t>290: source value from PATIENT - STATE (2-.115)</t>
@@ -2103,7 +2106,7 @@
     <t>SPatient.SPatientGISAddress.StateIEN,SPatient.SPatientGISAddress.StateSID</t>
   </si>
   <si>
-    <t>Patient.address:home.postalCode</t>
+    <t>Patient.address:va-home.postalCode</t>
   </si>
   <si>
     <t>291: source value from PATIENT - ZIP+4 (2-.1112)</t>
@@ -2112,28 +2115,28 @@
     <t>SPatient.SPatientGISAddress.Zip4</t>
   </si>
   <si>
-    <t>Patient.address:home.country</t>
+    <t>Patient.address:va-home.country</t>
   </si>
   <si>
     <t>292: source value from PATIENT - COUNTRY (2-.1173)</t>
   </si>
   <si>
-    <t>Patient.address:home.period</t>
-  </si>
-  <si>
-    <t>Patient.address:home.period.id</t>
+    <t>Patient.address:va-home.period</t>
+  </si>
+  <si>
+    <t>Patient.address:va-home.period.id</t>
   </si>
   <si>
     <t>Patient.address.period.id</t>
   </si>
   <si>
-    <t>Patient.address:home.period.extension</t>
+    <t>Patient.address:va-home.period.extension</t>
   </si>
   <si>
     <t>Patient.address.period.extension</t>
   </si>
   <si>
-    <t>Patient.address:home.period.start</t>
+    <t>Patient.address:va-home.period.start</t>
   </si>
   <si>
     <t>Patient.address.period.start</t>
@@ -2164,7 +2167,7 @@
     <t>DR.1</t>
   </si>
   <si>
-    <t>Patient.address:home.period.end</t>
+    <t>Patient.address:va-home.period.end</t>
   </si>
   <si>
     <t>Patient.address.period.end</t>
@@ -18670,7 +18673,7 @@
         <v>566</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>583</v>
+        <v>660</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>82</v>
@@ -18794,7 +18797,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>576</v>
@@ -18918,7 +18921,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>577</v>
@@ -19044,7 +19047,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>578</v>
@@ -19172,7 +19175,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>588</v>
@@ -19298,7 +19301,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>597</v>
@@ -19426,7 +19429,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>604</v>
@@ -19524,10 +19527,10 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
@@ -19550,7 +19553,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>611</v>
@@ -19648,10 +19651,10 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>82</v>
@@ -19674,7 +19677,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>619</v>
@@ -19800,7 +19803,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>628</v>
@@ -19898,10 +19901,10 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
@@ -19924,7 +19927,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>637</v>
@@ -20022,10 +20025,10 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
@@ -20048,7 +20051,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>645</v>
@@ -20148,7 +20151,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20174,7 +20177,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>652</v>
@@ -20300,10 +20303,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20424,10 +20427,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20550,10 +20553,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20579,13 +20582,13 @@
         <v>563</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -20635,7 +20638,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20644,13 +20647,13 @@
         <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -20659,7 +20662,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -20668,7 +20671,7 @@
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>82</v>
@@ -20676,10 +20679,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20705,20 +20708,20 @@
         <v>563</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q141" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="R141" t="s" s="2">
         <v>82</v>
@@ -20763,7 +20766,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20772,13 +20775,13 @@
         <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -20787,7 +20790,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -20796,7 +20799,7 @@
         <v>82</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>82</v>
@@ -20804,10 +20807,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20833,14 +20836,14 @@
         <v>319</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -20869,7 +20872,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -20887,7 +20890,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20902,25 +20905,25 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AP142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -20928,10 +20931,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20954,19 +20957,19 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21015,7 +21018,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21039,7 +21042,7 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>154</v>
@@ -21048,7 +21051,7 @@
         <v>82</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21056,10 +21059,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21082,19 +21085,19 @@
         <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -21143,7 +21146,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -21167,7 +21170,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>154</v>
@@ -21176,7 +21179,7 @@
         <v>82</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>82</v>
@@ -21184,10 +21187,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21210,19 +21213,19 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -21271,7 +21274,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -21283,7 +21286,7 @@
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
@@ -21295,7 +21298,7 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>154</v>
@@ -21312,10 +21315,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21436,10 +21439,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21562,14 +21565,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -21591,10 +21594,10 @@
         <v>135</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>160</v>
@@ -21649,7 +21652,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21690,10 +21693,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21719,14 +21722,14 @@
         <v>319</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -21754,10 +21757,10 @@
         <v>369</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -21775,7 +21778,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21799,7 +21802,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>154</v>
@@ -21808,7 +21811,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -21816,10 +21819,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21845,14 +21848,14 @@
         <v>418</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -21901,7 +21904,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21934,7 +21937,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -21942,10 +21945,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21971,13 +21974,13 @@
         <v>485</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O151" t="s" s="2">
         <v>489</v>
@@ -22029,7 +22032,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22062,7 +22065,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22070,10 +22073,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22099,14 +22102,14 @@
         <v>567</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -22155,7 +22158,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22188,7 +22191,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22196,10 +22199,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22228,11 +22231,11 @@
         <v>532</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -22260,10 +22263,10 @@
         <v>181</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -22281,7 +22284,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22314,7 +22317,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22322,10 +22325,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22351,14 +22354,14 @@
         <v>402</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -22407,7 +22410,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22416,7 +22419,7 @@
         <v>90</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>102</v>
@@ -22431,7 +22434,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>154</v>
@@ -22440,7 +22443,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22448,10 +22451,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22477,10 +22480,10 @@
         <v>395</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -22531,7 +22534,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22555,7 +22558,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>154</v>
@@ -22572,10 +22575,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22598,19 +22601,19 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22659,7 +22662,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22683,10 +22686,10 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
@@ -22700,10 +22703,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22824,10 +22827,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22950,14 +22953,14 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22979,10 +22982,10 @@
         <v>135</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>160</v>
@@ -23037,7 +23040,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23078,10 +23081,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23107,16 +23110,16 @@
         <v>319</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -23145,7 +23148,7 @@
       </c>
       <c r="Y160" s="2"/>
       <c r="Z160" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -23163,7 +23166,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>90</v>
@@ -23178,25 +23181,25 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AP160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23204,10 +23207,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23233,16 +23236,16 @@
         <v>226</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -23291,7 +23294,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23315,16 +23318,16 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23332,14 +23335,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -23358,16 +23361,16 @@
         <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -23417,7 +23420,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23441,7 +23444,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>154</v>
@@ -23450,7 +23453,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23458,10 +23461,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23487,16 +23490,16 @@
         <v>402</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -23545,7 +23548,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23569,10 +23572,10 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>82</v>
@@ -23586,10 +23589,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23710,10 +23713,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23836,10 +23839,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23865,13 +23868,13 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -23921,7 +23924,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23930,7 +23933,7 @@
         <v>90</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -23962,10 +23965,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23991,13 +23994,13 @@
         <v>104</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24026,10 +24029,10 @@
         <v>369</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -24047,7 +24050,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24088,10 +24091,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24117,13 +24120,13 @@
         <v>345</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -24173,7 +24176,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24197,7 +24200,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24214,10 +24217,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24243,13 +24246,13 @@
         <v>150</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24260,7 +24263,7 @@
         <v>82</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>82</v>
@@ -24299,7 +24302,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -24314,7 +24317,7 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>82</v>
@@ -24340,10 +24343,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24366,19 +24369,19 @@
         <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -24427,7 +24430,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -24451,7 +24454,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>154</v>
@@ -24468,10 +24471,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24592,10 +24595,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24718,14 +24721,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -24747,10 +24750,10 @@
         <v>135</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>160</v>
@@ -24805,7 +24808,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -24846,10 +24849,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24872,16 +24875,16 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -24931,7 +24934,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -24964,7 +24967,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -24972,10 +24975,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25001,10 +25004,10 @@
         <v>110</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -25034,10 +25037,10 @@
         <v>181</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
@@ -25055,7 +25058,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>90</v>
@@ -25079,7 +25082,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -997,12 +997,6 @@
     <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
   </si>
   <si>
-    <t>Patient.extension:us-core-genderIdentity</t>
-  </si>
-  <si>
-    <t>us-core-genderIdentity</t>
-  </si>
-  <si>
     <t>Patient.extension:us-core-ethnicity</t>
   </si>
   <si>
@@ -1060,6 +1054,12 @@
   </si>
   <si>
     <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode,Patient.Patient.ReligionIEN,SPatient.SPatient.ReligionIEN</t>
+  </si>
+  <si>
+    <t>Patient.extension:us-core-genderIdentity</t>
+  </si>
+  <si>
+    <t>us-core-genderIdentity</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -12003,13 +12003,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12129,13 +12129,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>261</v>
+        <v>146</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12255,13 +12255,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>144</v>
+        <v>322</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>145</v>
+        <v>323</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>146</v>
+        <v>324</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12353,14 +12353,12 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>82</v>
       </c>
@@ -12381,13 +12379,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>324</v>
+        <v>92</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>325</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12438,19 +12436,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -12462,7 +12460,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -12479,10 +12477,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12493,7 +12491,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -12505,13 +12503,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12550,31 +12548,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -12586,7 +12584,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -12603,10 +12601,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12614,10 +12612,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -12629,22 +12627,24 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>82</v>
@@ -12674,31 +12674,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -12710,7 +12710,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -12730,7 +12730,7 @@
         <v>329</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12744,7 +12744,7 @@
         <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -12753,24 +12753,22 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>311</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>82</v>
@@ -12788,13 +12786,11 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -12812,25 +12808,25 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
@@ -12853,24 +12849,26 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -12879,13 +12877,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12912,11 +12910,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -12934,31 +12934,31 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -997,6 +997,12 @@
     <t>Patient.Patient.SelfIdentifiedGender,SPatient.SPatient.SelfIdentifiedGender</t>
   </si>
   <si>
+    <t>Patient.extension:us-core-genderIdentity</t>
+  </si>
+  <si>
+    <t>us-core-genderIdentity</t>
+  </si>
+  <si>
     <t>Patient.extension:us-core-ethnicity</t>
   </si>
   <si>
@@ -1054,12 +1060,6 @@
   </si>
   <si>
     <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode,Patient.Patient.ReligionIEN,SPatient.SPatient.ReligionIEN</t>
-  </si>
-  <si>
-    <t>Patient.extension:us-core-genderIdentity</t>
-  </si>
-  <si>
-    <t>us-core-genderIdentity</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -12003,13 +12003,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>260</v>
+        <v>136</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>261</v>
+        <v>137</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12129,13 +12129,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>144</v>
+        <v>259</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>145</v>
+        <v>260</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>146</v>
+        <v>261</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12255,13 +12255,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>323</v>
+        <v>145</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>324</v>
+        <v>146</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12353,12 +12353,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>82</v>
       </c>
@@ -12379,13 +12381,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>92</v>
+        <v>324</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>325</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>326</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12436,19 +12438,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -12460,7 +12462,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -12477,10 +12479,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12491,7 +12493,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -12503,13 +12505,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12548,31 +12550,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -12584,7 +12586,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -12601,10 +12603,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12612,10 +12614,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -12627,24 +12629,22 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>82</v>
@@ -12674,31 +12674,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -12710,7 +12710,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -12730,7 +12730,7 @@
         <v>329</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12744,7 +12744,7 @@
         <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -12753,22 +12753,24 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>311</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>82</v>
@@ -12786,11 +12788,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -12808,25 +12812,25 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
@@ -12849,26 +12853,24 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -12877,13 +12879,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>137</v>
+        <v>332</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12910,13 +12912,11 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -12934,31 +12934,31 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8377" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8377" uniqueCount="953">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1311,9 +1311,6 @@
   </si>
   <si>
     <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.mechanism</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -3317,7 +3314,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.34765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -15359,19 +15356,19 @@
         <v>419</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>82</v>
@@ -15379,10 +15376,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15405,13 +15402,13 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -15462,7 +15459,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -15486,16 +15483,16 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>82</v>
@@ -15503,10 +15500,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15529,16 +15526,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15588,7 +15585,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -15612,16 +15609,16 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>82</v>
@@ -15629,10 +15626,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15658,23 +15655,23 @@
         <v>226</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="O99" t="s" s="2">
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="P99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q99" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="R99" t="s" s="2">
         <v>82</v>
       </c>
@@ -15718,7 +15715,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -15742,13 +15739,13 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>82</v>
@@ -15759,10 +15756,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15785,19 +15782,19 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15846,7 +15843,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15870,16 +15867,16 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AO100" t="s" s="2">
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15887,10 +15884,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16011,10 +16008,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16137,10 +16134,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16166,16 +16163,16 @@
         <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -16203,28 +16200,28 @@
         <v>181</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -16248,16 +16245,16 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16265,10 +16262,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16294,16 +16291,16 @@
         <v>150</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -16352,7 +16349,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16367,25 +16364,25 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL104" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL104" t="s" s="2">
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AM104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ104" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16393,14 +16390,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -16422,13 +16419,13 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -16439,79 +16436,79 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI105" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>82</v>
@@ -16519,14 +16516,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16548,13 +16545,13 @@
         <v>150</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -16565,46 +16562,46 @@
         <v>82</v>
       </c>
       <c r="S106" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16613,31 +16610,31 @@
         <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16645,10 +16642,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16674,10 +16671,10 @@
         <v>150</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16728,7 +16725,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16752,16 +16749,16 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16769,10 +16766,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16798,10 +16795,10 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16813,46 +16810,46 @@
         <v>82</v>
       </c>
       <c r="S108" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -16867,25 +16864,25 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>82</v>
@@ -16893,10 +16890,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16919,17 +16916,17 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -16978,7 +16975,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -17002,16 +16999,16 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>82</v>
@@ -17019,10 +17016,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17045,19 +17042,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -17094,7 +17091,7 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
@@ -17104,7 +17101,7 @@
         <v>139</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -17128,16 +17125,16 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO110" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AO110" t="s" s="2">
+      <c r="AP110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>82</v>
@@ -17145,10 +17142,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17269,10 +17266,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17395,10 +17392,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17424,10 +17421,10 @@
         <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17457,37 +17454,37 @@
         <v>181</v>
       </c>
       <c r="Y113" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z113" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z113" t="s" s="2">
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>102</v>
@@ -17502,16 +17499,16 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ113" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>82</v>
@@ -17519,10 +17516,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17548,16 +17545,16 @@
         <v>150</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -17606,7 +17603,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17630,16 +17627,16 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ114" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>82</v>
@@ -17647,10 +17644,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17676,16 +17673,16 @@
         <v>110</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17714,25 +17711,25 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17756,7 +17753,7 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -17765,7 +17762,7 @@
         <v>82</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17773,10 +17770,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17799,16 +17796,16 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17858,7 +17855,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -17899,10 +17896,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17925,13 +17922,13 @@
         <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17982,7 +17979,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -18006,7 +18003,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -18023,13 +18020,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -18051,19 +18048,19 @@
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -18112,7 +18109,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -18136,16 +18133,16 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO118" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AO118" t="s" s="2">
+      <c r="AP118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -18153,10 +18150,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18277,10 +18274,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18403,10 +18400,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18432,10 +18429,10 @@
         <v>110</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18447,7 +18444,7 @@
         <v>82</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>82</v>
@@ -18465,43 +18462,43 @@
         <v>181</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z121" t="s" s="2">
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
+      <c r="AG121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
@@ -18510,16 +18507,16 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>82</v>
@@ -18527,10 +18524,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18556,16 +18553,16 @@
         <v>150</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -18614,7 +18611,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -18629,7 +18626,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>82</v>
@@ -18638,16 +18635,16 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>82</v>
@@ -18655,10 +18652,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18684,16 +18681,16 @@
         <v>110</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -18703,7 +18700,7 @@
         <v>82</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>82</v>
@@ -18722,25 +18719,25 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -18755,7 +18752,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>82</v>
@@ -18764,7 +18761,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -18773,7 +18770,7 @@
         <v>82</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>82</v>
@@ -18781,10 +18778,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18807,16 +18804,16 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -18866,7 +18863,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -18907,10 +18904,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18933,13 +18930,13 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -18990,7 +18987,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -19014,7 +19011,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -19031,13 +19028,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C126" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>82</v>
@@ -19059,19 +19056,19 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -19120,7 +19117,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -19144,16 +19141,16 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AO126" t="s" s="2">
+      <c r="AP126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -19161,10 +19158,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19285,10 +19282,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19411,10 +19408,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19440,10 +19437,10 @@
         <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -19455,7 +19452,7 @@
         <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>82</v>
@@ -19473,43 +19470,43 @@
         <v>181</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z129" t="s" s="2">
+      <c r="AA129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AA129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF129" t="s" s="2">
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI129" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -19518,16 +19515,16 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ129" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ129" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>82</v>
@@ -19535,10 +19532,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19564,16 +19561,16 @@
         <v>150</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -19622,7 +19619,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19637,7 +19634,7 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>82</v>
@@ -19646,16 +19643,16 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ130" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ130" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>82</v>
@@ -19663,10 +19660,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19692,16 +19689,16 @@
         <v>110</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -19711,7 +19708,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -19730,25 +19727,25 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19763,7 +19760,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>82</v>
@@ -19772,7 +19769,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -19781,7 +19778,7 @@
         <v>82</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19789,10 +19786,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19815,16 +19812,16 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19874,7 +19871,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19915,10 +19912,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19941,13 +19938,13 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19998,7 +19995,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -20022,7 +20019,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -20039,13 +20036,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C134" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>82</v>
@@ -20067,19 +20064,19 @@
         <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -20128,7 +20125,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -20152,16 +20149,16 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AO134" t="s" s="2">
+      <c r="AP134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ134" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>82</v>
@@ -20169,10 +20166,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20293,10 +20290,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20419,10 +20416,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20448,10 +20445,10 @@
         <v>110</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -20463,7 +20460,7 @@
         <v>82</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>82</v>
@@ -20481,43 +20478,43 @@
         <v>181</v>
       </c>
       <c r="Y137" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z137" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z137" t="s" s="2">
+      <c r="AA137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF137" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AA137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF137" t="s" s="2">
+      <c r="AG137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI137" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -20526,16 +20523,16 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ137" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>82</v>
@@ -20543,10 +20540,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20572,16 +20569,16 @@
         <v>150</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="N138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -20630,7 +20627,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20645,7 +20642,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -20654,16 +20651,16 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ138" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ138" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>82</v>
@@ -20671,10 +20668,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20700,16 +20697,16 @@
         <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20719,7 +20716,7 @@
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -20738,25 +20735,25 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20771,7 +20768,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -20780,7 +20777,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -20789,7 +20786,7 @@
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20797,10 +20794,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20823,16 +20820,16 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -20882,7 +20879,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20923,10 +20920,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20949,13 +20946,13 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -21006,7 +21003,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -21030,7 +21027,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -21047,10 +21044,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21076,16 +21073,16 @@
         <v>110</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -21114,7 +21111,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -21132,7 +21129,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -21147,10 +21144,10 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AL142" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>82</v>
@@ -21159,13 +21156,13 @@
         <v>302</v>
       </c>
       <c r="AO142" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AP142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ142" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ142" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -21173,10 +21170,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21199,19 +21196,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21260,7 +21257,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21275,36 +21272,36 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AL143" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="AL143" t="s" s="2">
+      <c r="AM143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AM143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN143" t="s" s="2">
+      <c r="AO143" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="AO143" t="s" s="2">
+      <c r="AP143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ143" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AP143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ143" t="s" s="2">
+      <c r="AR143" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AR143" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21327,19 +21324,19 @@
         <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L144" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L144" t="s" s="2">
+      <c r="M144" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -21376,7 +21373,7 @@
         <v>82</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -21386,7 +21383,7 @@
         <v>139</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -21410,7 +21407,7 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>154</v>
@@ -21419,7 +21416,7 @@
         <v>82</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>82</v>
@@ -21427,13 +21424,13 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C145" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>82</v>
@@ -21455,19 +21452,19 @@
         <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -21516,7 +21513,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -21531,16 +21528,16 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL145" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AL145" t="s" s="2">
-        <v>641</v>
-      </c>
       <c r="AM145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>154</v>
@@ -21549,7 +21546,7 @@
         <v>82</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>82</v>
@@ -21557,10 +21554,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21583,19 +21580,19 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21632,7 +21629,7 @@
         <v>82</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC146" s="2"/>
       <c r="AD146" t="s" s="2">
@@ -21642,7 +21639,7 @@
         <v>139</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21666,16 +21663,16 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AO146" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AO146" t="s" s="2">
+      <c r="AP146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21683,10 +21680,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21807,10 +21804,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21933,10 +21930,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21962,16 +21959,16 @@
         <v>110</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -21984,7 +21981,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -21999,28 +21996,28 @@
         <v>181</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="Z149" t="s" s="2">
+      <c r="AA149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF149" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22044,7 +22041,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22053,7 +22050,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22061,10 +22058,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22090,13 +22087,13 @@
         <v>110</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -22110,7 +22107,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22125,28 +22122,28 @@
         <v>181</v>
       </c>
       <c r="Y150" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z150" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z150" t="s" s="2">
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22170,7 +22167,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22179,7 +22176,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22187,10 +22184,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22216,16 +22213,16 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="N151" t="s" s="2">
-        <v>674</v>
-      </c>
       <c r="O151" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -22238,43 +22235,43 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22298,7 +22295,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22307,7 +22304,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22315,10 +22312,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22344,10 +22341,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22362,43 +22359,43 @@
         <v>82</v>
       </c>
       <c r="T152" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF152" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22422,16 +22419,16 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ152" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ152" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22439,14 +22436,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22468,10 +22465,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22486,43 +22483,43 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF153" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22546,16 +22543,16 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ153" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ153" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22563,14 +22560,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -22592,13 +22589,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22612,43 +22609,43 @@
         <v>82</v>
       </c>
       <c r="T154" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF154" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22672,16 +22669,16 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ154" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP154" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ154" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22689,14 +22686,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -22718,10 +22715,10 @@
         <v>150</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -22751,28 +22748,28 @@
         <v>367</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="Z155" t="s" s="2">
+      <c r="AA155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF155" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22796,16 +22793,16 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ155" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ155" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22813,14 +22810,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -22842,10 +22839,10 @@
         <v>150</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -22860,43 +22857,43 @@
         <v>82</v>
       </c>
       <c r="T156" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF156" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22920,16 +22917,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ156" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ156" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22937,10 +22934,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22966,13 +22963,13 @@
         <v>150</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -23022,7 +23019,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -23046,16 +23043,16 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ157" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ157" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>82</v>
@@ -23063,10 +23060,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23089,17 +23086,17 @@
         <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -23112,43 +23109,43 @@
         <v>82</v>
       </c>
       <c r="T158" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -23172,7 +23169,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -23181,7 +23178,7 @@
         <v>82</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>82</v>
@@ -23189,13 +23186,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>82</v>
@@ -23217,19 +23214,19 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23278,7 +23275,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23302,16 +23299,16 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AO159" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AO159" t="s" s="2">
+      <c r="AP159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ159" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AP159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ159" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23319,10 +23316,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23443,10 +23440,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23569,10 +23566,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23598,16 +23595,16 @@
         <v>110</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -23617,10 +23614,10 @@
         <v>82</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23635,28 +23632,28 @@
         <v>181</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="Z162" t="s" s="2">
+      <c r="AA162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF162" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23671,7 +23668,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>82</v>
@@ -23680,7 +23677,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23689,7 +23686,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23697,10 +23694,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23726,13 +23723,13 @@
         <v>110</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23743,10 +23740,10 @@
         <v>82</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23761,28 +23758,28 @@
         <v>181</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z163" t="s" s="2">
+      <c r="AA163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF163" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23797,7 +23794,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>82</v>
@@ -23806,7 +23803,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23815,7 +23812,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23823,10 +23820,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23852,16 +23849,16 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="N164" t="s" s="2">
-        <v>674</v>
-      </c>
       <c r="O164" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -23874,43 +23871,43 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF164" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23934,7 +23931,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23943,7 +23940,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -23951,10 +23948,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23980,10 +23977,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -23998,43 +23995,43 @@
         <v>82</v>
       </c>
       <c r="T165" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24049,25 +24046,25 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AL165" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="AL165" t="s" s="2">
-        <v>744</v>
-      </c>
       <c r="AM165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ165" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ165" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24075,14 +24072,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24104,10 +24101,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24122,43 +24119,43 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF166" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="U166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24173,25 +24170,25 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AL166" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="AL166" t="s" s="2">
-        <v>747</v>
-      </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ166" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ166" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24199,14 +24196,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -24228,13 +24225,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24248,43 +24245,43 @@
         <v>82</v>
       </c>
       <c r="T167" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF167" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="U167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24308,16 +24305,16 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ167" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ167" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24325,14 +24322,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -24354,10 +24351,10 @@
         <v>150</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24387,28 +24384,28 @@
         <v>367</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="Z168" t="s" s="2">
+      <c r="AA168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF168" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24423,25 +24420,25 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AL168" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="AL168" t="s" s="2">
-        <v>751</v>
-      </c>
       <c r="AM168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ168" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ168" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24449,14 +24446,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24478,10 +24475,10 @@
         <v>150</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -24496,43 +24493,43 @@
         <v>82</v>
       </c>
       <c r="T169" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF169" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -24547,25 +24544,25 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AL169" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="AL169" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="AM169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ169" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ169" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="AR169" t="s" s="2">
         <v>82</v>
@@ -24573,10 +24570,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24602,13 +24599,13 @@
         <v>150</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24658,7 +24655,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -24673,7 +24670,7 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>82</v>
@@ -24682,16 +24679,16 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ170" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>82</v>
@@ -24699,10 +24696,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24725,17 +24722,17 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -24748,43 +24745,43 @@
         <v>82</v>
       </c>
       <c r="T171" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF171" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24808,7 +24805,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -24817,7 +24814,7 @@
         <v>82</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24825,10 +24822,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B172" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24949,10 +24946,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25075,10 +25072,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25101,16 +25098,16 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -25160,40 +25157,40 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI174" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH174" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI174" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN174" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="AL174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN174" t="s" s="2">
+      <c r="AO174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ174" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ174" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25201,10 +25198,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25227,69 +25224,69 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q175" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="R175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF175" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="R175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>778</v>
-      </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
@@ -25297,31 +25294,31 @@
         <v>90</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN175" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="AL175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN175" t="s" s="2">
+      <c r="AO175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ175" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ175" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25329,10 +25326,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25358,14 +25355,14 @@
         <v>311</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25394,7 +25391,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -25412,7 +25409,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25427,25 +25424,25 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AL176" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AL176" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="AM176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN176" t="s" s="2">
+      <c r="AO176" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="AO176" t="s" s="2">
+      <c r="AP176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ176" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="AP176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ176" t="s" s="2">
-        <v>791</v>
       </c>
       <c r="AR176" t="s" s="2">
         <v>82</v>
@@ -25453,10 +25450,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25479,19 +25476,19 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="M177" t="s" s="2">
         <v>794</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>797</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -25540,7 +25537,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -25564,7 +25561,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>154</v>
@@ -25573,7 +25570,7 @@
         <v>82</v>
       </c>
       <c r="AQ177" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AR177" t="s" s="2">
         <v>82</v>
@@ -25581,10 +25578,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25607,19 +25604,19 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>802</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -25668,7 +25665,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -25692,7 +25689,7 @@
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>154</v>
@@ -25701,7 +25698,7 @@
         <v>82</v>
       </c>
       <c r="AQ178" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AR178" t="s" s="2">
         <v>82</v>
@@ -25709,10 +25706,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25735,19 +25732,19 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>811</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -25796,7 +25793,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25808,19 +25805,19 @@
         <v>82</v>
       </c>
       <c r="AJ179" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN179" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>154</v>
@@ -25837,10 +25834,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25961,10 +25958,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26087,14 +26084,14 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -26116,10 +26113,10 @@
         <v>135</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="N182" t="s" s="2">
         <v>160</v>
@@ -26174,7 +26171,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26215,10 +26212,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26244,14 +26241,14 @@
         <v>311</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26279,11 +26276,11 @@
         <v>367</v>
       </c>
       <c r="Y183" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="Z183" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="Z183" t="s" s="2">
-        <v>828</v>
-      </c>
       <c r="AA183" t="s" s="2">
         <v>82</v>
       </c>
@@ -26300,7 +26297,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26324,7 +26321,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26333,7 +26330,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26341,10 +26338,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26367,17 +26364,17 @@
         <v>82</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26426,7 +26423,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26450,7 +26447,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>154</v>
@@ -26459,7 +26456,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26467,10 +26464,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26493,19 +26490,19 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="N185" t="s" s="2">
-        <v>839</v>
-      </c>
       <c r="O185" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26554,7 +26551,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26578,7 +26575,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26587,7 +26584,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26595,10 +26592,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26621,17 +26618,17 @@
         <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
@@ -26680,7 +26677,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26704,7 +26701,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26713,7 +26710,7 @@
         <v>82</v>
       </c>
       <c r="AQ186" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AR186" t="s" s="2">
         <v>82</v>
@@ -26721,10 +26718,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26750,14 +26747,14 @@
         <v>110</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26785,11 +26782,11 @@
         <v>181</v>
       </c>
       <c r="Y187" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="Z187" t="s" s="2">
         <v>849</v>
       </c>
-      <c r="Z187" t="s" s="2">
-        <v>850</v>
-      </c>
       <c r="AA187" t="s" s="2">
         <v>82</v>
       </c>
@@ -26806,7 +26803,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26839,7 +26836,7 @@
         <v>82</v>
       </c>
       <c r="AQ187" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AR187" t="s" s="2">
         <v>82</v>
@@ -26847,10 +26844,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26873,17 +26870,17 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>853</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>854</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -26932,7 +26929,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -26941,7 +26938,7 @@
         <v>90</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>102</v>
@@ -26956,7 +26953,7 @@
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>154</v>
@@ -26965,7 +26962,7 @@
         <v>82</v>
       </c>
       <c r="AQ188" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AR188" t="s" s="2">
         <v>82</v>
@@ -26973,10 +26970,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26999,13 +26996,13 @@
         <v>82</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L189" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="M189" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -27056,7 +27053,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -27080,7 +27077,7 @@
         <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>154</v>
@@ -27097,10 +27094,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -27123,19 +27120,19 @@
         <v>82</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="M190" t="s" s="2">
         <v>864</v>
       </c>
-      <c r="M190" t="s" s="2">
+      <c r="N190" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="N190" t="s" s="2">
+      <c r="O190" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -27184,7 +27181,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27208,10 +27205,10 @@
         <v>82</v>
       </c>
       <c r="AN190" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="AO190" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>82</v>
@@ -27225,10 +27222,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27349,10 +27346,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27475,14 +27472,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27504,10 +27501,10 @@
         <v>135</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>160</v>
@@ -27562,7 +27559,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27603,10 +27600,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27632,16 +27629,16 @@
         <v>311</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>875</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27670,7 +27667,7 @@
       </c>
       <c r="Y194" s="2"/>
       <c r="Z194" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -27688,7 +27685,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>90</v>
@@ -27703,25 +27700,25 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="AL194" t="s" s="2">
         <v>879</v>
       </c>
-      <c r="AL194" t="s" s="2">
+      <c r="AM194" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="AN194" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="AM194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN194" t="s" s="2">
+      <c r="AO194" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="AO194" t="s" s="2">
+      <c r="AP194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ194" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="AP194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ194" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="AR194" t="s" s="2">
         <v>82</v>
@@ -27729,10 +27726,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27758,16 +27755,16 @@
         <v>226</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>885</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>886</v>
       </c>
-      <c r="N195" t="s" s="2">
+      <c r="O195" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>82</v>
@@ -27816,7 +27813,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -27840,16 +27837,16 @@
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AO195" t="s" s="2">
         <v>889</v>
       </c>
-      <c r="AO195" t="s" s="2">
+      <c r="AP195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ195" t="s" s="2">
         <v>890</v>
-      </c>
-      <c r="AP195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ195" t="s" s="2">
-        <v>891</v>
       </c>
       <c r="AR195" t="s" s="2">
         <v>82</v>
@@ -27857,14 +27854,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -27883,16 +27880,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>894</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>895</v>
       </c>
-      <c r="M196" t="s" s="2">
+      <c r="N196" t="s" s="2">
         <v>896</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>897</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -27942,7 +27939,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -27966,7 +27963,7 @@
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>154</v>
@@ -27975,7 +27972,7 @@
         <v>82</v>
       </c>
       <c r="AQ196" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="AR196" t="s" s="2">
         <v>82</v>
@@ -27983,10 +27980,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28009,19 +28006,19 @@
         <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>901</v>
       </c>
-      <c r="M197" t="s" s="2">
+      <c r="N197" t="s" s="2">
         <v>902</v>
       </c>
-      <c r="N197" t="s" s="2">
+      <c r="O197" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>82</v>
@@ -28070,7 +28067,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28094,10 +28091,10 @@
         <v>82</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>82</v>
@@ -28111,10 +28108,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28235,10 +28232,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28361,10 +28358,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28390,13 +28387,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>909</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>910</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>911</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28446,16 +28443,16 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="AG200" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH200" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI200" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>102</v>
@@ -28487,10 +28484,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28516,13 +28513,13 @@
         <v>104</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="M201" t="s" s="2">
         <v>915</v>
       </c>
-      <c r="M201" t="s" s="2">
+      <c r="N201" t="s" s="2">
         <v>916</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>917</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -28551,28 +28548,28 @@
         <v>367</v>
       </c>
       <c r="Y201" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="Z201" t="s" s="2">
         <v>918</v>
       </c>
-      <c r="Z201" t="s" s="2">
+      <c r="AA201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF201" t="s" s="2">
         <v>919</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>920</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28613,10 +28610,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28642,13 +28639,13 @@
         <v>343</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>922</v>
       </c>
-      <c r="M202" t="s" s="2">
+      <c r="N202" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>924</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -28698,7 +28695,7 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -28722,7 +28719,7 @@
         <v>82</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>82</v>
@@ -28739,10 +28736,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28768,13 +28765,13 @@
         <v>150</v>
       </c>
       <c r="L203" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="M203" t="s" s="2">
         <v>928</v>
       </c>
-      <c r="M203" t="s" s="2">
+      <c r="N203" t="s" s="2">
         <v>929</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>930</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -28785,46 +28782,46 @@
         <v>82</v>
       </c>
       <c r="S203" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="T203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF203" t="s" s="2">
         <v>931</v>
-      </c>
-      <c r="T203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF203" t="s" s="2">
-        <v>932</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -28839,7 +28836,7 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>82</v>
@@ -28865,10 +28862,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28891,19 +28888,19 @@
         <v>91</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L204" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="M204" t="s" s="2">
         <v>935</v>
       </c>
-      <c r="M204" t="s" s="2">
+      <c r="N204" t="s" s="2">
         <v>936</v>
       </c>
-      <c r="N204" t="s" s="2">
+      <c r="O204" t="s" s="2">
         <v>937</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>938</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>82</v>
@@ -28952,7 +28949,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -28976,7 +28973,7 @@
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>154</v>
@@ -28993,10 +28990,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29117,10 +29114,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29243,14 +29240,14 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
@@ -29272,10 +29269,10 @@
         <v>135</v>
       </c>
       <c r="L207" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M207" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="N207" t="s" s="2">
         <v>160</v>
@@ -29330,7 +29327,7 @@
         <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -29371,10 +29368,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -29397,16 +29394,16 @@
         <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
+        <v>943</v>
+      </c>
+      <c r="L208" t="s" s="2">
         <v>944</v>
       </c>
-      <c r="L208" t="s" s="2">
+      <c r="M208" t="s" s="2">
         <v>945</v>
       </c>
-      <c r="M208" t="s" s="2">
+      <c r="N208" t="s" s="2">
         <v>946</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>947</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -29456,7 +29453,7 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>90</v>
@@ -29489,7 +29486,7 @@
         <v>82</v>
       </c>
       <c r="AQ208" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="AR208" t="s" s="2">
         <v>82</v>
@@ -29497,10 +29494,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -29526,10 +29523,10 @@
         <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>950</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>951</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -29559,11 +29556,11 @@
         <v>181</v>
       </c>
       <c r="Y209" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="Z209" t="s" s="2">
         <v>951</v>
       </c>
-      <c r="Z209" t="s" s="2">
-        <v>952</v>
-      </c>
       <c r="AA209" t="s" s="2">
         <v>82</v>
       </c>
@@ -29580,7 +29577,7 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>90</v>
@@ -29604,7 +29601,7 @@
         <v>82</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,7 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory</t>
+    <t>http://va.gov/fhir/ValueSet/raceCategory</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -871,7 +871,7 @@
     <t>Patient.extension:ethnicity.extension:ombCategory.value[x].code</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory</t>
+    <t>http://va.gov/fhir/ValueSet/ethnicityCategory</t>
   </si>
   <si>
     <t>575: terminologyMaps using VF_ethnicityCategory on PATIENT - ETHNICITY INFORMATION (2-6)</t>
@@ -988,7 +988,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity</t>
+    <t>http://va.gov/fhir/ValueSet/genderIdentity</t>
   </si>
   <si>
     <t>1808: terminologyMaps using VF_genderIdentity on PATIENT - SELF IDENTIFIED GENDER (2-.024)</t>
@@ -1031,7 +1031,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFReligion</t>
+    <t>http://va.gov/fhir/ValueSet/Religion</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -1881,7 +1881,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFadminGender</t>
+    <t>http://va.gov/fhir/ValueSet/adminGender</t>
   </si>
   <si>
     <t>555: terminologyMaps using VF_adminGender on PATIENT - SEX (2-.02)</t>
@@ -2419,7 +2419,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus</t>
+    <t>http://va.gov/fhir/ValueSet/MaritalStatus</t>
   </si>
   <si>
     <t>1597: terminologyMaps using VF_MaritalStatus on PATIENT - MARITAL STATUS (2-.05)</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="959">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -685,6 +685,9 @@
     <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (2-2)</t>
   </si>
   <si>
+    <t>demographics.race [m-P:10]</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -877,6 +880,9 @@
     <t>575: terminologyMaps using VF_ethnicityCategory on PATIENT - ETHNICITY INFORMATION (2-6)</t>
   </si>
   <si>
+    <t>demographics.ethnicity [m-P:10.2]</t>
+  </si>
+  <si>
     <t>Patient.extension:ethnicity.extension:ombCategory.value[x].display</t>
   </si>
   <si>
@@ -1044,6 +1050,9 @@
     <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode,Patient.Patient.ReligionIEN,SPatient.SPatient.ReligionIEN</t>
   </si>
   <si>
+    <t>demographics.religion</t>
+  </si>
+  <si>
     <t>Patient.modifierExtension</t>
   </si>
   <si>
@@ -1295,7 +1304,7 @@
     <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.mechanism</t>
+    <t>demographics.icn</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -1466,6 +1475,9 @@
     <t>SPatient.SPatient.DestinationMergePatientIEN,SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
   </si>
   <si>
+    <t>demographics.familyName,demographics.fullName,demographics.givenNames</t>
+  </si>
+  <si>
     <t>./formatted</t>
   </si>
   <si>
@@ -1812,6 +1824,9 @@
     <t>275: source value from PATIENT - PHONE NUMBER [WORK] (2-.132)</t>
   </si>
   <si>
+    <t>demographics.telecom</t>
+  </si>
+  <si>
     <t>Patient.telecom:va-work.use</t>
   </si>
   <si>
@@ -1888,6 +1903,9 @@
   </si>
   <si>
     <t>Patient.Patient.Gender,Patient.PatientBirthSex.BirthSex,SPatient.SPatient.Gender,SPatient.SPatientBirthSex.BirthSex,SPatient.SPatientBirthSex.BirthSex</t>
+  </si>
+  <si>
+    <t>demographics.gender</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1921,6 +1939,9 @@
     <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
+    <t>demographics.dob</t>
+  </si>
+  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
   </si>
   <si>
@@ -1976,6 +1997,9 @@
   </si>
   <si>
     <t>Patient.Patient.DeathDateTime,SPatient.SPatient.DeathDateTime</t>
+  </si>
+  <si>
+    <t>demographics.died</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2325,6 +2349,9 @@
     <t>SPatient.SPatientGISAddress.Zip4</t>
   </si>
   <si>
+    <t>demographics.address</t>
+  </si>
+  <si>
     <t>Patient.address:va-home.country</t>
   </si>
   <si>
@@ -2426,6 +2453,9 @@
   </si>
   <si>
     <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus,Patient.Patient.MaritalStatusIEN,SPatient.SPatient.MaritalStatusIEN</t>
+  </si>
+  <si>
+    <t>demographics.maritalStatus</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -2712,6 +2742,9 @@
   </si>
   <si>
     <t>Patient.PreferredLanguage.PreferredLanguage</t>
+  </si>
+  <si>
+    <t>demographics.language</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -3299,7 +3332,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.34765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="73.78515625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6053,10 +6086,10 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -6065,7 +6098,7 @@
         <v>82</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>82</v>
@@ -6073,10 +6106,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -6102,14 +6135,14 @@
         <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -6158,7 +6191,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -6182,7 +6215,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -6191,7 +6224,7 @@
         <v>82</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>82</v>
@@ -6199,10 +6232,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6225,19 +6258,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -6286,7 +6319,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -6310,7 +6343,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -6319,7 +6352,7 @@
         <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>82</v>
@@ -6327,13 +6360,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
@@ -6358,10 +6391,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -6453,7 +6486,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>167</v>
@@ -6577,7 +6610,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>169</v>
@@ -6703,7 +6736,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>171</v>
@@ -6746,7 +6779,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -6829,7 +6862,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>177</v>
@@ -6892,7 +6925,7 @@
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -6951,13 +6984,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -6982,10 +7015,10 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -7077,7 +7110,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>167</v>
@@ -7201,7 +7234,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>169</v>
@@ -7327,7 +7360,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>171</v>
@@ -7370,7 +7403,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -7453,7 +7486,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>177</v>
@@ -7577,10 +7610,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7620,7 +7653,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -7703,10 +7736,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7729,7 +7762,7 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>179</v>
@@ -7827,13 +7860,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
@@ -7855,13 +7888,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7953,7 +7986,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>149</v>
@@ -8077,7 +8110,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>156</v>
@@ -8203,7 +8236,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>156</v>
@@ -8329,7 +8362,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>167</v>
@@ -8453,7 +8486,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>169</v>
@@ -8577,7 +8610,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>171</v>
@@ -8703,7 +8736,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>177</v>
@@ -8766,7 +8799,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -8825,7 +8858,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>186</v>
@@ -8949,7 +8982,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>188</v>
@@ -9075,7 +9108,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>190</v>
@@ -9203,7 +9236,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>199</v>
@@ -9329,7 +9362,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>207</v>
@@ -9394,7 +9427,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9427,16 +9460,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -9445,7 +9478,7 @@
         <v>82</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>82</v>
@@ -9453,10 +9486,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9482,14 +9515,14 @@
         <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9538,7 +9571,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -9562,7 +9595,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -9571,7 +9604,7 @@
         <v>82</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>82</v>
@@ -9579,10 +9612,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9605,19 +9638,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9666,7 +9699,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9690,7 +9723,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -9699,7 +9732,7 @@
         <v>82</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>82</v>
@@ -9707,13 +9740,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
@@ -9738,10 +9771,10 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9833,7 +9866,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -9957,7 +9990,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>169</v>
@@ -10083,7 +10116,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>171</v>
@@ -10126,7 +10159,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -10209,7 +10242,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>177</v>
@@ -10272,7 +10305,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -10331,13 +10364,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
@@ -10362,10 +10395,10 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10457,7 +10490,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>167</v>
@@ -10581,7 +10614,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>169</v>
@@ -10707,7 +10740,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>171</v>
@@ -10750,7 +10783,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>82</v>
@@ -10833,7 +10866,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>177</v>
@@ -10957,10 +10990,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11000,7 +11033,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>82</v>
@@ -11083,10 +11116,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11109,7 +11142,7 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>179</v>
@@ -11207,13 +11240,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>82</v>
@@ -11235,16 +11268,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -11318,7 +11351,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -11335,13 +11368,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -11363,7 +11396,7 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>136</v>
@@ -11461,7 +11494,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>149</v>
@@ -11585,7 +11618,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>156</v>
@@ -11709,10 +11742,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11752,7 +11785,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -11835,10 +11868,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11861,13 +11894,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11898,7 +11931,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11931,10 +11964,10 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -11957,13 +11990,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>82</v>
@@ -11985,13 +12018,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12083,7 +12116,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>149</v>
@@ -12207,7 +12240,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>156</v>
@@ -12331,10 +12364,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12374,7 +12407,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>82</v>
@@ -12457,10 +12490,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12483,13 +12516,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12520,7 +12553,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -12547,19 +12580,19 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>133</v>
@@ -12579,10 +12612,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12608,16 +12641,16 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -12666,7 +12699,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -12707,10 +12740,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12733,17 +12766,17 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -12792,7 +12825,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12816,16 +12849,16 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>82</v>
@@ -12833,10 +12866,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12957,10 +12990,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13083,10 +13116,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13112,16 +13145,16 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -13149,10 +13182,10 @@
         <v>181</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -13170,7 +13203,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -13194,7 +13227,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -13211,10 +13244,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13237,19 +13270,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13274,13 +13307,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -13298,7 +13331,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -13322,7 +13355,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -13331,7 +13364,7 @@
         <v>82</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>82</v>
@@ -13339,10 +13372,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13463,10 +13496,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13589,10 +13622,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13618,16 +13651,16 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -13676,7 +13709,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -13700,7 +13733,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -13709,7 +13742,7 @@
         <v>82</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>82</v>
@@ -13717,10 +13750,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13841,10 +13874,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13967,10 +14000,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14015,7 +14048,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -14069,7 +14102,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -14095,10 +14128,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14221,10 +14254,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14267,7 +14300,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -14321,7 +14354,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -14330,7 +14363,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -14339,7 +14372,7 @@
         <v>82</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>82</v>
@@ -14347,10 +14380,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14376,14 +14409,14 @@
         <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -14432,7 +14465,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -14456,7 +14489,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -14465,7 +14498,7 @@
         <v>82</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>82</v>
@@ -14473,10 +14506,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14499,19 +14532,19 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -14560,7 +14593,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -14584,7 +14617,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -14593,7 +14626,7 @@
         <v>82</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>82</v>
@@ -14601,10 +14634,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14630,16 +14663,16 @@
         <v>150</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14688,7 +14721,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -14712,7 +14745,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -14721,7 +14754,7 @@
         <v>82</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>82</v>
@@ -14729,10 +14762,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14758,16 +14791,16 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -14777,10 +14810,10 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>82</v>
@@ -14816,7 +14849,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14831,7 +14864,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -14840,7 +14873,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -14849,7 +14882,7 @@
         <v>82</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>82</v>
@@ -14857,10 +14890,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14886,13 +14919,13 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14906,7 +14939,7 @@
         <v>82</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>82</v>
@@ -14942,7 +14975,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14957,16 +14990,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -14975,7 +15008,7 @@
         <v>82</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -14983,10 +15016,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15009,13 +15042,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -15066,7 +15099,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -15090,7 +15123,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -15099,7 +15132,7 @@
         <v>82</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -15107,10 +15140,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15133,16 +15166,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15192,7 +15225,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -15216,7 +15249,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -15225,7 +15258,7 @@
         <v>82</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -15233,10 +15266,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15259,70 +15292,70 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N96" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -15346,13 +15379,13 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>82</v>
@@ -15363,10 +15396,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15389,19 +15422,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15450,7 +15483,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -15474,16 +15507,16 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>82</v>
@@ -15491,10 +15524,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15615,10 +15648,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15741,10 +15774,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15770,16 +15803,16 @@
         <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15807,10 +15840,10 @@
         <v>181</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -15828,7 +15861,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15852,7 +15885,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -15861,7 +15894,7 @@
         <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15869,10 +15902,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15898,16 +15931,16 @@
         <v>150</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15956,7 +15989,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15971,16 +16004,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -15989,7 +16022,7 @@
         <v>82</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -15997,14 +16030,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16026,13 +16059,13 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -16043,7 +16076,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -16082,7 +16115,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -16091,13 +16124,13 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -16106,7 +16139,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -16115,7 +16148,7 @@
         <v>82</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>82</v>
@@ -16123,14 +16156,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -16152,13 +16185,13 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16169,7 +16202,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -16208,7 +16241,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -16217,13 +16250,13 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -16232,7 +16265,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -16241,7 +16274,7 @@
         <v>82</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16249,10 +16282,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16278,10 +16311,10 @@
         <v>150</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -16332,7 +16365,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16356,7 +16389,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -16365,7 +16398,7 @@
         <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16373,10 +16406,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16402,10 +16435,10 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -16417,7 +16450,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>82</v>
@@ -16456,7 +16489,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16471,7 +16504,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -16480,7 +16513,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -16489,7 +16522,7 @@
         <v>82</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>82</v>
@@ -16497,10 +16530,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16523,17 +16556,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16582,7 +16615,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16606,7 +16639,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -16615,7 +16648,7 @@
         <v>82</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16623,10 +16656,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16649,19 +16682,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16698,7 +16731,7 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -16708,7 +16741,7 @@
         <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16732,16 +16765,16 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16749,10 +16782,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16873,10 +16906,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16999,10 +17032,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17028,10 +17061,10 @@
         <v>110</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -17061,10 +17094,10 @@
         <v>181</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -17082,7 +17115,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -17091,7 +17124,7 @@
         <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
@@ -17106,7 +17139,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -17115,7 +17148,7 @@
         <v>82</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>82</v>
@@ -17123,10 +17156,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17152,16 +17185,16 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -17210,7 +17243,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -17234,7 +17267,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -17243,7 +17276,7 @@
         <v>82</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17251,10 +17284,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17280,16 +17313,16 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -17318,7 +17351,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -17336,7 +17369,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17360,7 +17393,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -17369,7 +17402,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17377,10 +17410,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17403,16 +17436,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -17462,7 +17495,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17503,10 +17536,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17529,13 +17562,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17586,7 +17619,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17610,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17627,13 +17660,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -17655,19 +17688,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17716,7 +17749,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17740,16 +17773,16 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17757,10 +17790,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17881,10 +17914,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18007,10 +18040,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18036,10 +18069,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -18051,7 +18084,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -18069,10 +18102,10 @@
         <v>181</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -18090,7 +18123,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -18099,13 +18132,13 @@
         <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -18114,7 +18147,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -18123,7 +18156,7 @@
         <v>82</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -18131,10 +18164,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18160,16 +18193,16 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -18218,7 +18251,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -18233,7 +18266,7 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -18242,7 +18275,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -18251,7 +18284,7 @@
         <v>82</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18259,10 +18292,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18288,16 +18321,16 @@
         <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18307,7 +18340,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -18326,7 +18359,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -18344,7 +18377,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18359,7 +18392,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -18368,7 +18401,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -18377,7 +18410,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18385,10 +18418,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18411,16 +18444,16 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -18470,7 +18503,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18511,10 +18544,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18537,13 +18570,13 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18594,7 +18627,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -18618,7 +18651,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -18635,13 +18668,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -18663,19 +18696,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -18724,7 +18757,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -18748,16 +18781,16 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>82</v>
@@ -18765,10 +18798,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18889,10 +18922,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19015,10 +19048,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19044,10 +19077,10 @@
         <v>110</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -19059,7 +19092,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -19077,10 +19110,10 @@
         <v>181</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -19098,7 +19131,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -19107,13 +19140,13 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -19122,7 +19155,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -19131,7 +19164,7 @@
         <v>82</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -19139,10 +19172,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19168,16 +19201,16 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -19226,7 +19259,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -19241,16 +19274,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -19259,7 +19292,7 @@
         <v>82</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19267,10 +19300,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19296,16 +19329,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -19315,7 +19348,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -19334,7 +19367,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -19352,7 +19385,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19367,7 +19400,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -19376,7 +19409,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19385,7 +19418,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19393,10 +19426,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19419,16 +19452,16 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19478,7 +19511,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19519,10 +19552,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19545,13 +19578,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19602,7 +19635,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19626,7 +19659,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19643,13 +19676,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>82</v>
@@ -19671,19 +19704,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -19732,7 +19765,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19756,16 +19789,16 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19773,10 +19806,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19897,10 +19930,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20023,10 +20056,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20052,10 +20085,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -20067,7 +20100,7 @@
         <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>82</v>
@@ -20085,10 +20118,10 @@
         <v>181</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>82</v>
@@ -20106,7 +20139,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -20115,13 +20148,13 @@
         <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -20130,7 +20163,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -20139,7 +20172,7 @@
         <v>82</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>82</v>
@@ -20147,10 +20180,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20176,16 +20209,16 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -20234,7 +20267,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -20249,7 +20282,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
@@ -20258,7 +20291,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -20267,7 +20300,7 @@
         <v>82</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AR135" t="s" s="2">
         <v>82</v>
@@ -20275,10 +20308,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20304,16 +20337,16 @@
         <v>110</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -20323,7 +20356,7 @@
         <v>82</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>82</v>
@@ -20342,7 +20375,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -20360,7 +20393,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20375,7 +20408,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20384,7 +20417,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20393,7 +20426,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20401,10 +20434,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20427,16 +20460,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -20486,7 +20519,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20527,10 +20560,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20553,13 +20586,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20610,7 +20643,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20634,7 +20667,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -20651,10 +20684,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20680,16 +20713,16 @@
         <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20718,25 +20751,25 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20751,25 +20784,25 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20777,10 +20810,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20803,19 +20836,19 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20864,7 +20897,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20879,36 +20912,36 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20931,19 +20964,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -20980,7 +21013,7 @@
         <v>82</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -20990,7 +21023,7 @@
         <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -21014,7 +21047,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -21023,7 +21056,7 @@
         <v>82</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>82</v>
@@ -21031,13 +21064,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -21059,19 +21092,19 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="L142" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="O142" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -21120,7 +21153,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -21135,16 +21168,16 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>154</v>
@@ -21153,7 +21186,7 @@
         <v>82</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -21161,10 +21194,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21187,19 +21220,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21236,7 +21269,7 @@
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -21246,7 +21279,7 @@
         <v>139</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21270,16 +21303,16 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21287,10 +21320,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21411,10 +21444,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21537,10 +21570,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21566,16 +21599,16 @@
         <v>110</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21588,7 +21621,7 @@
         <v>82</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>82</v>
@@ -21603,10 +21636,10 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -21624,7 +21657,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21648,7 +21681,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -21657,7 +21690,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21665,10 +21698,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21694,13 +21727,13 @@
         <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -21714,7 +21747,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21729,10 +21762,10 @@
         <v>181</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -21750,7 +21783,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21774,7 +21807,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -21783,7 +21816,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21791,10 +21824,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21820,16 +21853,16 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21842,7 +21875,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -21878,7 +21911,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21902,7 +21935,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -21911,7 +21944,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21919,10 +21952,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21948,10 +21981,10 @@
         <v>150</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21966,7 +21999,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -22002,7 +22035,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22026,7 +22059,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22035,7 +22068,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22043,14 +22076,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22072,10 +22105,10 @@
         <v>150</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -22090,7 +22123,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22126,7 +22159,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22150,7 +22183,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22159,7 +22192,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22167,14 +22200,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -22196,13 +22229,13 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22216,7 +22249,7 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>82</v>
@@ -22252,7 +22285,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22276,7 +22309,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22285,7 +22318,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22293,14 +22326,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22322,10 +22355,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22352,13 +22385,13 @@
         <v>82</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -22376,7 +22409,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22400,7 +22433,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -22409,7 +22442,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22417,14 +22450,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22446,10 +22479,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22464,7 +22497,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22500,7 +22533,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22524,7 +22557,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22533,7 +22566,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22541,10 +22574,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22570,13 +22603,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22626,7 +22659,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22650,7 +22683,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22659,7 +22692,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22667,10 +22700,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22693,17 +22726,17 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22716,7 +22749,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22752,7 +22785,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22776,7 +22809,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22785,7 +22818,7 @@
         <v>82</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22793,13 +22826,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>82</v>
@@ -22821,19 +22854,19 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22882,7 +22915,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22906,16 +22939,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22923,10 +22956,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23047,10 +23080,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23173,10 +23206,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23202,16 +23235,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23221,10 +23254,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -23239,10 +23272,10 @@
         <v>181</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -23260,7 +23293,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23275,7 +23308,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -23284,7 +23317,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -23293,7 +23326,7 @@
         <v>82</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23301,10 +23334,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23330,13 +23363,13 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23347,10 +23380,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -23365,10 +23398,10 @@
         <v>181</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -23386,7 +23419,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -23401,7 +23434,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -23410,7 +23443,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -23419,7 +23452,7 @@
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23427,10 +23460,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23456,16 +23489,16 @@
         <v>150</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -23478,7 +23511,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -23514,7 +23547,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23538,7 +23571,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -23547,7 +23580,7 @@
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23555,10 +23588,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23584,10 +23617,10 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23602,7 +23635,7 @@
         <v>82</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23638,7 +23671,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23653,16 +23686,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23671,7 +23704,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23679,14 +23712,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23708,10 +23741,10 @@
         <v>150</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23726,7 +23759,7 @@
         <v>82</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23762,7 +23795,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23777,16 +23810,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23795,7 +23828,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23803,14 +23836,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23832,13 +23865,13 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23852,7 +23885,7 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="U164" t="s" s="2">
         <v>82</v>
@@ -23888,7 +23921,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23912,7 +23945,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23921,7 +23954,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -23929,14 +23962,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23958,10 +23991,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -23988,13 +24021,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -24012,7 +24045,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24027,16 +24060,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -24045,7 +24078,7 @@
         <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24053,14 +24086,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24082,10 +24115,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24100,7 +24133,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -24136,7 +24169,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24151,16 +24184,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>82</v>
+        <v>757</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -24169,7 +24202,7 @@
         <v>82</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24177,10 +24210,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24206,13 +24239,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24262,7 +24295,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24277,7 +24310,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
@@ -24286,7 +24319,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24295,7 +24328,7 @@
         <v>82</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24303,10 +24336,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24329,17 +24362,17 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -24352,7 +24385,7 @@
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -24388,7 +24421,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24412,7 +24445,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24421,7 +24454,7 @@
         <v>82</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24429,10 +24462,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24553,10 +24586,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24679,10 +24712,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24705,16 +24738,16 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24764,7 +24797,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24773,13 +24806,13 @@
         <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
@@ -24788,7 +24821,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -24797,7 +24830,7 @@
         <v>82</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24805,10 +24838,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24831,83 +24864,83 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q172" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="R172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI172" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="R172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
@@ -24916,7 +24949,7 @@
         <v>82</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -24925,7 +24958,7 @@
         <v>82</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>82</v>
@@ -24933,10 +24966,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24959,17 +24992,17 @@
         <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -24998,7 +25031,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -25016,7 +25049,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -25031,25 +25064,25 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>82</v>
+        <v>792</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>82</v>
@@ -25057,10 +25090,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25083,19 +25116,19 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -25144,7 +25177,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -25168,7 +25201,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>154</v>
@@ -25177,7 +25210,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25185,10 +25218,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25211,19 +25244,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -25272,7 +25305,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -25296,7 +25329,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>
@@ -25305,7 +25338,7 @@
         <v>82</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25313,10 +25346,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25339,19 +25372,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25400,7 +25433,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25412,7 +25445,7 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -25424,7 +25457,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>154</v>
@@ -25441,10 +25474,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25565,10 +25598,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25691,14 +25724,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25720,16 +25753,16 @@
         <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -25778,7 +25811,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25819,10 +25852,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25845,17 +25878,17 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -25880,13 +25913,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -25904,7 +25937,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -25928,7 +25961,7 @@
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>154</v>
@@ -25937,7 +25970,7 @@
         <v>82</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>82</v>
@@ -25945,10 +25978,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25971,17 +26004,17 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -26030,7 +26063,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -26054,7 +26087,7 @@
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>154</v>
@@ -26063,7 +26096,7 @@
         <v>82</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>82</v>
@@ -26071,10 +26104,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26097,19 +26130,19 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -26158,7 +26191,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26182,7 +26215,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>154</v>
@@ -26191,7 +26224,7 @@
         <v>82</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>82</v>
@@ -26199,10 +26232,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26225,17 +26258,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26284,7 +26317,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26308,7 +26341,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26317,7 +26350,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26325,10 +26358,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26354,14 +26387,14 @@
         <v>110</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26389,10 +26422,10 @@
         <v>181</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -26410,7 +26443,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26434,7 +26467,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>154</v>
@@ -26443,7 +26476,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26451,10 +26484,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26477,17 +26510,17 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26536,7 +26569,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26545,7 +26578,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -26560,7 +26593,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26569,7 +26602,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26577,10 +26610,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26603,13 +26636,13 @@
         <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -26660,7 +26693,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26684,7 +26717,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26701,10 +26734,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26727,19 +26760,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26788,7 +26821,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26812,10 +26845,10 @@
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>82</v>
@@ -26829,10 +26862,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26953,10 +26986,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -27079,14 +27112,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -27108,16 +27141,16 @@
         <v>135</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -27166,7 +27199,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27207,10 +27240,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27233,19 +27266,19 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -27270,11 +27303,11 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -27292,7 +27325,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>90</v>
@@ -27307,25 +27340,25 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>82</v>
+        <v>885</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ191" t="s" s="2">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="AR191" t="s" s="2">
         <v>82</v>
@@ -27333,10 +27366,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27359,19 +27392,19 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -27420,7 +27453,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -27444,16 +27477,16 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>82</v>
@@ -27461,14 +27494,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27487,16 +27520,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -27546,7 +27579,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27570,7 +27603,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>154</v>
@@ -27579,7 +27612,7 @@
         <v>82</v>
       </c>
       <c r="AQ193" t="s" s="2">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="AR193" t="s" s="2">
         <v>82</v>
@@ -27587,10 +27620,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27613,19 +27646,19 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27674,7 +27707,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -27698,10 +27731,10 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>82</v>
@@ -27715,10 +27748,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27839,10 +27872,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27965,10 +27998,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27994,13 +28027,13 @@
         <v>150</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -28050,7 +28083,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28059,7 +28092,7 @@
         <v>90</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>102</v>
@@ -28091,10 +28124,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28120,13 +28153,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -28152,13 +28185,13 @@
         <v>82</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -28176,7 +28209,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -28217,10 +28250,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28243,16 +28276,16 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -28302,7 +28335,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -28326,7 +28359,7 @@
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -28343,10 +28376,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28372,13 +28405,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28389,7 +28422,7 @@
         <v>82</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>82</v>
@@ -28428,7 +28461,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -28443,7 +28476,7 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>82</v>
@@ -28469,10 +28502,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28495,19 +28528,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -28556,7 +28589,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28580,7 +28613,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>154</v>
@@ -28597,10 +28630,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28721,10 +28754,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28847,14 +28880,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -28876,16 +28909,16 @@
         <v>135</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>82</v>
@@ -28934,7 +28967,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -28975,10 +29008,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29001,16 +29034,16 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -29060,7 +29093,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -29084,7 +29117,7 @@
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>154</v>
@@ -29093,7 +29126,7 @@
         <v>82</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="AR205" t="s" s="2">
         <v>82</v>
@@ -29101,10 +29134,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29130,10 +29163,10 @@
         <v>110</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -29163,10 +29196,10 @@
         <v>181</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>82</v>
@@ -29184,7 +29217,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>90</v>
@@ -29208,7 +29241,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1785,6 +1785,9 @@
     <t>274: source value from PATIENT - PHONE NUMBER [RESIDENCE] (2-.131)</t>
   </si>
   <si>
+    <t>demographics.telecom</t>
+  </si>
+  <si>
     <t>Patient.telecom:va-home.use</t>
   </si>
   <si>
@@ -1822,9 +1825,6 @@
   </si>
   <si>
     <t>275: source value from PATIENT - PHONE NUMBER [WORK] (2-.132)</t>
-  </si>
-  <si>
-    <t>demographics.telecom</t>
   </si>
   <si>
     <t>Patient.telecom:va-work.use</t>
@@ -2319,6 +2319,9 @@
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
   </si>
   <si>
+    <t>demographics.address</t>
+  </si>
+  <si>
     <t>Patient.address:va-home.city</t>
   </si>
   <si>
@@ -2347,9 +2350,6 @@
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.Zip4</t>
-  </si>
-  <si>
-    <t>demographics.address</t>
   </si>
   <si>
     <t>Patient.address:va-home.country</t>
@@ -18272,7 +18272,7 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>544</v>
@@ -18292,7 +18292,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>546</v>
@@ -18340,7 +18340,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -18392,7 +18392,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -18418,7 +18418,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>554</v>
@@ -18544,7 +18544,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>560</v>
@@ -18668,13 +18668,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>517</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -18798,7 +18798,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>527</v>
@@ -18922,7 +18922,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>528</v>
@@ -19048,7 +19048,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>529</v>
@@ -19146,7 +19146,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -19172,7 +19172,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>538</v>
@@ -19274,13 +19274,13 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>544</v>
@@ -20288,7 +20288,7 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>544</v>
@@ -21621,7 +21621,7 @@
         <v>82</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>82</v>
@@ -23254,10 +23254,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -23692,7 +23692,7 @@
         <v>746</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>685</v>
@@ -23712,7 +23712,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>687</v>
@@ -23810,13 +23810,13 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>693</v>
@@ -23836,7 +23836,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>695</v>
@@ -23962,7 +23962,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>704</v>
@@ -24060,13 +24060,13 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>711</v>
@@ -24086,7 +24086,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>713</v>
@@ -24184,13 +24184,13 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>719</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="965">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -685,7 +685,7 @@
     <t>576: terminologyMaps using VF_raceCategory on PATIENT - RACE INFORMATION (2-2)</t>
   </si>
   <si>
-    <t>demographics.race [m-P:10]</t>
+    <t>Patient.Races</t>
   </si>
   <si>
     <t>./code</t>
@@ -880,7 +880,7 @@
     <t>575: terminologyMaps using VF_ethnicityCategory on PATIENT - ETHNICITY INFORMATION (2-6)</t>
   </si>
   <si>
-    <t>demographics.ethnicity [m-P:10.2]</t>
+    <t>Patient.EthnicGroup</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:ombCategory.value[x].display</t>
@@ -1050,7 +1050,7 @@
     <t>Outpat.Visit.PatientReligion,Outpat.Visit.PatientReligionCode,Outpat.Workload.PatientReligion,Outpat.Workload.PatientReligionCode,Patient.Patient.ReligionIEN,SPatient.SPatient.ReligionIEN</t>
   </si>
   <si>
-    <t>demographics.religion</t>
+    <t>Patient.Religion</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1302,9 +1302,6 @@
   </si>
   <si>
     <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
-  </si>
-  <si>
-    <t>demographics.icn</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -1475,7 +1472,7 @@
     <t>SPatient.SPatient.DestinationMergePatientIEN,SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
   </si>
   <si>
-    <t>demographics.familyName,demographics.fullName,demographics.givenNames</t>
+    <t>Patient.Name</t>
   </si>
   <si>
     <t>./formatted</t>
@@ -1785,7 +1782,7 @@
     <t>274: source value from PATIENT - PHONE NUMBER [RESIDENCE] (2-.131)</t>
   </si>
   <si>
-    <t>demographics.telecom</t>
+    <t>Patient.HomePhoneNumber</t>
   </si>
   <si>
     <t>Patient.telecom:va-home.use</t>
@@ -1827,6 +1824,9 @@
     <t>275: source value from PATIENT - PHONE NUMBER [WORK] (2-.132)</t>
   </si>
   <si>
+    <t>Patient.WorkPhoneNumber</t>
+  </si>
+  <si>
     <t>Patient.telecom:va-work.use</t>
   </si>
   <si>
@@ -1866,6 +1866,9 @@
     <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (2-.134)</t>
   </si>
   <si>
+    <t>Patient.MobilePhoneNumber</t>
+  </si>
+  <si>
     <t>Patient.telecom:va-mobile.use</t>
   </si>
   <si>
@@ -1905,7 +1908,7 @@
     <t>Patient.Patient.Gender,Patient.PatientBirthSex.BirthSex,SPatient.SPatient.Gender,SPatient.SPatientBirthSex.BirthSex,SPatient.SPatientBirthSex.BirthSex</t>
   </si>
   <si>
-    <t>demographics.gender</t>
+    <t>Patient.BirthGender,Patient.Gender</t>
   </si>
   <si>
     <t>.patient.administrativeGenderCode</t>
@@ -1939,7 +1942,7 @@
     <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
-    <t>demographics.dob</t>
+    <t>Patient.BirthTime,Patient.PatientExtension.Dob</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1999,7 +2002,7 @@
     <t>Patient.Patient.DeathDateTime,SPatient.SPatient.DeathDateTime</t>
   </si>
   <si>
-    <t>demographics.died</t>
+    <t>Patient.DeathTime,Patient.IsDead</t>
   </si>
   <si>
     <t>Patient.address</t>
@@ -2319,7 +2322,7 @@
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
   </si>
   <si>
-    <t>demographics.address</t>
+    <t>Patient.Address.Street</t>
   </si>
   <si>
     <t>Patient.address:va-home.city</t>
@@ -2331,6 +2334,9 @@
     <t>SPatient.SPatientGISAddress.City</t>
   </si>
   <si>
+    <t>Patient.Address.City</t>
+  </si>
+  <si>
     <t>Patient.address:va-home.district</t>
   </si>
   <si>
@@ -2343,6 +2349,9 @@
     <t>SPatient.SPatientGISAddress.StateIEN,SPatient.SPatientGISAddress.StateSID</t>
   </si>
   <si>
+    <t>Patient.Address.State</t>
+  </si>
+  <si>
     <t>Patient.address:va-home.postalCode</t>
   </si>
   <si>
@@ -2356,6 +2365,9 @@
   </si>
   <si>
     <t>292: source value from PATIENT - COUNTRY (2-.1173)</t>
+  </si>
+  <si>
+    <t>Patient.Address.Country</t>
   </si>
   <si>
     <t>Patient.address:va-home.period</t>
@@ -2398,6 +2410,9 @@
     <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (2-.1217)</t>
   </si>
   <si>
+    <t>Patient.Address.FromTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
@@ -2428,6 +2443,9 @@
     <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (2-.1218)</t>
   </si>
   <si>
+    <t>Patient.Address.ToTime</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
@@ -2455,7 +2473,7 @@
     <t>Outpat.Visit.PatientMaritalStatus,Outpat.Workload.PatientMaritalStatus,Patient.Patient.MaritalStatusIEN,SPatient.SPatient.MaritalStatusIEN</t>
   </si>
   <si>
-    <t>demographics.maritalStatus</t>
+    <t>Patient.MaritalStatus</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -2744,7 +2762,7 @@
     <t>Patient.PreferredLanguage.PreferredLanguage</t>
   </si>
   <si>
-    <t>demographics.language</t>
+    <t>Patient.PatientLanguage.Preferred Language</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -3332,7 +3350,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.34765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="73.78515625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -14996,19 +15014,19 @@
         <v>416</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -15016,10 +15034,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15042,13 +15060,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -15099,7 +15117,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -15123,16 +15141,16 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -15140,10 +15158,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15166,16 +15184,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15225,7 +15243,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -15249,16 +15267,16 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -15266,10 +15284,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15295,23 +15313,23 @@
         <v>227</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="O96" t="s" s="2">
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="R96" t="s" s="2">
         <v>82</v>
       </c>
@@ -15355,7 +15373,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -15379,13 +15397,13 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>82</v>
@@ -15396,10 +15414,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15422,19 +15440,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15483,7 +15501,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -15507,16 +15525,16 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AO97" t="s" s="2">
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>82</v>
@@ -15524,10 +15542,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15648,10 +15666,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15774,10 +15792,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15803,16 +15821,16 @@
         <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15840,28 +15858,28 @@
         <v>181</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15885,16 +15903,16 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15902,10 +15920,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15931,16 +15949,16 @@
         <v>150</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15989,7 +16007,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -16004,25 +16022,25 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AM101" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -16030,14 +16048,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16059,13 +16077,13 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -16076,79 +16094,79 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="T102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI102" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>82</v>
@@ -16156,14 +16174,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -16185,13 +16203,13 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16202,46 +16220,46 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -16250,31 +16268,31 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16282,10 +16300,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16311,10 +16329,10 @@
         <v>150</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -16365,7 +16383,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16389,16 +16407,16 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ104" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16406,10 +16424,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16435,10 +16453,10 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -16450,46 +16468,46 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16504,25 +16522,25 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>82</v>
@@ -16530,10 +16548,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16556,17 +16574,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16615,7 +16633,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16639,16 +16657,16 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16656,10 +16674,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16682,19 +16700,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16731,7 +16749,7 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -16741,7 +16759,7 @@
         <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16765,16 +16783,16 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AO107" t="s" s="2">
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16782,10 +16800,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16906,10 +16924,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17032,10 +17050,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17061,10 +17079,10 @@
         <v>110</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -17094,37 +17112,37 @@
         <v>181</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Z110" t="s" s="2">
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI110" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
@@ -17139,16 +17157,16 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>82</v>
@@ -17156,10 +17174,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17185,16 +17203,16 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -17243,7 +17261,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -17267,16 +17285,16 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17284,10 +17302,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17313,16 +17331,16 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -17351,25 +17369,25 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17393,7 +17411,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -17402,7 +17420,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17410,10 +17428,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17436,16 +17454,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -17495,7 +17513,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17536,10 +17554,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17562,13 +17580,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17619,7 +17637,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17643,7 +17661,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17660,13 +17678,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C115" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -17688,19 +17706,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17749,7 +17767,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17773,16 +17791,16 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO115" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AO115" t="s" s="2">
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17790,10 +17808,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17914,10 +17932,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18040,10 +18058,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18069,10 +18087,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -18084,7 +18102,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -18102,43 +18120,43 @@
         <v>181</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Z118" t="s" s="2">
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -18147,16 +18165,16 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -18164,10 +18182,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18193,16 +18211,16 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -18251,7 +18269,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -18266,25 +18284,25 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AN119" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ119" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18292,10 +18310,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18321,16 +18339,16 @@
         <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18340,7 +18358,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -18359,25 +18377,25 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18392,7 +18410,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -18401,7 +18419,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -18410,7 +18428,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18418,10 +18436,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18444,16 +18462,16 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -18503,7 +18521,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18544,10 +18562,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18570,13 +18588,13 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18627,7 +18645,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -18651,7 +18669,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -18668,13 +18686,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -18696,19 +18714,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -18757,7 +18775,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -18781,16 +18799,16 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO123" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AO123" t="s" s="2">
+      <c r="AP123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>82</v>
@@ -18798,10 +18816,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18922,10 +18940,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19048,10 +19066,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19077,10 +19095,10 @@
         <v>110</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -19092,7 +19110,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -19110,43 +19128,43 @@
         <v>181</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -19155,16 +19173,16 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -19172,10 +19190,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19201,16 +19219,16 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -19259,7 +19277,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -19274,25 +19292,25 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM127" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AL127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="AN127" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ127" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ127" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19303,7 +19321,7 @@
         <v>587</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19329,16 +19347,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -19367,25 +19385,25 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19409,7 +19427,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19418,7 +19436,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19429,7 +19447,7 @@
         <v>590</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19452,16 +19470,16 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19511,7 +19529,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19555,7 +19573,7 @@
         <v>591</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19578,13 +19596,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19635,7 +19653,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19659,7 +19677,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19679,7 +19697,7 @@
         <v>592</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C131" t="s" s="2">
         <v>593</v>
@@ -19704,19 +19722,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -19765,7 +19783,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19789,16 +19807,16 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AO131" t="s" s="2">
+      <c r="AP131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ131" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ131" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19809,7 +19827,7 @@
         <v>594</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19933,7 +19951,7 @@
         <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20059,7 +20077,7 @@
         <v>596</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20085,10 +20103,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -20100,7 +20118,7 @@
         <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>82</v>
@@ -20118,37 +20136,37 @@
         <v>181</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="Z134" t="s" s="2">
+      <c r="AA134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AA134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF134" t="s" s="2">
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI134" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>102</v>
@@ -20163,16 +20181,16 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ134" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>82</v>
@@ -20183,7 +20201,7 @@
         <v>598</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20209,16 +20227,16 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -20267,7 +20285,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -20288,19 +20306,19 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="AN135" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ135" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ135" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AR135" t="s" s="2">
         <v>82</v>
@@ -20308,10 +20326,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20337,16 +20355,16 @@
         <v>110</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -20356,7 +20374,7 @@
         <v>82</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>82</v>
@@ -20375,25 +20393,25 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF136" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20408,7 +20426,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20417,7 +20435,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20426,7 +20444,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20434,10 +20452,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20460,16 +20478,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -20519,7 +20537,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20560,10 +20578,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20586,13 +20604,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20643,7 +20661,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20667,7 +20685,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -20684,10 +20702,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20713,16 +20731,16 @@
         <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20751,7 +20769,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -20769,7 +20787,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20784,25 +20802,25 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>304</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20810,10 +20828,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20836,19 +20854,19 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20897,7 +20915,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20912,36 +20930,36 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20964,19 +20982,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -21013,7 +21031,7 @@
         <v>82</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -21023,7 +21041,7 @@
         <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -21047,7 +21065,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -21056,7 +21074,7 @@
         <v>82</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>82</v>
@@ -21064,13 +21082,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -21092,19 +21110,19 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -21153,7 +21171,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -21168,16 +21186,16 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>154</v>
@@ -21186,7 +21204,7 @@
         <v>82</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -21194,10 +21212,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21220,19 +21238,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21269,7 +21287,7 @@
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -21279,7 +21297,7 @@
         <v>139</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21303,16 +21321,16 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21320,10 +21338,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21444,10 +21462,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21570,10 +21588,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21599,16 +21617,16 @@
         <v>110</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21621,7 +21639,7 @@
         <v>82</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>82</v>
@@ -21636,10 +21654,10 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -21657,7 +21675,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21681,7 +21699,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -21690,7 +21708,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21698,10 +21716,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21727,13 +21745,13 @@
         <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -21747,7 +21765,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21762,10 +21780,10 @@
         <v>181</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -21783,7 +21801,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21807,7 +21825,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -21816,7 +21834,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21824,10 +21842,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21853,16 +21871,16 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21875,7 +21893,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -21911,7 +21929,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21935,7 +21953,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -21944,7 +21962,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21952,10 +21970,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21981,10 +21999,10 @@
         <v>150</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21999,7 +22017,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -22035,7 +22053,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22059,7 +22077,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22068,7 +22086,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22076,14 +22094,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22105,10 +22123,10 @@
         <v>150</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -22123,7 +22141,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22159,7 +22177,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22183,7 +22201,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22192,7 +22210,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22200,14 +22218,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -22229,13 +22247,13 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22249,7 +22267,7 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>82</v>
@@ -22285,7 +22303,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22309,7 +22327,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22318,7 +22336,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22326,14 +22344,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22355,10 +22373,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22388,10 +22406,10 @@
         <v>364</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -22409,7 +22427,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22433,7 +22451,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -22442,7 +22460,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22450,14 +22468,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22479,10 +22497,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22497,7 +22515,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22533,7 +22551,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22557,7 +22575,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22566,7 +22584,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22574,10 +22592,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22603,13 +22621,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22659,7 +22677,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22683,7 +22701,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22692,7 +22710,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22700,10 +22718,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22726,17 +22744,17 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22749,7 +22767,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22785,7 +22803,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22809,7 +22827,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22818,7 +22836,7 @@
         <v>82</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22826,13 +22844,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>82</v>
@@ -22854,19 +22872,19 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22915,7 +22933,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22939,16 +22957,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22956,10 +22974,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23080,10 +23098,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23206,10 +23224,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23235,16 +23253,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23254,10 +23272,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -23272,10 +23290,10 @@
         <v>181</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -23293,7 +23311,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23308,7 +23326,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -23317,7 +23335,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -23326,7 +23344,7 @@
         <v>82</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23334,10 +23352,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23363,13 +23381,13 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23380,10 +23398,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -23398,10 +23416,10 @@
         <v>181</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -23419,7 +23437,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -23434,7 +23452,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -23443,7 +23461,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -23452,7 +23470,7 @@
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23460,10 +23478,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23489,16 +23507,16 @@
         <v>150</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -23511,7 +23529,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -23547,7 +23565,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23571,7 +23589,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -23580,7 +23598,7 @@
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23588,10 +23606,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23617,10 +23635,10 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23635,7 +23653,7 @@
         <v>82</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23671,7 +23689,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23686,16 +23704,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23704,7 +23722,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23712,14 +23730,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23741,10 +23759,10 @@
         <v>150</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23759,7 +23777,7 @@
         <v>82</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23795,7 +23813,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23810,16 +23828,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23828,7 +23846,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23836,14 +23854,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23865,13 +23883,13 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23885,7 +23903,7 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="U164" t="s" s="2">
         <v>82</v>
@@ -23921,7 +23939,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23945,7 +23963,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23954,7 +23972,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -23962,14 +23980,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23991,10 +24009,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24024,10 +24042,10 @@
         <v>364</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -24045,7 +24063,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24060,16 +24078,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -24078,7 +24096,7 @@
         <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24086,14 +24104,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24115,10 +24133,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24133,7 +24151,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -24169,7 +24187,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24184,16 +24202,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>747</v>
+        <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -24202,7 +24220,7 @@
         <v>82</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24210,10 +24228,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24239,13 +24257,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24295,7 +24313,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24310,16 +24328,16 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>82</v>
+        <v>763</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24328,7 +24346,7 @@
         <v>82</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24336,10 +24354,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24362,17 +24380,17 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -24385,7 +24403,7 @@
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -24421,7 +24439,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24445,7 +24463,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24454,7 +24472,7 @@
         <v>82</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24462,10 +24480,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24586,10 +24604,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24712,10 +24730,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24738,16 +24756,16 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24797,7 +24815,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24806,22 +24824,22 @@
         <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>82</v>
+        <v>777</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -24830,7 +24848,7 @@
         <v>82</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24838,10 +24856,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24864,23 +24882,23 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q172" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="R172" t="s" s="2">
         <v>82</v>
@@ -24925,7 +24943,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -24934,22 +24952,22 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>82</v>
+        <v>788</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -24958,7 +24976,7 @@
         <v>82</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>82</v>
@@ -24966,10 +24984,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24995,14 +25013,14 @@
         <v>313</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -25031,7 +25049,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -25049,7 +25067,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -25064,25 +25082,25 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>82</v>
@@ -25090,10 +25108,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25116,19 +25134,19 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -25177,7 +25195,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -25201,7 +25219,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>154</v>
@@ -25210,7 +25228,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25218,10 +25236,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25244,19 +25262,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -25305,7 +25323,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -25329,7 +25347,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>
@@ -25338,7 +25356,7 @@
         <v>82</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25346,10 +25364,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25372,19 +25390,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25433,7 +25451,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25445,7 +25463,7 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -25457,7 +25475,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>154</v>
@@ -25474,10 +25492,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25598,10 +25616,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25724,14 +25742,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25753,10 +25771,10 @@
         <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>160</v>
@@ -25811,7 +25829,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25852,10 +25870,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25881,14 +25899,14 @@
         <v>313</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -25916,10 +25934,10 @@
         <v>364</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -25937,7 +25955,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -25961,7 +25979,7 @@
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>154</v>
@@ -25970,7 +25988,7 @@
         <v>82</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>82</v>
@@ -25978,10 +25996,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26004,17 +26022,17 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -26063,7 +26081,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -26087,7 +26105,7 @@
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>154</v>
@@ -26096,7 +26114,7 @@
         <v>82</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>82</v>
@@ -26104,10 +26122,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26130,19 +26148,19 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -26191,7 +26209,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26215,7 +26233,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>154</v>
@@ -26224,7 +26242,7 @@
         <v>82</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>82</v>
@@ -26232,10 +26250,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26258,17 +26276,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26317,7 +26335,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26341,7 +26359,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26350,7 +26368,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26358,10 +26376,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26387,14 +26405,14 @@
         <v>110</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26422,10 +26440,10 @@
         <v>181</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -26443,7 +26461,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26476,7 +26494,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26484,10 +26502,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26510,17 +26528,17 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26569,7 +26587,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26578,7 +26596,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -26593,7 +26611,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26602,7 +26620,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26610,10 +26628,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26636,13 +26654,13 @@
         <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -26693,7 +26711,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26717,7 +26735,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26734,10 +26752,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26760,19 +26778,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26821,7 +26839,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26845,10 +26863,10 @@
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>82</v>
@@ -26862,10 +26880,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26986,10 +27004,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -27112,14 +27130,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -27141,10 +27159,10 @@
         <v>135</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>160</v>
@@ -27199,7 +27217,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27240,10 +27258,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27269,16 +27287,16 @@
         <v>313</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -27307,7 +27325,7 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -27325,7 +27343,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>90</v>
@@ -27340,25 +27358,25 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ191" t="s" s="2">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="AR191" t="s" s="2">
         <v>82</v>
@@ -27366,10 +27384,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27395,16 +27413,16 @@
         <v>227</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -27453,7 +27471,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -27477,16 +27495,16 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>82</v>
@@ -27494,14 +27512,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27520,16 +27538,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -27579,7 +27597,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27603,7 +27621,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>154</v>
@@ -27612,7 +27630,7 @@
         <v>82</v>
       </c>
       <c r="AQ193" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="AR193" t="s" s="2">
         <v>82</v>
@@ -27620,10 +27638,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27646,19 +27664,19 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27707,7 +27725,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -27731,10 +27749,10 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>82</v>
@@ -27748,10 +27766,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27872,10 +27890,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27998,10 +28016,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28027,13 +28045,13 @@
         <v>150</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -28083,7 +28101,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28092,7 +28110,7 @@
         <v>90</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>102</v>
@@ -28124,10 +28142,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28153,13 +28171,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -28188,10 +28206,10 @@
         <v>364</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -28209,7 +28227,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -28250,10 +28268,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28279,13 +28297,13 @@
         <v>340</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -28335,7 +28353,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -28359,7 +28377,7 @@
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -28376,10 +28394,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28405,13 +28423,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28422,7 +28440,7 @@
         <v>82</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>82</v>
@@ -28461,7 +28479,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -28476,7 +28494,7 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>82</v>
@@ -28502,10 +28520,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28528,19 +28546,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -28589,7 +28607,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28613,7 +28631,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>154</v>
@@ -28630,10 +28648,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28754,10 +28772,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28880,14 +28898,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -28909,10 +28927,10 @@
         <v>135</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>160</v>
@@ -28967,7 +28985,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -29008,10 +29026,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29034,16 +29052,16 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -29093,7 +29111,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -29126,7 +29144,7 @@
         <v>82</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="AR205" t="s" s="2">
         <v>82</v>
@@ -29134,10 +29152,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29163,10 +29181,10 @@
         <v>110</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -29196,10 +29214,10 @@
         <v>181</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>82</v>
@@ -29217,7 +29235,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>90</v>
@@ -29241,7 +29259,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1942,7 +1942,7 @@
     <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
   </si>
   <si>
-    <t>Patient.BirthTime,Patient.PatientExtension.Dob</t>
+    <t>Patient.BirthTime,Patient.Extension[PatientExtension].Dob</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -2322,7 +2322,7 @@
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
   </si>
   <si>
-    <t>Patient.Address.Street</t>
+    <t>Patient.PermanentAddress[Address].Street</t>
   </si>
   <si>
     <t>Patient.address:va-home.city</t>
@@ -2334,7 +2334,7 @@
     <t>SPatient.SPatientGISAddress.City</t>
   </si>
   <si>
-    <t>Patient.Address.City</t>
+    <t>Patient.PermanentAddress[Address].City</t>
   </si>
   <si>
     <t>Patient.address:va-home.district</t>
@@ -2349,7 +2349,7 @@
     <t>SPatient.SPatientGISAddress.StateIEN,SPatient.SPatientGISAddress.StateSID</t>
   </si>
   <si>
-    <t>Patient.Address.State</t>
+    <t>Patient.PermanentAddress[Address].State</t>
   </si>
   <si>
     <t>Patient.address:va-home.postalCode</t>
@@ -2367,7 +2367,7 @@
     <t>292: source value from PATIENT - COUNTRY (2-.1173)</t>
   </si>
   <si>
-    <t>Patient.Address.Country</t>
+    <t>Patient.PermanentAddress[Address].Country</t>
   </si>
   <si>
     <t>Patient.address:va-home.period</t>
@@ -2410,7 +2410,7 @@
     <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (2-.1217)</t>
   </si>
   <si>
-    <t>Patient.Address.FromTime</t>
+    <t>Patient.TemporaryAddress[Address].FromTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -2443,7 +2443,7 @@
     <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (2-.1218)</t>
   </si>
   <si>
-    <t>Patient.Address.ToTime</t>
+    <t>Patient.TemporaryAddress[Address].ToTime</t>
   </si>
   <si>
     <t>./high</t>
@@ -3350,7 +3350,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.34765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="54.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-patient</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-patient.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1629,7 +1629,7 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="966">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1298,7 +1298,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>272: source value from PATIENT - INTEGRATION CONTROL NUMBER (2-991.01)</t>
+    <t>272: source value based on PATIENT - INTEGRATION CONTROL NUMBER (2-991.01)</t>
   </si>
   <si>
     <t>Patient.Patient.PatientICN,Patient.PatientICN.PatientICN,SPatient.SPatient.PatientICN,SPatient.SPatientGISAddress.PatientICN</t>
@@ -1466,7 +1466,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>273: source value from PATIENT - NAME (2-.01)</t>
+    <t>273: source value based on PATIENT - NAME (2-.01)</t>
   </si>
   <si>
     <t>SPatient.SPatient.DestinationMergePatientIEN,SPatient.SPatient.PatientFirstName,SPatient.SPatient.PatientLastName,SPatient.SPatient.PatientName,SPatient.SPatientAlias.PatientName</t>
@@ -1779,7 +1779,7 @@
     <t>Patient.telecom:va-home.value</t>
   </si>
   <si>
-    <t>274: source value from PATIENT - PHONE NUMBER [RESIDENCE] (2-.131)</t>
+    <t>274: source value based on PATIENT - PHONE NUMBER [RESIDENCE] (2-.131)</t>
   </si>
   <si>
     <t>Patient.HomePhoneNumber</t>
@@ -1821,7 +1821,7 @@
     <t>Patient.telecom:va-work.value</t>
   </si>
   <si>
-    <t>275: source value from PATIENT - PHONE NUMBER [WORK] (2-.132)</t>
+    <t>275: source value based on PATIENT - PHONE NUMBER [WORK] (2-.132)</t>
   </si>
   <si>
     <t>Patient.WorkPhoneNumber</t>
@@ -1863,7 +1863,7 @@
     <t>Patient.telecom:va-mobile.value</t>
   </si>
   <si>
-    <t>276: source value from PATIENT - PHONE NUMBER [CELLULAR] (2-.134)</t>
+    <t>276: source value based on PATIENT - PHONE NUMBER [CELLULAR] (2-.134)</t>
   </si>
   <si>
     <t>Patient.MobilePhoneNumber</t>
@@ -1936,7 +1936,7 @@
     <t>Age of the individual drives many clinical processes.</t>
   </si>
   <si>
-    <t>284: source value from PATIENT - DATE OF BIRTH (2-.03)</t>
+    <t>284: source value based on PATIENT - DATE OF BIRTH (2-.03)</t>
   </si>
   <si>
     <t>SPatient.PlaceOfBirth.BirthDateTime,SPatient.SPatient.BirthDateTime</t>
@@ -1996,7 +1996,11 @@
 </t>
   </si>
   <si>
-    <t>285: source value from PATIENT - DATE OF DEATH (2-.351) case not null</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+p-7-285:If not null then source value from (2-.351) {null}</t>
+  </si>
+  <si>
+    <t>285: source value based on PATIENT - DATE OF DEATH (2-.351) if not null</t>
   </si>
   <si>
     <t>Patient.Patient.DeathDateTime,SPatient.SPatient.DeathDateTime</t>
@@ -2316,7 +2320,7 @@
     <t>Patient.address:va-home.line</t>
   </si>
   <si>
-    <t>288: source value from PATIENT - STREET ADDRESS [LINE 3] (2-.113)</t>
+    <t>288: source value based on PATIENT - STREET ADDRESS [LINE 3] (2-.113)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.StreetAddress2</t>
@@ -2328,7 +2332,7 @@
     <t>Patient.address:va-home.city</t>
   </si>
   <si>
-    <t>289: source value from PATIENT - CITY (2-.114)</t>
+    <t>289: source value based on PATIENT - CITY (2-.114)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.City</t>
@@ -2343,7 +2347,7 @@
     <t>Patient.address:va-home.state</t>
   </si>
   <si>
-    <t>290: source value from PATIENT - STATE (2-.115)</t>
+    <t>290: source value based on PATIENT - STATE (2-.115)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.StateIEN,SPatient.SPatientGISAddress.StateSID</t>
@@ -2355,7 +2359,7 @@
     <t>Patient.address:va-home.postalCode</t>
   </si>
   <si>
-    <t>291: source value from PATIENT - ZIP+4 (2-.1112)</t>
+    <t>291: source value based on PATIENT - ZIP+4 (2-.1112)</t>
   </si>
   <si>
     <t>SPatient.SPatientGISAddress.Zip4</t>
@@ -2364,7 +2368,7 @@
     <t>Patient.address:va-home.country</t>
   </si>
   <si>
-    <t>292: source value from PATIENT - COUNTRY (2-.1173)</t>
+    <t>292: source value based on PATIENT - COUNTRY (2-.1173)</t>
   </si>
   <si>
     <t>Patient.PermanentAddress[Address].Country</t>
@@ -2407,7 +2411,7 @@
 </t>
   </si>
   <si>
-    <t>293: source value from PATIENT - TEMPORARY ADDRESS START DATE (2-.1217)</t>
+    <t>293: source value based on PATIENT - TEMPORARY ADDRESS START DATE (2-.1217)</t>
   </si>
   <si>
     <t>Patient.TemporaryAddress[Address].FromTime</t>
@@ -2440,7 +2444,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>294: source value from PATIENT - TEMPORARY ADDRESS END DATE (2-.1218)</t>
+    <t>294: source value based on PATIENT - TEMPORARY ADDRESS END DATE (2-.1218)</t>
   </si>
   <si>
     <t>Patient.TemporaryAddress[Address].ToTime</t>
@@ -2756,7 +2760,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/simple-language</t>
   </si>
   <si>
-    <t>295: source value from PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (2-7 &gt; 2.07-.02)</t>
+    <t>295: source value based on PATIENT - LANGUAGE DATE/TIME &gt; LANGUAGE DATE/TIME - PREFERRED LANGUAGE (2-7 &gt; 2.07-.02)</t>
   </si>
   <si>
     <t>Patient.PreferredLanguage.PreferredLanguage</t>
@@ -3348,7 +3352,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="115.59765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="119.69140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="175.34765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="54.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="156.828125" customWidth="true" bestFit="true"/>
@@ -21183,16 +21187,16 @@
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>642</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>637</v>
@@ -21212,10 +21216,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21238,19 +21242,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21297,7 +21301,7 @@
         <v>139</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21321,16 +21325,16 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21338,10 +21342,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21462,10 +21466,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21588,10 +21592,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21617,16 +21621,16 @@
         <v>110</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21654,10 +21658,10 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -21675,7 +21679,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21708,7 +21712,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21716,10 +21720,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21745,13 +21749,13 @@
         <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -21765,7 +21769,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21780,10 +21784,10 @@
         <v>181</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -21801,7 +21805,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21834,7 +21838,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21842,10 +21846,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21871,13 +21875,13 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>467</v>
@@ -21893,7 +21897,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -21929,7 +21933,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21962,7 +21966,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21970,10 +21974,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21999,10 +22003,10 @@
         <v>150</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22017,7 +22021,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -22053,7 +22057,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22077,7 +22081,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22086,7 +22090,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22094,14 +22098,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22123,10 +22127,10 @@
         <v>150</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -22141,7 +22145,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22177,7 +22181,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22201,7 +22205,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22210,7 +22214,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22218,14 +22222,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -22247,13 +22251,13 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22267,7 +22271,7 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>82</v>
@@ -22303,7 +22307,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22327,7 +22331,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22336,7 +22340,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22344,14 +22348,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22373,10 +22377,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22406,10 +22410,10 @@
         <v>364</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -22427,7 +22431,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22451,7 +22455,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -22460,7 +22464,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22468,14 +22472,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22497,10 +22501,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22515,7 +22519,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22551,7 +22555,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22575,7 +22579,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22584,7 +22588,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22592,10 +22596,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22621,13 +22625,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22677,7 +22681,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22701,7 +22705,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22710,7 +22714,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22718,10 +22722,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22747,14 +22751,14 @@
         <v>420</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22767,7 +22771,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22803,7 +22807,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22836,7 +22840,7 @@
         <v>82</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22844,10 +22848,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>564</v>
@@ -22872,19 +22876,19 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22933,7 +22937,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22957,16 +22961,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22974,10 +22978,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23098,10 +23102,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23224,10 +23228,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23253,16 +23257,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23290,10 +23294,10 @@
         <v>181</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -23311,7 +23315,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23326,7 +23330,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -23344,7 +23348,7 @@
         <v>82</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23352,10 +23356,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23381,13 +23385,13 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23398,10 +23402,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -23416,10 +23420,10 @@
         <v>181</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -23437,7 +23441,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -23452,7 +23456,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -23470,7 +23474,7 @@
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23478,10 +23482,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23507,13 +23511,13 @@
         <v>150</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>467</v>
@@ -23529,7 +23533,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -23565,7 +23569,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23598,7 +23602,7 @@
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23606,10 +23610,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23635,10 +23639,10 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23653,7 +23657,7 @@
         <v>82</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23689,7 +23693,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23704,16 +23708,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23722,7 +23726,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23730,14 +23734,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23759,10 +23763,10 @@
         <v>150</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23777,7 +23781,7 @@
         <v>82</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23813,7 +23817,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23828,16 +23832,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23846,7 +23850,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23854,14 +23858,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23883,13 +23887,13 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23903,7 +23907,7 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="U164" t="s" s="2">
         <v>82</v>
@@ -23939,7 +23943,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23963,7 +23967,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23972,7 +23976,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -23980,14 +23984,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -24009,10 +24013,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24042,10 +24046,10 @@
         <v>364</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -24063,7 +24067,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24078,16 +24082,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -24096,7 +24100,7 @@
         <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24104,14 +24108,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24133,10 +24137,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24151,7 +24155,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -24187,7 +24191,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24202,16 +24206,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -24220,7 +24224,7 @@
         <v>82</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24228,10 +24232,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24257,13 +24261,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24313,7 +24317,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24328,16 +24332,16 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24346,7 +24350,7 @@
         <v>82</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24354,10 +24358,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24383,14 +24387,14 @@
         <v>420</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -24403,7 +24407,7 @@
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -24439,7 +24443,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24472,7 +24476,7 @@
         <v>82</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24480,10 +24484,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24604,10 +24608,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24730,10 +24734,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24759,13 +24763,13 @@
         <v>641</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24815,7 +24819,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24824,22 +24828,22 @@
         <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -24848,7 +24852,7 @@
         <v>82</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24856,10 +24860,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24885,20 +24889,20 @@
         <v>641</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q172" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="R172" t="s" s="2">
         <v>82</v>
@@ -24943,7 +24947,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -24952,22 +24956,22 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -24976,7 +24980,7 @@
         <v>82</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>82</v>
@@ -24984,10 +24988,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25013,14 +25017,14 @@
         <v>313</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -25049,7 +25053,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -25067,7 +25071,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -25082,25 +25086,25 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>82</v>
@@ -25108,10 +25112,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25134,19 +25138,19 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -25195,7 +25199,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -25219,7 +25223,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>154</v>
@@ -25228,7 +25232,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25236,10 +25240,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25262,19 +25266,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -25323,7 +25327,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -25347,7 +25351,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>
@@ -25356,7 +25360,7 @@
         <v>82</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25364,10 +25368,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25390,19 +25394,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25451,7 +25455,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25463,7 +25467,7 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -25475,7 +25479,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>154</v>
@@ -25492,10 +25496,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25616,10 +25620,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25742,14 +25746,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25771,10 +25775,10 @@
         <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>160</v>
@@ -25829,7 +25833,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25870,10 +25874,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25899,14 +25903,14 @@
         <v>313</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -25934,10 +25938,10 @@
         <v>364</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -25955,7 +25959,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -25979,7 +25983,7 @@
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>154</v>
@@ -25988,7 +25992,7 @@
         <v>82</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>82</v>
@@ -25996,10 +26000,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26025,14 +26029,14 @@
         <v>443</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -26081,7 +26085,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -26114,7 +26118,7 @@
         <v>82</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>82</v>
@@ -26122,10 +26126,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26151,13 +26155,13 @@
         <v>517</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="O182" t="s" s="2">
         <v>521</v>
@@ -26209,7 +26213,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26242,7 +26246,7 @@
         <v>82</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>82</v>
@@ -26250,10 +26254,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26276,17 +26280,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26335,7 +26339,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26359,7 +26363,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26368,7 +26372,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26376,10 +26380,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26408,11 +26412,11 @@
         <v>607</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26440,10 +26444,10 @@
         <v>181</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -26461,7 +26465,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26494,7 +26498,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26502,10 +26506,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26531,14 +26535,14 @@
         <v>427</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26587,7 +26591,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26596,7 +26600,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -26611,7 +26615,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26620,7 +26624,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26628,10 +26632,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26657,10 +26661,10 @@
         <v>420</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -26711,7 +26715,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26735,7 +26739,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26752,10 +26756,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26778,19 +26782,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26839,7 +26843,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26863,10 +26867,10 @@
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>82</v>
@@ -26880,10 +26884,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27004,10 +27008,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -27130,14 +27134,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -27159,10 +27163,10 @@
         <v>135</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>160</v>
@@ -27217,7 +27221,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27258,10 +27262,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27287,16 +27291,16 @@
         <v>313</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -27325,7 +27329,7 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -27343,7 +27347,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>90</v>
@@ -27358,25 +27362,25 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ191" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AR191" t="s" s="2">
         <v>82</v>
@@ -27384,10 +27388,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27413,16 +27417,16 @@
         <v>227</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -27471,7 +27475,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -27495,16 +27499,16 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>82</v>
@@ -27512,14 +27516,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27538,16 +27542,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -27597,7 +27601,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27621,7 +27625,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>154</v>
@@ -27630,7 +27634,7 @@
         <v>82</v>
       </c>
       <c r="AQ193" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AR193" t="s" s="2">
         <v>82</v>
@@ -27638,10 +27642,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27667,16 +27671,16 @@
         <v>427</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27725,7 +27729,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -27749,10 +27753,10 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>82</v>
@@ -27766,10 +27770,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27890,10 +27894,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -28016,10 +28020,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28045,13 +28049,13 @@
         <v>150</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -28101,7 +28105,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28110,7 +28114,7 @@
         <v>90</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>102</v>
@@ -28142,10 +28146,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28171,13 +28175,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -28206,10 +28210,10 @@
         <v>364</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -28227,7 +28231,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -28268,10 +28272,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28297,13 +28301,13 @@
         <v>340</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -28353,7 +28357,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -28377,7 +28381,7 @@
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -28394,10 +28398,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28423,13 +28427,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28440,7 +28444,7 @@
         <v>82</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>82</v>
@@ -28479,7 +28483,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -28494,7 +28498,7 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>82</v>
@@ -28520,10 +28524,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28546,19 +28550,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -28607,7 +28611,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28631,7 +28635,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>154</v>
@@ -28648,10 +28652,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28772,10 +28776,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28898,14 +28902,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -28927,10 +28931,10 @@
         <v>135</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>160</v>
@@ -28985,7 +28989,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -29026,10 +29030,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29052,16 +29056,16 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -29111,7 +29115,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -29144,7 +29148,7 @@
         <v>82</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AR205" t="s" s="2">
         <v>82</v>
@@ -29152,10 +29156,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29181,10 +29185,10 @@
         <v>110</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -29214,10 +29218,10 @@
         <v>181</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>82</v>
@@ -29235,7 +29239,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>90</v>
@@ -29259,7 +29263,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8263" uniqueCount="972">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,6 +676,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>see mapping [VF_raceCategory](ConceptMap-VF-raceCategory.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/raceCategory</t>
   </si>
   <si>
@@ -874,6 +877,9 @@
     <t>Patient.extension:ethnicity.extension:ombCategory.value[x].code</t>
   </si>
   <si>
+    <t>see mapping [VF_ethnicityCategory](ConceptMap-VF-ethnicityCategory.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/ethnicityCategory</t>
   </si>
   <si>
@@ -994,6 +1000,9 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
+    <t>see mapping [VF_genderIdentity](ConceptMap-VF-genderIdentity.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/genderIdentity</t>
   </si>
   <si>
@@ -1035,6 +1044,9 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>see mapping [VF_Religion](ConceptMap-VF-Religion.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/Religion</t>
@@ -1899,6 +1911,9 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
+    <t>see mapping [VF_adminGender](ConceptMap-VF-adminGender.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/adminGender</t>
   </si>
   <si>
@@ -2466,6 +2481,9 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_MaritalStatus](ConceptMap-VF-MaritalStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/MaritalStatus</t>
@@ -6067,9 +6085,11 @@
       <c r="X22" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -6087,7 +6107,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -6102,16 +6122,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -6120,7 +6140,7 @@
         <v>82</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>82</v>
@@ -6128,10 +6148,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -6157,14 +6177,14 @@
         <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -6213,7 +6233,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -6237,7 +6257,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -6246,7 +6266,7 @@
         <v>82</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>82</v>
@@ -6254,10 +6274,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6280,19 +6300,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -6341,7 +6361,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -6365,7 +6385,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -6374,7 +6394,7 @@
         <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>82</v>
@@ -6382,13 +6402,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
@@ -6413,10 +6433,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -6508,7 +6528,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>167</v>
@@ -6632,7 +6652,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>169</v>
@@ -6758,7 +6778,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>171</v>
@@ -6801,7 +6821,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -6884,7 +6904,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>177</v>
@@ -6947,7 +6967,7 @@
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -7006,13 +7026,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -7037,10 +7057,10 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -7132,7 +7152,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>167</v>
@@ -7256,7 +7276,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>169</v>
@@ -7382,7 +7402,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>171</v>
@@ -7425,7 +7445,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -7508,7 +7528,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>177</v>
@@ -7632,10 +7652,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7675,7 +7695,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -7758,10 +7778,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7784,7 +7804,7 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>179</v>
@@ -7882,13 +7902,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
@@ -7910,13 +7930,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -8008,7 +8028,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>149</v>
@@ -8132,7 +8152,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>156</v>
@@ -8258,7 +8278,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>156</v>
@@ -8384,7 +8404,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>167</v>
@@ -8508,7 +8528,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>169</v>
@@ -8632,7 +8652,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>171</v>
@@ -8758,7 +8778,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>177</v>
@@ -8821,7 +8841,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -8880,7 +8900,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>186</v>
@@ -9004,7 +9024,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>188</v>
@@ -9130,7 +9150,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>190</v>
@@ -9258,7 +9278,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>199</v>
@@ -9384,7 +9404,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>207</v>
@@ -9447,9 +9467,11 @@
       <c r="X49" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y49" s="2"/>
+      <c r="Y49" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9467,7 +9489,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -9482,16 +9504,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -9500,7 +9522,7 @@
         <v>82</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>82</v>
@@ -9508,10 +9530,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9537,14 +9559,14 @@
         <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9593,7 +9615,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -9617,7 +9639,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -9626,7 +9648,7 @@
         <v>82</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>82</v>
@@ -9634,10 +9656,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9660,19 +9682,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9721,7 +9743,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9745,7 +9767,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -9754,7 +9776,7 @@
         <v>82</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>82</v>
@@ -9762,13 +9784,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
@@ -9793,10 +9815,10 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9888,7 +9910,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -10012,7 +10034,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>169</v>
@@ -10138,7 +10160,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>171</v>
@@ -10181,7 +10203,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -10264,7 +10286,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>177</v>
@@ -10327,7 +10349,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -10386,13 +10408,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>156</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
@@ -10417,10 +10439,10 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10512,7 +10534,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>167</v>
@@ -10636,7 +10658,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>169</v>
@@ -10762,7 +10784,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>171</v>
@@ -10805,7 +10827,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>82</v>
@@ -10888,7 +10910,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>177</v>
@@ -11012,10 +11034,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11055,7 +11077,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>82</v>
@@ -11138,10 +11160,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11164,7 +11186,7 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>179</v>
@@ -11262,13 +11284,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>82</v>
@@ -11290,16 +11312,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -11373,7 +11395,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -11390,13 +11412,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -11418,7 +11440,7 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>136</v>
@@ -11516,7 +11538,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>149</v>
@@ -11640,7 +11662,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>156</v>
@@ -11764,10 +11786,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11807,7 +11829,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -11890,10 +11912,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11916,13 +11938,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11951,9 +11973,11 @@
       <c r="X69" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y69" s="2"/>
+      <c r="Y69" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11986,10 +12010,10 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -12012,13 +12036,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>82</v>
@@ -12040,13 +12064,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12138,7 +12162,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>149</v>
@@ -12262,7 +12286,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>156</v>
@@ -12386,10 +12410,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12429,7 +12453,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>82</v>
@@ -12512,10 +12536,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12538,13 +12562,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12573,9 +12597,11 @@
       <c r="X74" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y74" s="2"/>
+      <c r="Y74" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -12602,19 +12628,19 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>133</v>
@@ -12634,10 +12660,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12663,16 +12689,16 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -12721,7 +12747,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -12762,10 +12788,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12788,17 +12814,17 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -12847,7 +12873,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12871,16 +12897,16 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>82</v>
@@ -12888,10 +12914,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13012,10 +13038,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13138,10 +13164,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13167,16 +13193,16 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -13204,10 +13230,10 @@
         <v>181</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -13225,7 +13251,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -13249,7 +13275,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -13266,10 +13292,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13292,19 +13318,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13329,13 +13355,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -13353,7 +13379,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -13377,7 +13403,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -13386,7 +13412,7 @@
         <v>82</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>82</v>
@@ -13394,10 +13420,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13518,10 +13544,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13644,10 +13670,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13673,16 +13699,16 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -13731,7 +13757,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -13755,7 +13781,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -13764,7 +13790,7 @@
         <v>82</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>82</v>
@@ -13772,10 +13798,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13896,10 +13922,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14022,10 +14048,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14070,7 +14096,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -14124,7 +14150,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -14150,10 +14176,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14276,10 +14302,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14322,7 +14348,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -14361,7 +14387,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -14376,7 +14402,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -14385,7 +14411,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -14394,7 +14420,7 @@
         <v>82</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>82</v>
@@ -14402,10 +14428,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14431,14 +14457,14 @@
         <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -14487,7 +14513,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -14511,7 +14537,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -14520,7 +14546,7 @@
         <v>82</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>82</v>
@@ -14528,10 +14554,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14554,19 +14580,19 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -14615,7 +14641,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -14639,7 +14665,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -14648,7 +14674,7 @@
         <v>82</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>82</v>
@@ -14656,10 +14682,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14685,16 +14711,16 @@
         <v>150</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14743,7 +14769,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -14767,7 +14793,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -14776,7 +14802,7 @@
         <v>82</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>82</v>
@@ -14784,10 +14810,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14813,16 +14839,16 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -14832,10 +14858,10 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>82</v>
@@ -14871,7 +14897,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14886,7 +14912,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -14895,7 +14921,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -14904,7 +14930,7 @@
         <v>82</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>82</v>
@@ -14912,10 +14938,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14941,13 +14967,13 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14961,7 +14987,7 @@
         <v>82</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>82</v>
@@ -14997,7 +15023,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -15012,16 +15038,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -15030,7 +15056,7 @@
         <v>82</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -15038,10 +15064,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15064,13 +15090,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -15121,7 +15147,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -15145,7 +15171,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -15154,7 +15180,7 @@
         <v>82</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -15162,10 +15188,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15188,16 +15214,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15247,7 +15273,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -15271,7 +15297,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -15280,7 +15306,7 @@
         <v>82</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -15288,10 +15314,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15314,70 +15340,70 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O96" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -15401,13 +15427,13 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>82</v>
@@ -15418,10 +15444,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15444,19 +15470,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15505,7 +15531,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -15529,16 +15555,16 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>82</v>
@@ -15546,10 +15572,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15670,10 +15696,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15796,10 +15822,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15825,16 +15851,16 @@
         <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15862,10 +15888,10 @@
         <v>181</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -15883,7 +15909,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15907,7 +15933,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -15916,7 +15942,7 @@
         <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15924,10 +15950,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15953,16 +15979,16 @@
         <v>150</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -16011,7 +16037,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -16026,16 +16052,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -16044,7 +16070,7 @@
         <v>82</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -16052,14 +16078,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16081,13 +16107,13 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -16098,7 +16124,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -16137,7 +16163,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -16146,13 +16172,13 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -16161,7 +16187,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -16170,7 +16196,7 @@
         <v>82</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>82</v>
@@ -16178,14 +16204,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -16207,13 +16233,13 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16224,7 +16250,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -16263,7 +16289,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -16272,13 +16298,13 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -16287,7 +16313,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -16296,7 +16322,7 @@
         <v>82</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16304,10 +16330,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16333,10 +16359,10 @@
         <v>150</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -16387,7 +16413,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16411,7 +16437,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -16420,7 +16446,7 @@
         <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16428,10 +16454,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16457,10 +16483,10 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -16472,7 +16498,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>82</v>
@@ -16511,7 +16537,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16526,7 +16552,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -16535,7 +16561,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -16544,7 +16570,7 @@
         <v>82</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>82</v>
@@ -16552,10 +16578,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16578,17 +16604,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16637,7 +16663,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16661,7 +16687,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -16670,7 +16696,7 @@
         <v>82</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16678,10 +16704,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16704,19 +16730,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16753,7 +16779,7 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -16763,7 +16789,7 @@
         <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16787,16 +16813,16 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16804,10 +16830,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16928,10 +16954,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17054,10 +17080,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17083,10 +17109,10 @@
         <v>110</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -17116,10 +17142,10 @@
         <v>181</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -17137,7 +17163,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -17146,7 +17172,7 @@
         <v>90</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
@@ -17161,7 +17187,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -17170,7 +17196,7 @@
         <v>82</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>82</v>
@@ -17178,10 +17204,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17207,16 +17233,16 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -17265,7 +17291,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -17289,7 +17315,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -17298,7 +17324,7 @@
         <v>82</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17306,10 +17332,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17335,16 +17361,16 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -17373,7 +17399,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -17391,7 +17417,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17415,7 +17441,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -17424,7 +17450,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17432,10 +17458,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17458,16 +17484,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -17517,7 +17543,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17558,10 +17584,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17584,13 +17610,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17641,7 +17667,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17665,7 +17691,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17682,13 +17708,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -17710,19 +17736,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17771,7 +17797,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17795,16 +17821,16 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17812,10 +17838,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17936,10 +17962,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18062,10 +18088,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18091,10 +18117,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -18106,7 +18132,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -18124,10 +18150,10 @@
         <v>181</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -18145,7 +18171,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -18154,13 +18180,13 @@
         <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -18169,7 +18195,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -18178,7 +18204,7 @@
         <v>82</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -18186,10 +18212,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18215,16 +18241,16 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -18273,7 +18299,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -18288,16 +18314,16 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -18306,7 +18332,7 @@
         <v>82</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18314,10 +18340,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18343,16 +18369,16 @@
         <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18362,7 +18388,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -18381,7 +18407,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -18399,7 +18425,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18414,7 +18440,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -18423,7 +18449,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -18432,7 +18458,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18440,10 +18466,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18466,16 +18492,16 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -18525,7 +18551,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18566,10 +18592,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18592,13 +18618,13 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18649,7 +18675,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -18673,7 +18699,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -18690,13 +18716,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -18718,19 +18744,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -18779,7 +18805,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -18803,16 +18829,16 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>82</v>
@@ -18820,10 +18846,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18944,10 +18970,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19070,10 +19096,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19099,10 +19125,10 @@
         <v>110</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -19114,7 +19140,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -19132,10 +19158,10 @@
         <v>181</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -19153,7 +19179,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -19162,13 +19188,13 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -19177,7 +19203,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -19186,7 +19212,7 @@
         <v>82</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -19194,10 +19220,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19223,16 +19249,16 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -19281,7 +19307,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -19296,16 +19322,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -19314,7 +19340,7 @@
         <v>82</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19322,10 +19348,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19351,16 +19377,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -19370,7 +19396,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -19389,7 +19415,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -19407,7 +19433,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19422,7 +19448,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -19431,7 +19457,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19440,7 +19466,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19448,10 +19474,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19474,16 +19500,16 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19533,7 +19559,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19574,10 +19600,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19600,13 +19626,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19657,7 +19683,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19681,7 +19707,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19698,13 +19724,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>82</v>
@@ -19726,19 +19752,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -19787,7 +19813,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19811,16 +19837,16 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AP131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19828,10 +19854,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19952,10 +19978,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20078,10 +20104,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20107,10 +20133,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -20122,7 +20148,7 @@
         <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>82</v>
@@ -20140,10 +20166,10 @@
         <v>181</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>82</v>
@@ -20161,7 +20187,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -20170,13 +20196,13 @@
         <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -20185,7 +20211,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -20194,7 +20220,7 @@
         <v>82</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>82</v>
@@ -20202,10 +20228,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20231,16 +20257,16 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -20289,7 +20315,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -20304,16 +20330,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -20322,7 +20348,7 @@
         <v>82</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AR135" t="s" s="2">
         <v>82</v>
@@ -20330,10 +20356,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20359,16 +20385,16 @@
         <v>110</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -20378,7 +20404,7 @@
         <v>82</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>82</v>
@@ -20397,7 +20423,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -20415,7 +20441,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20430,7 +20456,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20439,7 +20465,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20448,7 +20474,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20456,10 +20482,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20482,16 +20508,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -20541,7 +20567,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20582,10 +20608,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20608,13 +20634,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20665,7 +20691,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20689,7 +20715,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -20706,10 +20732,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20735,16 +20761,16 @@
         <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20771,9 +20797,11 @@
       <c r="X139" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y139" s="2"/>
+      <c r="Y139" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="Z139" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -20791,7 +20819,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20806,25 +20834,25 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20832,10 +20860,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20858,19 +20886,19 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20919,7 +20947,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20934,36 +20962,36 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20986,19 +21014,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -21035,7 +21063,7 @@
         <v>82</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -21045,7 +21073,7 @@
         <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -21069,7 +21097,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -21078,7 +21106,7 @@
         <v>82</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>82</v>
@@ -21086,13 +21114,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -21114,19 +21142,19 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -21175,7 +21203,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -21187,19 +21215,19 @@
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>154</v>
@@ -21208,7 +21236,7 @@
         <v>82</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -21216,10 +21244,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21242,19 +21270,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21291,7 +21319,7 @@
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -21301,7 +21329,7 @@
         <v>139</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21325,16 +21353,16 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21342,10 +21370,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21466,10 +21494,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21592,10 +21620,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21621,16 +21649,16 @@
         <v>110</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21643,7 +21671,7 @@
         <v>82</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>82</v>
@@ -21658,10 +21686,10 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -21679,7 +21707,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21703,7 +21731,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -21712,7 +21740,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21720,10 +21748,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21749,13 +21777,13 @@
         <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -21769,7 +21797,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21784,10 +21812,10 @@
         <v>181</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -21805,7 +21833,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21829,7 +21857,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -21838,7 +21866,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21846,10 +21874,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21875,16 +21903,16 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21897,7 +21925,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -21933,7 +21961,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21957,7 +21985,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -21966,7 +21994,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -21974,10 +22002,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22003,10 +22031,10 @@
         <v>150</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22021,7 +22049,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -22057,7 +22085,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22081,7 +22109,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22090,7 +22118,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22098,14 +22126,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22127,10 +22155,10 @@
         <v>150</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -22145,7 +22173,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22181,7 +22209,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22205,7 +22233,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22214,7 +22242,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22222,14 +22250,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -22251,13 +22279,13 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22271,7 +22299,7 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>82</v>
@@ -22307,7 +22335,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22331,7 +22359,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22340,7 +22368,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22348,14 +22376,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22377,10 +22405,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22407,13 +22435,13 @@
         <v>82</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>82</v>
@@ -22431,7 +22459,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22455,7 +22483,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -22464,7 +22492,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22472,14 +22500,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22501,10 +22529,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22519,7 +22547,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22555,7 +22583,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22579,7 +22607,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22588,7 +22616,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22596,10 +22624,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22625,13 +22653,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22681,7 +22709,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22705,7 +22733,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22714,7 +22742,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22722,10 +22750,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22748,17 +22776,17 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22771,7 +22799,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22807,7 +22835,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22831,7 +22859,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22840,7 +22868,7 @@
         <v>82</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22848,13 +22876,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>82</v>
@@ -22876,19 +22904,19 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22937,7 +22965,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22961,16 +22989,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -22978,10 +23006,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23102,10 +23130,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23228,10 +23256,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23257,16 +23285,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23276,10 +23304,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -23294,10 +23322,10 @@
         <v>181</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -23315,7 +23343,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23330,7 +23358,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -23339,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -23348,7 +23376,7 @@
         <v>82</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23356,10 +23384,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23385,13 +23413,13 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23402,10 +23430,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -23420,10 +23448,10 @@
         <v>181</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -23441,7 +23469,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -23456,7 +23484,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -23465,7 +23493,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -23474,7 +23502,7 @@
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23482,10 +23510,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23511,16 +23539,16 @@
         <v>150</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -23533,7 +23561,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -23569,7 +23597,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23593,7 +23621,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -23602,7 +23630,7 @@
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23610,10 +23638,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23639,10 +23667,10 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23657,7 +23685,7 @@
         <v>82</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23693,7 +23721,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23708,16 +23736,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23726,7 +23754,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23734,14 +23762,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23763,10 +23791,10 @@
         <v>150</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23781,7 +23809,7 @@
         <v>82</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23817,7 +23845,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23832,16 +23860,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23850,7 +23878,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23858,14 +23886,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23887,13 +23915,13 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23907,7 +23935,7 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="U164" t="s" s="2">
         <v>82</v>
@@ -23943,7 +23971,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23967,7 +23995,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -23976,7 +24004,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -23984,14 +24012,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -24013,10 +24041,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24043,13 +24071,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -24067,7 +24095,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24082,16 +24110,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -24100,7 +24128,7 @@
         <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24108,14 +24136,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24137,10 +24165,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24155,7 +24183,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -24191,7 +24219,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24206,16 +24234,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -24224,7 +24252,7 @@
         <v>82</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24232,10 +24260,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24261,13 +24289,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24317,7 +24345,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24332,16 +24360,16 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24350,7 +24378,7 @@
         <v>82</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24358,10 +24386,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24384,17 +24412,17 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -24407,7 +24435,7 @@
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -24443,7 +24471,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24467,7 +24495,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24476,7 +24504,7 @@
         <v>82</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24484,10 +24512,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24608,10 +24636,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24734,10 +24762,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24760,16 +24788,16 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24819,7 +24847,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24828,22 +24856,22 @@
         <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -24852,7 +24880,7 @@
         <v>82</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24860,10 +24888,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24886,23 +24914,23 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q172" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="R172" t="s" s="2">
         <v>82</v>
@@ -24947,7 +24975,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -24956,22 +24984,22 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -24980,7 +25008,7 @@
         <v>82</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>82</v>
@@ -24988,10 +25016,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25014,17 +25042,17 @@
         <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -25051,9 +25079,11 @@
       <c r="X173" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y173" s="2"/>
+      <c r="Y173" t="s" s="2">
+        <v>801</v>
+      </c>
       <c r="Z173" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -25071,7 +25101,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -25086,25 +25116,25 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>82</v>
@@ -25112,10 +25142,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25138,19 +25168,19 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -25199,7 +25229,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -25223,7 +25253,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>154</v>
@@ -25232,7 +25262,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25240,10 +25270,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25266,19 +25296,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -25327,7 +25357,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -25351,7 +25381,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>
@@ -25360,7 +25390,7 @@
         <v>82</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25368,10 +25398,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25394,19 +25424,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25455,7 +25485,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25467,7 +25497,7 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -25479,7 +25509,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>154</v>
@@ -25496,10 +25526,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25620,10 +25650,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25746,14 +25776,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25775,16 +25805,16 @@
         <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -25833,7 +25863,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25874,10 +25904,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25900,17 +25930,17 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -25935,13 +25965,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -25959,7 +25989,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -25983,7 +26013,7 @@
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>154</v>
@@ -25992,7 +26022,7 @@
         <v>82</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>82</v>
@@ -26000,10 +26030,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26026,17 +26056,17 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -26085,7 +26115,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -26109,7 +26139,7 @@
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>154</v>
@@ -26118,7 +26148,7 @@
         <v>82</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>82</v>
@@ -26126,10 +26156,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26152,19 +26182,19 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -26213,7 +26243,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26237,7 +26267,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>154</v>
@@ -26246,7 +26276,7 @@
         <v>82</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>82</v>
@@ -26254,10 +26284,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26280,17 +26310,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26339,7 +26369,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26363,7 +26393,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26372,7 +26402,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26380,10 +26410,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26409,14 +26439,14 @@
         <v>110</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26444,10 +26474,10 @@
         <v>181</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -26465,7 +26495,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26489,7 +26519,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>154</v>
@@ -26498,7 +26528,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26506,10 +26536,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26532,17 +26562,17 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26591,7 +26621,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26600,7 +26630,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -26615,7 +26645,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26624,7 +26654,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26632,10 +26662,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26658,13 +26688,13 @@
         <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -26715,7 +26745,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26739,7 +26769,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26756,10 +26786,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26782,19 +26812,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26843,7 +26873,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26867,10 +26897,10 @@
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>82</v>
@@ -26884,10 +26914,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27008,10 +27038,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -27134,14 +27164,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -27163,16 +27193,16 @@
         <v>135</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -27221,7 +27251,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27262,10 +27292,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27288,19 +27318,19 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -27325,11 +27355,11 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -27347,7 +27377,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>90</v>
@@ -27362,25 +27392,25 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ191" t="s" s="2">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="AR191" t="s" s="2">
         <v>82</v>
@@ -27388,10 +27418,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27414,19 +27444,19 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -27475,7 +27505,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -27499,16 +27529,16 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>82</v>
@@ -27516,14 +27546,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27542,16 +27572,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -27601,7 +27631,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27625,7 +27655,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>154</v>
@@ -27634,7 +27664,7 @@
         <v>82</v>
       </c>
       <c r="AQ193" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="AR193" t="s" s="2">
         <v>82</v>
@@ -27642,10 +27672,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27668,19 +27698,19 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27729,7 +27759,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -27753,10 +27783,10 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>82</v>
@@ -27770,10 +27800,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27894,10 +27924,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -28020,10 +28050,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28049,13 +28079,13 @@
         <v>150</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -28105,7 +28135,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28114,7 +28144,7 @@
         <v>90</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>102</v>
@@ -28146,10 +28176,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28175,13 +28205,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -28207,13 +28237,13 @@
         <v>82</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -28231,7 +28261,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -28272,10 +28302,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28298,16 +28328,16 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -28357,7 +28387,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -28381,7 +28411,7 @@
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -28398,10 +28428,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28427,13 +28457,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28444,7 +28474,7 @@
         <v>82</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>82</v>
@@ -28483,7 +28513,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -28498,7 +28528,7 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>82</v>
@@ -28524,10 +28554,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28550,19 +28580,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -28611,7 +28641,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28635,7 +28665,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>154</v>
@@ -28652,10 +28682,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28776,10 +28806,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28902,14 +28932,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -28931,16 +28961,16 @@
         <v>135</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>82</v>
@@ -28989,7 +29019,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -29030,10 +29060,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29056,16 +29086,16 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -29115,7 +29145,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -29139,7 +29169,7 @@
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>154</v>
@@ -29148,7 +29178,7 @@
         <v>82</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="AR205" t="s" s="2">
         <v>82</v>
@@ -29156,10 +29186,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29185,10 +29215,10 @@
         <v>110</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -29218,10 +29248,10 @@
         <v>181</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>82</v>
@@ -29239,7 +29269,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>90</v>
@@ -29263,7 +29293,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2012,7 +2012,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-p-7-285:If not null then source value from (2-.351) {null}</t>
+p-7-285:If not null then source value from (2-.351) {true}</t>
   </si>
   <si>
     <t>285: source value based on PATIENT - DATE OF DEATH (2-.351) if not null</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8263" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8261" uniqueCount="970">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -785,12 +785,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>Race Text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the race concept(s).</t>
-  </si>
-  <si>
     <t>Patient.extension:race.extension:text.id</t>
   </si>
   <si>
@@ -801,6 +795,9 @@
   </si>
   <si>
     <t>Patient.extension:race.extension:text.value[x]</t>
+  </si>
+  <si>
+    <t>576-1: source value based on PATIENT - RACE INFORMATION &gt; undefinedINFORMATION (2-2 &gt; undefined2)</t>
   </si>
   <si>
     <t>Patient.extension:race.url</t>
@@ -922,12 +919,6 @@
     <t>Patient.extension:ethnicity.extension:text</t>
   </si>
   <si>
-    <t>ethnicity Text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the ethnicity concept(s).</t>
-  </si>
-  <si>
     <t>Patient.extension:ethnicity.extension:text.id</t>
   </si>
   <si>
@@ -938,6 +929,9 @@
   </si>
   <si>
     <t>Patient.extension:ethnicity.extension:text.value[x]</t>
+  </si>
+  <si>
+    <t>575-1: source value based on PATIENT - ETHNICITY INFORMATION &gt; undefinedETHNICITY INFORMATION (2-6 &gt; undefined6)</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.url</t>
@@ -7057,10 +7051,10 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -7152,7 +7146,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>167</v>
@@ -7276,21 +7270,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -7305,14 +7299,12 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -7385,7 +7377,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -7402,7 +7394,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>171</v>
@@ -7528,7 +7520,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>177</v>
@@ -7545,7 +7537,7 @@
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -7626,13 +7618,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>133</v>
@@ -7652,10 +7644,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7695,7 +7687,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -7778,10 +7770,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7804,7 +7796,7 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>179</v>
@@ -7902,13 +7894,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
@@ -7930,13 +7922,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -8028,7 +8020,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>149</v>
@@ -8152,7 +8144,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>156</v>
@@ -8278,7 +8270,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>156</v>
@@ -8404,7 +8396,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>167</v>
@@ -8528,7 +8520,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>169</v>
@@ -8652,7 +8644,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>171</v>
@@ -8778,7 +8770,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>177</v>
@@ -8841,7 +8833,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -8900,7 +8892,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>186</v>
@@ -9024,7 +9016,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>188</v>
@@ -9150,7 +9142,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>190</v>
@@ -9278,7 +9270,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>199</v>
@@ -9404,7 +9396,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>207</v>
@@ -9468,10 +9460,10 @@
         <v>181</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9504,13 +9496,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>216</v>
@@ -9530,7 +9522,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>219</v>
@@ -9656,7 +9648,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>227</v>
@@ -9784,7 +9776,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>156</v>
@@ -9815,10 +9807,10 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9910,7 +9902,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -10034,7 +10026,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>169</v>
@@ -10160,7 +10152,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>171</v>
@@ -10286,7 +10278,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>177</v>
@@ -10349,7 +10341,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -10408,7 +10400,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>156</v>
@@ -10439,10 +10431,10 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>292</v>
+        <v>136</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>293</v>
+        <v>137</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10534,7 +10526,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>167</v>
@@ -10658,21 +10650,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -10687,14 +10679,12 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -10767,7 +10757,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -10784,7 +10774,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>171</v>
@@ -10910,7 +10900,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>177</v>
@@ -10927,7 +10917,7 @@
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -11008,13 +10998,13 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>133</v>
@@ -11034,10 +11024,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11077,7 +11067,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>82</v>
@@ -11160,10 +11150,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11186,7 +11176,7 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>179</v>
@@ -11284,13 +11274,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>82</v>
@@ -11312,16 +11302,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -11395,7 +11385,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -11412,13 +11402,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -11440,7 +11430,7 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>136</v>
@@ -11538,7 +11528,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>149</v>
@@ -11662,7 +11652,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>156</v>
@@ -11786,10 +11776,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11829,7 +11819,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -11912,10 +11902,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11938,13 +11928,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11974,10 +11964,10 @@
         <v>181</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -12010,10 +12000,10 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -12036,13 +12026,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>82</v>
@@ -12064,13 +12054,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12162,7 +12152,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>149</v>
@@ -12286,7 +12276,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>156</v>
@@ -12410,10 +12400,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12453,7 +12443,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>82</v>
@@ -12536,10 +12526,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12562,13 +12552,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12598,10 +12588,10 @@
         <v>181</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -12628,19 +12618,19 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>133</v>
@@ -12660,10 +12650,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12689,16 +12679,16 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -12747,7 +12737,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -12788,10 +12778,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12814,17 +12804,17 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -12873,7 +12863,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12897,16 +12887,16 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>82</v>
@@ -12914,10 +12904,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13038,10 +13028,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13164,10 +13154,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13193,16 +13183,16 @@
         <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -13230,28 +13220,28 @@
         <v>181</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -13275,7 +13265,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -13292,10 +13282,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13318,19 +13308,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13355,31 +13345,31 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Y80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -13403,7 +13393,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -13412,7 +13402,7 @@
         <v>82</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>82</v>
@@ -13420,10 +13410,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13544,10 +13534,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13670,10 +13660,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13699,16 +13689,16 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -13757,7 +13747,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -13781,7 +13771,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -13790,7 +13780,7 @@
         <v>82</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>82</v>
@@ -13798,10 +13788,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13922,10 +13912,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14048,10 +14038,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14096,7 +14086,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -14150,7 +14140,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -14176,10 +14166,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14302,10 +14292,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14348,7 +14338,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -14402,7 +14392,7 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -14428,10 +14418,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14554,10 +14544,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14682,10 +14672,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14711,16 +14701,16 @@
         <v>150</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14769,7 +14759,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -14793,7 +14783,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -14802,7 +14792,7 @@
         <v>82</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>82</v>
@@ -14810,10 +14800,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14839,16 +14829,16 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -14858,46 +14848,46 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14912,25 +14902,25 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>82</v>
@@ -14938,10 +14928,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14967,13 +14957,13 @@
         <v>150</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14987,7 +14977,7 @@
         <v>82</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>82</v>
@@ -15023,7 +15013,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -15038,25 +15028,25 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>82</v>
@@ -15064,10 +15054,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15090,13 +15080,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -15147,7 +15137,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -15171,7 +15161,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -15180,7 +15170,7 @@
         <v>82</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>82</v>
@@ -15188,10 +15178,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15214,16 +15204,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15273,7 +15263,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -15297,7 +15287,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -15306,7 +15296,7 @@
         <v>82</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>82</v>
@@ -15314,10 +15304,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15343,23 +15333,23 @@
         <v>228</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="O96" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="R96" t="s" s="2">
         <v>82</v>
       </c>
@@ -15403,7 +15393,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -15427,13 +15417,13 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>154</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>82</v>
@@ -15444,10 +15434,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15470,19 +15460,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15531,7 +15521,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -15555,16 +15545,16 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>82</v>
@@ -15572,10 +15562,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15696,10 +15686,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15822,10 +15812,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15851,16 +15841,16 @@
         <v>110</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15888,28 +15878,28 @@
         <v>181</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15933,7 +15923,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -15942,7 +15932,7 @@
         <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>82</v>
@@ -15950,10 +15940,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15979,16 +15969,16 @@
         <v>150</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -16037,7 +16027,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -16052,25 +16042,25 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL101" t="s" s="2">
+      <c r="AN101" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AM101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>82</v>
@@ -16078,14 +16068,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16107,13 +16097,13 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -16124,79 +16114,79 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI102" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>82</v>
@@ -16204,14 +16194,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -16233,13 +16223,13 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16250,7 +16240,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -16289,7 +16279,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -16298,31 +16288,31 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>82</v>
@@ -16330,10 +16320,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16359,10 +16349,10 @@
         <v>150</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -16413,7 +16403,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -16437,7 +16427,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -16446,7 +16436,7 @@
         <v>82</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>82</v>
@@ -16454,10 +16444,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16483,10 +16473,10 @@
         <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -16498,7 +16488,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>82</v>
@@ -16537,7 +16527,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -16552,25 +16542,25 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>82</v>
@@ -16578,10 +16568,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16604,17 +16594,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -16663,7 +16653,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -16687,7 +16677,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -16696,7 +16686,7 @@
         <v>82</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>82</v>
@@ -16704,10 +16694,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16730,19 +16720,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -16779,7 +16769,7 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -16789,7 +16779,7 @@
         <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -16813,16 +16803,16 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>82</v>
@@ -16830,10 +16820,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16954,10 +16944,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17080,10 +17070,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17109,10 +17099,10 @@
         <v>110</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -17142,37 +17132,37 @@
         <v>181</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z110" t="s" s="2">
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI110" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
@@ -17187,7 +17177,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -17196,7 +17186,7 @@
         <v>82</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>82</v>
@@ -17204,10 +17194,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17233,16 +17223,16 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -17291,7 +17281,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -17315,7 +17305,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -17324,7 +17314,7 @@
         <v>82</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>82</v>
@@ -17332,10 +17322,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17361,16 +17351,16 @@
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -17399,7 +17389,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -17417,7 +17407,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -17441,7 +17431,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -17450,7 +17440,7 @@
         <v>82</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>82</v>
@@ -17458,10 +17448,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17484,16 +17474,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -17543,7 +17533,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -17584,10 +17574,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17610,13 +17600,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -17667,7 +17657,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -17691,7 +17681,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -17708,13 +17698,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -17736,19 +17726,19 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17797,7 +17787,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17821,16 +17811,16 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>82</v>
@@ -17838,10 +17828,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17962,10 +17952,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18088,10 +18078,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18117,10 +18107,10 @@
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -18132,7 +18122,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -18150,43 +18140,43 @@
         <v>181</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z118" t="s" s="2">
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -18195,7 +18185,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -18204,7 +18194,7 @@
         <v>82</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>82</v>
@@ -18212,10 +18202,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18241,16 +18231,16 @@
         <v>150</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N119" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -18299,7 +18289,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -18314,16 +18304,16 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -18332,7 +18322,7 @@
         <v>82</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>82</v>
@@ -18340,10 +18330,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18369,16 +18359,16 @@
         <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -18388,7 +18378,7 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>82</v>
@@ -18407,7 +18397,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -18425,7 +18415,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -18440,7 +18430,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -18449,7 +18439,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -18458,7 +18448,7 @@
         <v>82</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>82</v>
@@ -18466,10 +18456,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18492,16 +18482,16 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -18551,7 +18541,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -18592,10 +18582,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18618,13 +18608,13 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18675,7 +18665,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -18699,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -18716,13 +18706,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>82</v>
@@ -18744,19 +18734,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -18805,7 +18795,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -18829,16 +18819,16 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>82</v>
@@ -18846,10 +18836,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18970,10 +18960,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19096,10 +19086,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19125,10 +19115,10 @@
         <v>110</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -19140,7 +19130,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -19158,43 +19148,43 @@
         <v>181</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -19203,7 +19193,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -19212,7 +19202,7 @@
         <v>82</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>82</v>
@@ -19220,10 +19210,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19249,16 +19239,16 @@
         <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -19307,7 +19297,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -19322,16 +19312,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -19340,7 +19330,7 @@
         <v>82</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>82</v>
@@ -19348,10 +19338,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19377,16 +19367,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -19396,7 +19386,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -19415,7 +19405,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -19433,7 +19423,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -19448,7 +19438,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -19457,7 +19447,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -19466,7 +19456,7 @@
         <v>82</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>82</v>
@@ -19474,10 +19464,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19500,16 +19490,16 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19559,7 +19549,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -19600,10 +19590,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19626,13 +19616,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19683,7 +19673,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -19707,7 +19697,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19724,13 +19714,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>82</v>
@@ -19752,19 +19742,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -19813,7 +19803,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -19837,16 +19827,16 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AP131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ131" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ131" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>82</v>
@@ -19854,10 +19844,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19978,10 +19968,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20104,10 +20094,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20133,10 +20123,10 @@
         <v>110</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -20148,7 +20138,7 @@
         <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>82</v>
@@ -20166,43 +20156,43 @@
         <v>181</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z134" t="s" s="2">
+      <c r="AG134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI134" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -20211,7 +20201,7 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -20220,7 +20210,7 @@
         <v>82</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>82</v>
@@ -20228,10 +20218,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20257,16 +20247,16 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -20315,7 +20305,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -20330,16 +20320,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -20348,7 +20338,7 @@
         <v>82</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AR135" t="s" s="2">
         <v>82</v>
@@ -20356,10 +20346,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20385,16 +20375,16 @@
         <v>110</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -20404,7 +20394,7 @@
         <v>82</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>82</v>
@@ -20423,7 +20413,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -20441,7 +20431,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -20456,7 +20446,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -20465,7 +20455,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -20474,7 +20464,7 @@
         <v>82</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>82</v>
@@ -20482,10 +20472,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20508,16 +20498,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -20567,7 +20557,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -20608,10 +20598,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20634,13 +20624,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20691,7 +20681,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -20715,7 +20705,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -20732,10 +20722,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20761,16 +20751,16 @@
         <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -20798,10 +20788,10 @@
         <v>181</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -20819,7 +20809,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -20834,25 +20824,25 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AL139" t="s" s="2">
+      <c r="AN139" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AM139" t="s" s="2">
+      <c r="AP139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ139" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>82</v>
@@ -20860,10 +20850,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20886,19 +20876,19 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -20947,7 +20937,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -20962,36 +20952,36 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AL140" t="s" s="2">
+      <c r="AN140" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM140" t="s" s="2">
+      <c r="AO140" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AN140" t="s" s="2">
+      <c r="AP140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ140" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AO140" t="s" s="2">
+      <c r="AR140" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ140" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AR140" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21014,19 +21004,19 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -21063,7 +21053,7 @@
         <v>82</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -21073,7 +21063,7 @@
         <v>139</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -21097,7 +21087,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>154</v>
@@ -21106,7 +21096,7 @@
         <v>82</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>82</v>
@@ -21114,13 +21104,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -21142,19 +21132,19 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -21203,7 +21193,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -21215,19 +21205,19 @@
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AL142" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="AK142" t="s" s="2">
+      <c r="AM142" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AL142" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>650</v>
-      </c>
       <c r="AN142" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>154</v>
@@ -21236,7 +21226,7 @@
         <v>82</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>82</v>
@@ -21244,10 +21234,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21270,19 +21260,19 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -21319,7 +21309,7 @@
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -21329,7 +21319,7 @@
         <v>139</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -21353,16 +21343,16 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AP143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ143" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ143" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>82</v>
@@ -21370,10 +21360,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21494,10 +21484,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21620,10 +21610,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21649,16 +21639,16 @@
         <v>110</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -21671,7 +21661,7 @@
         <v>82</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>82</v>
@@ -21686,28 +21676,28 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF146" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -21731,7 +21721,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -21740,7 +21730,7 @@
         <v>82</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>82</v>
@@ -21748,10 +21738,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21777,13 +21767,13 @@
         <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -21797,7 +21787,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -21812,28 +21802,28 @@
         <v>181</v>
       </c>
       <c r="Y147" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -21857,7 +21847,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -21866,7 +21856,7 @@
         <v>82</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>82</v>
@@ -21874,10 +21864,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21903,16 +21893,16 @@
         <v>150</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="M148" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="O148" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -21925,7 +21915,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -21961,7 +21951,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -21985,7 +21975,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -21994,7 +21984,7 @@
         <v>82</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>82</v>
@@ -22002,10 +21992,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22031,10 +22021,10 @@
         <v>150</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22049,7 +22039,7 @@
         <v>82</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>82</v>
@@ -22085,7 +22075,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -22109,7 +22099,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -22118,7 +22108,7 @@
         <v>82</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>82</v>
@@ -22126,14 +22116,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22155,10 +22145,10 @@
         <v>150</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -22173,7 +22163,7 @@
         <v>82</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>82</v>
@@ -22209,7 +22199,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -22233,7 +22223,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -22242,7 +22232,7 @@
         <v>82</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>82</v>
@@ -22250,14 +22240,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -22279,13 +22269,13 @@
         <v>150</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22299,7 +22289,7 @@
         <v>82</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>82</v>
@@ -22335,7 +22325,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -22359,7 +22349,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -22368,7 +22358,7 @@
         <v>82</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>82</v>
@@ -22376,14 +22366,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -22405,10 +22395,10 @@
         <v>150</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22435,31 +22425,31 @@
         <v>82</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Y152" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF152" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -22483,7 +22473,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -22492,7 +22482,7 @@
         <v>82</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>82</v>
@@ -22500,14 +22490,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22529,10 +22519,10 @@
         <v>150</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22547,7 +22537,7 @@
         <v>82</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>82</v>
@@ -22583,7 +22573,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -22607,7 +22597,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
@@ -22616,7 +22606,7 @@
         <v>82</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>82</v>
@@ -22624,10 +22614,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22653,13 +22643,13 @@
         <v>150</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22709,7 +22699,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -22733,7 +22723,7 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
@@ -22742,7 +22732,7 @@
         <v>82</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>82</v>
@@ -22750,10 +22740,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22776,17 +22766,17 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -22799,7 +22789,7 @@
         <v>82</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>82</v>
@@ -22835,7 +22825,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -22859,7 +22849,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -22868,7 +22858,7 @@
         <v>82</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>82</v>
@@ -22876,13 +22866,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>82</v>
@@ -22904,19 +22894,19 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -22965,7 +22955,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -22989,16 +22979,16 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ156" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ156" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>82</v>
@@ -23006,10 +22996,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23130,10 +23120,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23256,10 +23246,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23285,16 +23275,16 @@
         <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -23304,10 +23294,10 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>82</v>
@@ -23322,28 +23312,28 @@
         <v>181</v>
       </c>
       <c r="Y159" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF159" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -23358,7 +23348,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -23367,7 +23357,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -23376,7 +23366,7 @@
         <v>82</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>82</v>
@@ -23384,10 +23374,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23413,13 +23403,13 @@
         <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23430,10 +23420,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -23448,28 +23438,28 @@
         <v>181</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF160" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -23484,7 +23474,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -23493,7 +23483,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -23502,7 +23492,7 @@
         <v>82</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>82</v>
@@ -23510,10 +23500,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23539,16 +23529,16 @@
         <v>150</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="M161" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="O161" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -23561,7 +23551,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -23597,7 +23587,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -23621,7 +23611,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -23630,7 +23620,7 @@
         <v>82</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>82</v>
@@ -23638,10 +23628,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23667,10 +23657,10 @@
         <v>150</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23685,7 +23675,7 @@
         <v>82</v>
       </c>
       <c r="T162" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="U162" t="s" s="2">
         <v>82</v>
@@ -23721,7 +23711,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -23736,16 +23726,16 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AM162" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="AL162" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="AN162" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -23754,7 +23744,7 @@
         <v>82</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>82</v>
@@ -23762,14 +23752,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -23791,10 +23781,10 @@
         <v>150</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23809,7 +23799,7 @@
         <v>82</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>82</v>
@@ -23845,7 +23835,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -23860,16 +23850,16 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AM163" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="AL163" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>758</v>
-      </c>
       <c r="AN163" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -23878,7 +23868,7 @@
         <v>82</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>82</v>
@@ -23886,14 +23876,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23915,13 +23905,13 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23935,7 +23925,7 @@
         <v>82</v>
       </c>
       <c r="T164" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="U164" t="s" s="2">
         <v>82</v>
@@ -23971,7 +23961,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -23995,7 +23985,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -24004,7 +23994,7 @@
         <v>82</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>82</v>
@@ -24012,14 +24002,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -24041,10 +24031,10 @@
         <v>150</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24071,31 +24061,31 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Y165" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -24110,16 +24100,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AM165" t="s" s="2">
         <v>761</v>
       </c>
-      <c r="AL165" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>763</v>
-      </c>
       <c r="AN165" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -24128,7 +24118,7 @@
         <v>82</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AR165" t="s" s="2">
         <v>82</v>
@@ -24136,14 +24126,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24165,10 +24155,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -24183,7 +24173,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -24219,7 +24209,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -24234,16 +24224,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -24252,7 +24242,7 @@
         <v>82</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>82</v>
@@ -24260,10 +24250,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24289,13 +24279,13 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24345,7 +24335,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -24360,16 +24350,16 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -24378,7 +24368,7 @@
         <v>82</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>82</v>
@@ -24386,10 +24376,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24412,17 +24402,17 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -24435,7 +24425,7 @@
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -24471,7 +24461,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -24495,7 +24485,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -24504,7 +24494,7 @@
         <v>82</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>82</v>
@@ -24512,10 +24502,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24636,10 +24626,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24762,10 +24752,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24788,16 +24778,16 @@
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N171" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24847,7 +24837,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -24856,31 +24846,31 @@
         <v>90</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="AN171" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="AL171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM171" t="s" s="2">
+      <c r="AO171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ171" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ171" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>82</v>
@@ -24888,10 +24878,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24914,23 +24904,23 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q172" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="R172" t="s" s="2">
         <v>82</v>
@@ -24975,7 +24965,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -24984,31 +24974,31 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AN172" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="AL172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM172" t="s" s="2">
+      <c r="AO172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ172" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ172" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>82</v>
@@ -25016,10 +25006,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25042,17 +25032,17 @@
         <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -25080,10 +25070,10 @@
         <v>181</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -25101,7 +25091,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -25116,25 +25106,25 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AM173" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="AL173" t="s" s="2">
+      <c r="AN173" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="AM173" t="s" s="2">
+      <c r="AO173" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="AN173" t="s" s="2">
+      <c r="AP173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ173" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="AP173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ173" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>82</v>
@@ -25142,10 +25132,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25168,19 +25158,19 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="L174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>811</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>814</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -25229,7 +25219,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -25253,7 +25243,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>154</v>
@@ -25262,7 +25252,7 @@
         <v>82</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>82</v>
@@ -25270,10 +25260,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25296,19 +25286,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>818</v>
       </c>
-      <c r="L175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -25357,7 +25347,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -25381,7 +25371,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>154</v>
@@ -25390,7 +25380,7 @@
         <v>82</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>82</v>
@@ -25398,10 +25388,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25424,19 +25414,19 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>826</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="O176" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -25485,7 +25475,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -25497,7 +25487,7 @@
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -25509,7 +25499,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>154</v>
@@ -25526,10 +25516,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25650,10 +25640,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25776,14 +25766,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25805,16 +25795,16 @@
         <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -25863,7 +25853,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -25904,10 +25894,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25930,17 +25920,17 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -25965,13 +25955,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -25989,7 +25979,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -26013,7 +26003,7 @@
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>154</v>
@@ -26022,7 +26012,7 @@
         <v>82</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>82</v>
@@ -26030,10 +26020,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26056,17 +26046,17 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -26115,7 +26105,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -26139,7 +26129,7 @@
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>154</v>
@@ -26148,7 +26138,7 @@
         <v>82</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>82</v>
@@ -26156,10 +26146,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26182,19 +26172,19 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="M182" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>856</v>
-      </c>
       <c r="O182" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -26243,7 +26233,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -26267,7 +26257,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>154</v>
@@ -26276,7 +26266,7 @@
         <v>82</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>82</v>
@@ -26284,10 +26274,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26310,17 +26300,17 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -26369,7 +26359,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -26393,7 +26383,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>154</v>
@@ -26402,7 +26392,7 @@
         <v>82</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>82</v>
@@ -26410,10 +26400,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26439,14 +26429,14 @@
         <v>110</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -26474,10 +26464,10 @@
         <v>181</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -26495,7 +26485,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -26519,7 +26509,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>154</v>
@@ -26528,7 +26518,7 @@
         <v>82</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>82</v>
@@ -26536,10 +26526,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26562,17 +26552,17 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -26621,7 +26611,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -26630,7 +26620,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -26645,7 +26635,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>154</v>
@@ -26654,7 +26644,7 @@
         <v>82</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>82</v>
@@ -26662,10 +26652,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26688,13 +26678,13 @@
         <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -26745,7 +26735,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -26769,7 +26759,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>154</v>
@@ -26786,10 +26776,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26812,19 +26802,19 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>884</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -26873,7 +26863,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -26897,10 +26887,10 @@
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>82</v>
@@ -26914,10 +26904,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27038,10 +27028,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -27164,14 +27154,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -27193,16 +27183,16 @@
         <v>135</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -27251,7 +27241,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -27292,10 +27282,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27318,19 +27308,19 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L191" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="N191" t="s" s="2">
         <v>891</v>
       </c>
-      <c r="M191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>892</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -27355,11 +27345,11 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -27377,7 +27367,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>90</v>
@@ -27392,25 +27382,25 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="AL191" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="AM191" t="s" s="2">
         <v>896</v>
       </c>
-      <c r="AL191" t="s" s="2">
+      <c r="AN191" t="s" s="2">
         <v>897</v>
       </c>
-      <c r="AM191" t="s" s="2">
+      <c r="AO191" t="s" s="2">
         <v>898</v>
       </c>
-      <c r="AN191" t="s" s="2">
+      <c r="AP191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ191" t="s" s="2">
         <v>899</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="AP191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ191" t="s" s="2">
-        <v>901</v>
       </c>
       <c r="AR191" t="s" s="2">
         <v>82</v>
@@ -27418,10 +27408,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27447,16 +27437,16 @@
         <v>228</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="N192" t="s" s="2">
         <v>903</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="O192" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>906</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -27505,7 +27495,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -27529,16 +27519,16 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="AO192" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="AP192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ192" t="s" s="2">
         <v>907</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ192" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>82</v>
@@ -27546,14 +27536,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27572,16 +27562,16 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>912</v>
       </c>
-      <c r="L193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>915</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -27631,7 +27621,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -27655,7 +27645,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>154</v>
@@ -27664,7 +27654,7 @@
         <v>82</v>
       </c>
       <c r="AQ193" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AR193" t="s" s="2">
         <v>82</v>
@@ -27672,10 +27662,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27698,19 +27688,19 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>919</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>920</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -27759,7 +27749,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -27783,10 +27773,10 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>82</v>
@@ -27800,10 +27790,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27924,10 +27914,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -28050,10 +28040,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28079,13 +28069,13 @@
         <v>150</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="M197" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>927</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>929</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -28135,7 +28125,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -28144,7 +28134,7 @@
         <v>90</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>102</v>
@@ -28176,10 +28166,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28205,13 +28195,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="M198" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="N198" t="s" s="2">
         <v>933</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>934</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>935</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -28237,31 +28227,31 @@
         <v>82</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Y198" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="Z198" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="AA198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF198" t="s" s="2">
         <v>936</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>938</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -28302,10 +28292,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28328,16 +28318,16 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="N199" t="s" s="2">
         <v>940</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -28387,7 +28377,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -28411,7 +28401,7 @@
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -28428,10 +28418,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -28457,13 +28447,13 @@
         <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="M200" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="N200" t="s" s="2">
         <v>946</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>947</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>948</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -28474,7 +28464,7 @@
         <v>82</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>82</v>
@@ -28513,7 +28503,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -28528,7 +28518,7 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>82</v>
@@ -28554,10 +28544,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -28580,19 +28570,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="M201" t="s" s="2">
+      <c r="O201" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>956</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -28641,7 +28631,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -28665,7 +28655,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>154</v>
@@ -28682,10 +28672,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28806,10 +28796,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28932,14 +28922,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -28961,16 +28951,16 @@
         <v>135</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>82</v>
@@ -29019,7 +29009,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -29060,10 +29050,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -29086,16 +29076,16 @@
         <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="L205" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="M205" t="s" s="2">
         <v>962</v>
       </c>
-      <c r="L205" t="s" s="2">
+      <c r="N205" t="s" s="2">
         <v>963</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>964</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>965</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -29145,7 +29135,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>90</v>
@@ -29169,7 +29159,7 @@
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>154</v>
@@ -29178,7 +29168,7 @@
         <v>82</v>
       </c>
       <c r="AQ205" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="AR205" t="s" s="2">
         <v>82</v>
@@ -29186,10 +29176,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -29215,10 +29205,10 @@
         <v>110</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -29248,10 +29238,10 @@
         <v>181</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>82</v>
@@ -29269,7 +29259,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>90</v>
@@ -29293,7 +29283,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>154</v>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Patient.extension:race.extension:text.value[x]</t>
   </si>
   <si>
-    <t>576-1: source value based on PATIENT - RACE INFORMATION &gt; undefinedINFORMATION (2-2 &gt; undefined2)</t>
+    <t>576-1: source value based on PATIENT - RACE INFORMATION (2-2)</t>
   </si>
   <si>
     <t>Patient.extension:race.url</t>
@@ -931,7 +931,7 @@
     <t>Patient.extension:ethnicity.extension:text.value[x]</t>
   </si>
   <si>
-    <t>575-1: source value based on PATIENT - ETHNICITY INFORMATION &gt; undefinedETHNICITY INFORMATION (2-6 &gt; undefined6)</t>
+    <t>575-1: source value based on PATIENT - ETHNICITY INFORMATION (2-6)</t>
   </si>
   <si>
     <t>Patient.extension:ethnicity.url</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient.xlsx
+++ b/docs/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
